--- a/Dados semanais com gráficos.xlsx
+++ b/Dados semanais com gráficos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ab19778ff6fa8e3f/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{CD0323FD-5F08-4711-8DA8-A123DF3DE36A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FB4E8EF-3528-4DBF-8B35-790C450FE2C1}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="13_ncr:1_{CD0323FD-5F08-4711-8DA8-A123DF3DE36A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79E34BBA-CF7A-44D8-A3CC-E15D137CB9A8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Produto1" sheetId="1" r:id="rId1"/>
@@ -186,10 +186,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -513,7 +509,7 @@
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" customWidth="1"/>
     <col min="4" max="4" width="43.28515625" customWidth="1"/>
     <col min="5" max="5" width="12.28515625" customWidth="1"/>
@@ -535,7 +531,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>20180101</v>
+        <v>20170101</v>
       </c>
       <c r="C2">
         <f ca="1">(B2/$C$2)*100</f>
@@ -547,10 +543,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>20180107</v>
+        <v>20170107</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:D66" ca="1" si="0">(B3/$C$2)*100</f>
+        <f t="shared" ref="C3:C66" ca="1" si="0">(B3/$C$2)*100</f>
         <v>140.23891857906318</v>
       </c>
     </row>
@@ -559,7 +555,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>20180114</v>
+        <v>20170114</v>
       </c>
       <c r="C4">
         <f t="shared" ca="1" si="0"/>
@@ -571,7 +567,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>20180121</v>
+        <v>20170121</v>
       </c>
       <c r="C5">
         <f t="shared" ca="1" si="0"/>
@@ -583,7 +579,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>20180128</v>
+        <v>20170128</v>
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="0"/>
@@ -595,7 +591,7 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>20180197</v>
+        <v>20170197</v>
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="0"/>
@@ -607,7 +603,7 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>20180204</v>
+        <v>20170204</v>
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="0"/>
@@ -619,7 +615,7 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>20180211</v>
+        <v>20170211</v>
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="0"/>
@@ -631,7 +627,7 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>20180218</v>
+        <v>20170218</v>
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="0"/>
@@ -643,7 +639,7 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>20180225</v>
+        <v>20170225</v>
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="0"/>
@@ -655,7 +651,7 @@
         <v>9</v>
       </c>
       <c r="B12">
-        <v>20180297</v>
+        <v>20170297</v>
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="0"/>
@@ -667,7 +663,7 @@
         <v>10</v>
       </c>
       <c r="B13">
-        <v>20180304</v>
+        <v>20170304</v>
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="0"/>
@@ -679,7 +675,7 @@
         <v>11</v>
       </c>
       <c r="B14">
-        <v>20180311</v>
+        <v>20170311</v>
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="0"/>
@@ -691,7 +687,7 @@
         <v>12</v>
       </c>
       <c r="B15">
-        <v>20180318</v>
+        <v>20170318</v>
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="0"/>
@@ -703,7 +699,7 @@
         <v>13</v>
       </c>
       <c r="B16">
-        <v>20180325</v>
+        <v>20170325</v>
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="0"/>
@@ -715,7 +711,7 @@
         <v>14</v>
       </c>
       <c r="B17">
-        <v>20180401</v>
+        <v>20170401</v>
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="0"/>
@@ -727,7 +723,7 @@
         <v>15</v>
       </c>
       <c r="B18">
-        <v>20180408</v>
+        <v>20170408</v>
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="0"/>
@@ -739,7 +735,7 @@
         <v>16</v>
       </c>
       <c r="B19">
-        <v>20180415</v>
+        <v>20170415</v>
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="0"/>
@@ -751,7 +747,7 @@
         <v>17</v>
       </c>
       <c r="B20">
-        <v>20180422</v>
+        <v>20170422</v>
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="0"/>
@@ -763,7 +759,7 @@
         <v>18</v>
       </c>
       <c r="B21">
-        <v>20180429</v>
+        <v>20170429</v>
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="0"/>
@@ -775,7 +771,7 @@
         <v>18</v>
       </c>
       <c r="B22">
-        <v>20180499</v>
+        <v>20170499</v>
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="0"/>
@@ -787,7 +783,7 @@
         <v>19</v>
       </c>
       <c r="B23">
-        <v>20180506</v>
+        <v>20170506</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="0"/>
@@ -799,7 +795,7 @@
         <v>20</v>
       </c>
       <c r="B24">
-        <v>20180513</v>
+        <v>20170513</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="0"/>
@@ -811,7 +807,7 @@
         <v>21</v>
       </c>
       <c r="B25">
-        <v>20180520</v>
+        <v>20170520</v>
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="0"/>
@@ -823,7 +819,7 @@
         <v>22</v>
       </c>
       <c r="B26">
-        <v>20180527</v>
+        <v>20170527</v>
       </c>
       <c r="C26">
         <f t="shared" ca="1" si="0"/>
@@ -835,7 +831,7 @@
         <v>22</v>
       </c>
       <c r="B27">
-        <v>20180596</v>
+        <v>20170596</v>
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="0"/>
@@ -847,7 +843,7 @@
         <v>23</v>
       </c>
       <c r="B28">
-        <v>20180603</v>
+        <v>20170603</v>
       </c>
       <c r="C28">
         <f t="shared" ca="1" si="0"/>
@@ -859,7 +855,7 @@
         <v>24</v>
       </c>
       <c r="B29">
-        <v>20180610</v>
+        <v>20170610</v>
       </c>
       <c r="C29">
         <f t="shared" ca="1" si="0"/>
@@ -871,7 +867,7 @@
         <v>25</v>
       </c>
       <c r="B30">
-        <v>20180617</v>
+        <v>20170617</v>
       </c>
       <c r="C30">
         <f t="shared" ca="1" si="0"/>
@@ -883,7 +879,7 @@
         <v>26</v>
       </c>
       <c r="B31">
-        <v>20180624</v>
+        <v>20170624</v>
       </c>
       <c r="C31">
         <f t="shared" ca="1" si="0"/>
@@ -895,7 +891,7 @@
         <v>27</v>
       </c>
       <c r="B32">
-        <v>20180701</v>
+        <v>20170701</v>
       </c>
       <c r="C32">
         <f t="shared" ca="1" si="0"/>
@@ -907,7 +903,7 @@
         <v>28</v>
       </c>
       <c r="B33">
-        <v>20180708</v>
+        <v>20170708</v>
       </c>
       <c r="C33">
         <f t="shared" ca="1" si="0"/>
@@ -919,7 +915,7 @@
         <v>29</v>
       </c>
       <c r="B34">
-        <v>20180715</v>
+        <v>20170715</v>
       </c>
       <c r="C34">
         <f t="shared" ca="1" si="0"/>
@@ -931,7 +927,7 @@
         <v>30</v>
       </c>
       <c r="B35">
-        <v>20180722</v>
+        <v>20170722</v>
       </c>
       <c r="C35">
         <f t="shared" ca="1" si="0"/>
@@ -943,7 +939,7 @@
         <v>31</v>
       </c>
       <c r="B36">
-        <v>20180729</v>
+        <v>20170729</v>
       </c>
       <c r="C36">
         <f t="shared" ca="1" si="0"/>
@@ -955,7 +951,7 @@
         <v>31</v>
       </c>
       <c r="B37">
-        <v>20180798</v>
+        <v>20170798</v>
       </c>
       <c r="C37">
         <f t="shared" ca="1" si="0"/>
@@ -967,7 +963,7 @@
         <v>32</v>
       </c>
       <c r="B38">
-        <v>20180805</v>
+        <v>20170805</v>
       </c>
       <c r="C38">
         <f t="shared" ca="1" si="0"/>
@@ -979,7 +975,7 @@
         <v>33</v>
       </c>
       <c r="B39">
-        <v>20180812</v>
+        <v>20170812</v>
       </c>
       <c r="C39">
         <f t="shared" ca="1" si="0"/>
@@ -991,7 +987,7 @@
         <v>34</v>
       </c>
       <c r="B40">
-        <v>20180819</v>
+        <v>20170819</v>
       </c>
       <c r="C40">
         <f t="shared" ca="1" si="0"/>
@@ -1003,7 +999,7 @@
         <v>35</v>
       </c>
       <c r="B41">
-        <v>20180826</v>
+        <v>20170826</v>
       </c>
       <c r="C41">
         <f t="shared" ca="1" si="0"/>
@@ -1015,7 +1011,7 @@
         <v>36</v>
       </c>
       <c r="B42">
-        <v>20180902</v>
+        <v>20170902</v>
       </c>
       <c r="C42">
         <f t="shared" ca="1" si="0"/>
@@ -1027,7 +1023,7 @@
         <v>37</v>
       </c>
       <c r="B43">
-        <v>20180909</v>
+        <v>20170909</v>
       </c>
       <c r="C43">
         <f t="shared" ca="1" si="0"/>
@@ -1039,7 +1035,7 @@
         <v>38</v>
       </c>
       <c r="B44">
-        <v>20180916</v>
+        <v>20170916</v>
       </c>
       <c r="C44">
         <f t="shared" ca="1" si="0"/>
@@ -1051,7 +1047,7 @@
         <v>39</v>
       </c>
       <c r="B45">
-        <v>20180923</v>
+        <v>20170923</v>
       </c>
       <c r="C45">
         <f t="shared" ca="1" si="0"/>
@@ -1063,7 +1059,7 @@
         <v>40</v>
       </c>
       <c r="B46">
-        <v>20181000</v>
+        <v>20171000</v>
       </c>
       <c r="C46">
         <f t="shared" ca="1" si="0"/>
@@ -1075,7 +1071,7 @@
         <v>41</v>
       </c>
       <c r="B47">
-        <v>20181007</v>
+        <v>20171007</v>
       </c>
       <c r="C47">
         <f t="shared" ca="1" si="0"/>
@@ -1087,7 +1083,7 @@
         <v>42</v>
       </c>
       <c r="B48">
-        <v>20181014</v>
+        <v>20171014</v>
       </c>
       <c r="C48">
         <f t="shared" ca="1" si="0"/>
@@ -1099,7 +1095,7 @@
         <v>43</v>
       </c>
       <c r="B49">
-        <v>20181021</v>
+        <v>20171021</v>
       </c>
       <c r="C49">
         <f t="shared" ca="1" si="0"/>
@@ -1111,7 +1107,7 @@
         <v>44</v>
       </c>
       <c r="B50">
-        <v>20181028</v>
+        <v>20171028</v>
       </c>
       <c r="C50">
         <f t="shared" ca="1" si="0"/>
@@ -1123,7 +1119,7 @@
         <v>44</v>
       </c>
       <c r="B51">
-        <v>20181097</v>
+        <v>20171097</v>
       </c>
       <c r="C51">
         <f t="shared" ca="1" si="0"/>
@@ -1135,7 +1131,7 @@
         <v>45</v>
       </c>
       <c r="B52">
-        <v>20181104</v>
+        <v>20171104</v>
       </c>
       <c r="C52">
         <f t="shared" ca="1" si="0"/>
@@ -1147,7 +1143,7 @@
         <v>46</v>
       </c>
       <c r="B53">
-        <v>20181111</v>
+        <v>20171111</v>
       </c>
       <c r="C53">
         <f t="shared" ca="1" si="0"/>
@@ -1159,7 +1155,7 @@
         <v>47</v>
       </c>
       <c r="B54">
-        <v>20181118</v>
+        <v>20171118</v>
       </c>
       <c r="C54">
         <f t="shared" ca="1" si="0"/>
@@ -1171,7 +1167,7 @@
         <v>48</v>
       </c>
       <c r="B55">
-        <v>20181125</v>
+        <v>20171125</v>
       </c>
       <c r="C55">
         <f t="shared" ca="1" si="0"/>
@@ -1183,7 +1179,7 @@
         <v>48</v>
       </c>
       <c r="B56">
-        <v>20181195</v>
+        <v>20171195</v>
       </c>
       <c r="C56">
         <f t="shared" ca="1" si="0"/>
@@ -1195,7 +1191,7 @@
         <v>49</v>
       </c>
       <c r="B57">
-        <v>20181202</v>
+        <v>20171202</v>
       </c>
       <c r="C57">
         <f t="shared" ca="1" si="0"/>
@@ -1207,7 +1203,7 @@
         <v>50</v>
       </c>
       <c r="B58">
-        <v>20181209</v>
+        <v>20171209</v>
       </c>
       <c r="C58">
         <f t="shared" ca="1" si="0"/>
@@ -1219,7 +1215,7 @@
         <v>51</v>
       </c>
       <c r="B59">
-        <v>20181216</v>
+        <v>20171216</v>
       </c>
       <c r="C59">
         <f t="shared" ca="1" si="0"/>
@@ -1231,7 +1227,7 @@
         <v>52</v>
       </c>
       <c r="B60">
-        <v>20181223</v>
+        <v>20171223</v>
       </c>
       <c r="C60">
         <f t="shared" ca="1" si="0"/>
@@ -1243,7 +1239,7 @@
         <v>53</v>
       </c>
       <c r="B61">
-        <v>20181230</v>
+        <v>20171230</v>
       </c>
       <c r="C61">
         <f t="shared" ca="1" si="0"/>
@@ -1255,7 +1251,7 @@
         <v>1</v>
       </c>
       <c r="B62">
-        <v>20190101</v>
+        <v>20180101</v>
       </c>
       <c r="C62">
         <f t="shared" ca="1" si="0"/>
@@ -1267,7 +1263,7 @@
         <v>2</v>
       </c>
       <c r="B63">
-        <v>20190106</v>
+        <v>20180106</v>
       </c>
       <c r="C63">
         <f t="shared" ca="1" si="0"/>
@@ -1279,7 +1275,7 @@
         <v>3</v>
       </c>
       <c r="B64">
-        <v>20190113</v>
+        <v>20180113</v>
       </c>
       <c r="C64">
         <f t="shared" ca="1" si="0"/>
@@ -1291,7 +1287,7 @@
         <v>4</v>
       </c>
       <c r="B65">
-        <v>20190120</v>
+        <v>20180120</v>
       </c>
       <c r="C65">
         <f t="shared" ca="1" si="0"/>
@@ -1303,7 +1299,7 @@
         <v>5</v>
       </c>
       <c r="B66">
-        <v>20190127</v>
+        <v>20180127</v>
       </c>
       <c r="C66">
         <f t="shared" ca="1" si="0"/>
@@ -1315,10 +1311,10 @@
         <v>5</v>
       </c>
       <c r="B67">
-        <v>20190196</v>
+        <v>20180196</v>
       </c>
       <c r="C67">
-        <f t="shared" ref="C67:D130" ca="1" si="1">(B67/$C$2)*100</f>
+        <f t="shared" ref="C67:C130" ca="1" si="1">(B67/$C$2)*100</f>
         <v>64.350833071361208</v>
       </c>
     </row>
@@ -1327,7 +1323,7 @@
         <v>6</v>
       </c>
       <c r="B68">
-        <v>20190203</v>
+        <v>20180203</v>
       </c>
       <c r="C68">
         <f t="shared" ca="1" si="1"/>
@@ -1339,7 +1335,7 @@
         <v>7</v>
       </c>
       <c r="B69">
-        <v>20190210</v>
+        <v>20180210</v>
       </c>
       <c r="C69">
         <f t="shared" ca="1" si="1"/>
@@ -1351,7 +1347,7 @@
         <v>8</v>
       </c>
       <c r="B70">
-        <v>20190217</v>
+        <v>20180217</v>
       </c>
       <c r="C70">
         <f t="shared" ca="1" si="1"/>
@@ -1363,7 +1359,7 @@
         <v>9</v>
       </c>
       <c r="B71">
-        <v>20190224</v>
+        <v>20180224</v>
       </c>
       <c r="C71">
         <f t="shared" ca="1" si="1"/>
@@ -1375,7 +1371,7 @@
         <v>9</v>
       </c>
       <c r="B72">
-        <v>20190296</v>
+        <v>20180296</v>
       </c>
       <c r="C72">
         <f t="shared" ca="1" si="1"/>
@@ -1387,7 +1383,7 @@
         <v>10</v>
       </c>
       <c r="B73">
-        <v>20190303</v>
+        <v>20180303</v>
       </c>
       <c r="C73">
         <f t="shared" ca="1" si="1"/>
@@ -1399,7 +1395,7 @@
         <v>11</v>
       </c>
       <c r="B74">
-        <v>20190310</v>
+        <v>20180310</v>
       </c>
       <c r="C74">
         <f t="shared" ca="1" si="1"/>
@@ -1411,7 +1407,7 @@
         <v>12</v>
       </c>
       <c r="B75">
-        <v>20190317</v>
+        <v>20180317</v>
       </c>
       <c r="C75">
         <f t="shared" ca="1" si="1"/>
@@ -1423,7 +1419,7 @@
         <v>13</v>
       </c>
       <c r="B76">
-        <v>20190324</v>
+        <v>20180324</v>
       </c>
       <c r="C76">
         <f t="shared" ca="1" si="1"/>
@@ -1435,7 +1431,7 @@
         <v>14</v>
       </c>
       <c r="B77">
-        <v>20190400</v>
+        <v>20180400</v>
       </c>
       <c r="C77">
         <f t="shared" ca="1" si="1"/>
@@ -1447,7 +1443,7 @@
         <v>15</v>
       </c>
       <c r="B78">
-        <v>20190407</v>
+        <v>20180407</v>
       </c>
       <c r="C78">
         <f t="shared" ca="1" si="1"/>
@@ -1459,7 +1455,7 @@
         <v>16</v>
       </c>
       <c r="B79">
-        <v>20190414</v>
+        <v>20180414</v>
       </c>
       <c r="C79">
         <f t="shared" ca="1" si="1"/>
@@ -1471,7 +1467,7 @@
         <v>17</v>
       </c>
       <c r="B80">
-        <v>20190421</v>
+        <v>20180421</v>
       </c>
       <c r="C80">
         <f t="shared" ca="1" si="1"/>
@@ -1483,7 +1479,7 @@
         <v>18</v>
       </c>
       <c r="B81">
-        <v>20190428</v>
+        <v>20180428</v>
       </c>
       <c r="C81">
         <f t="shared" ca="1" si="1"/>
@@ -1495,7 +1491,7 @@
         <v>18</v>
       </c>
       <c r="B82">
-        <v>20190498</v>
+        <v>20180498</v>
       </c>
       <c r="C82">
         <f t="shared" ca="1" si="1"/>
@@ -1507,7 +1503,7 @@
         <v>19</v>
       </c>
       <c r="B83">
-        <v>20190505</v>
+        <v>20180505</v>
       </c>
       <c r="C83">
         <f t="shared" ca="1" si="1"/>
@@ -1519,7 +1515,7 @@
         <v>20</v>
       </c>
       <c r="B84">
-        <v>20190512</v>
+        <v>20180512</v>
       </c>
       <c r="C84">
         <f t="shared" ca="1" si="1"/>
@@ -1531,7 +1527,7 @@
         <v>21</v>
       </c>
       <c r="B85">
-        <v>20190519</v>
+        <v>20180519</v>
       </c>
       <c r="C85">
         <f t="shared" ca="1" si="1"/>
@@ -1543,7 +1539,7 @@
         <v>22</v>
       </c>
       <c r="B86">
-        <v>20190526</v>
+        <v>20180526</v>
       </c>
       <c r="C86">
         <f t="shared" ca="1" si="1"/>
@@ -1555,7 +1551,7 @@
         <v>23</v>
       </c>
       <c r="B87">
-        <v>20190602</v>
+        <v>20180602</v>
       </c>
       <c r="C87">
         <f t="shared" ca="1" si="1"/>
@@ -1567,7 +1563,7 @@
         <v>24</v>
       </c>
       <c r="B88">
-        <v>20190609</v>
+        <v>20180609</v>
       </c>
       <c r="C88">
         <f t="shared" ca="1" si="1"/>
@@ -1579,7 +1575,7 @@
         <v>25</v>
       </c>
       <c r="B89">
-        <v>20190616</v>
+        <v>20180616</v>
       </c>
       <c r="C89">
         <f t="shared" ca="1" si="1"/>
@@ -1591,7 +1587,7 @@
         <v>26</v>
       </c>
       <c r="B90">
-        <v>20190623</v>
+        <v>20180623</v>
       </c>
       <c r="C90">
         <f t="shared" ca="1" si="1"/>
@@ -1603,7 +1599,7 @@
         <v>27</v>
       </c>
       <c r="B91">
-        <v>20190700</v>
+        <v>20180700</v>
       </c>
       <c r="C91">
         <f t="shared" ca="1" si="1"/>
@@ -1615,7 +1611,7 @@
         <v>28</v>
       </c>
       <c r="B92">
-        <v>20190707</v>
+        <v>20180707</v>
       </c>
       <c r="C92">
         <f t="shared" ca="1" si="1"/>
@@ -1627,7 +1623,7 @@
         <v>29</v>
       </c>
       <c r="B93">
-        <v>20190714</v>
+        <v>20180714</v>
       </c>
       <c r="C93">
         <f t="shared" ca="1" si="1"/>
@@ -1639,7 +1635,7 @@
         <v>30</v>
       </c>
       <c r="B94">
-        <v>20190721</v>
+        <v>20180721</v>
       </c>
       <c r="C94">
         <f t="shared" ca="1" si="1"/>
@@ -1651,7 +1647,7 @@
         <v>31</v>
       </c>
       <c r="B95">
-        <v>20190728</v>
+        <v>20180728</v>
       </c>
       <c r="C95">
         <f t="shared" ca="1" si="1"/>
@@ -1663,7 +1659,7 @@
         <v>31</v>
       </c>
       <c r="B96">
-        <v>20190797</v>
+        <v>20180797</v>
       </c>
       <c r="C96">
         <f t="shared" ca="1" si="1"/>
@@ -1675,7 +1671,7 @@
         <v>32</v>
       </c>
       <c r="B97">
-        <v>20190804</v>
+        <v>20180804</v>
       </c>
       <c r="C97">
         <f t="shared" ca="1" si="1"/>
@@ -1687,7 +1683,7 @@
         <v>33</v>
       </c>
       <c r="B98">
-        <v>20190811</v>
+        <v>20180811</v>
       </c>
       <c r="C98">
         <f t="shared" ca="1" si="1"/>
@@ -1699,7 +1695,7 @@
         <v>34</v>
       </c>
       <c r="B99">
-        <v>20190818</v>
+        <v>20180818</v>
       </c>
       <c r="C99">
         <f t="shared" ca="1" si="1"/>
@@ -1711,7 +1707,7 @@
         <v>35</v>
       </c>
       <c r="B100">
-        <v>20190825</v>
+        <v>20180825</v>
       </c>
       <c r="C100">
         <f t="shared" ca="1" si="1"/>
@@ -1723,7 +1719,7 @@
         <v>36</v>
       </c>
       <c r="B101">
-        <v>20190901</v>
+        <v>20180901</v>
       </c>
       <c r="C101">
         <f t="shared" ca="1" si="1"/>
@@ -1735,7 +1731,7 @@
         <v>37</v>
       </c>
       <c r="B102">
-        <v>20190908</v>
+        <v>20180908</v>
       </c>
       <c r="C102">
         <f t="shared" ca="1" si="1"/>
@@ -1747,7 +1743,7 @@
         <v>38</v>
       </c>
       <c r="B103">
-        <v>20190915</v>
+        <v>20180915</v>
       </c>
       <c r="C103">
         <f t="shared" ca="1" si="1"/>
@@ -1759,7 +1755,7 @@
         <v>39</v>
       </c>
       <c r="B104">
-        <v>20190922</v>
+        <v>20180922</v>
       </c>
       <c r="C104">
         <f t="shared" ca="1" si="1"/>
@@ -1771,7 +1767,7 @@
         <v>40</v>
       </c>
       <c r="B105">
-        <v>20190929</v>
+        <v>20180929</v>
       </c>
       <c r="C105">
         <f t="shared" ca="1" si="1"/>
@@ -1783,7 +1779,7 @@
         <v>40</v>
       </c>
       <c r="B106">
-        <v>20190999</v>
+        <v>20180999</v>
       </c>
       <c r="C106">
         <f t="shared" ca="1" si="1"/>
@@ -1795,7 +1791,7 @@
         <v>41</v>
       </c>
       <c r="B107">
-        <v>20191006</v>
+        <v>20181006</v>
       </c>
       <c r="C107">
         <f t="shared" ca="1" si="1"/>
@@ -1807,7 +1803,7 @@
         <v>42</v>
       </c>
       <c r="B108">
-        <v>20191013</v>
+        <v>20181013</v>
       </c>
       <c r="C108">
         <f t="shared" ca="1" si="1"/>
@@ -1819,7 +1815,7 @@
         <v>43</v>
       </c>
       <c r="B109">
-        <v>20191020</v>
+        <v>20181020</v>
       </c>
       <c r="C109">
         <f t="shared" ca="1" si="1"/>
@@ -1831,7 +1827,7 @@
         <v>44</v>
       </c>
       <c r="B110">
-        <v>20191027</v>
+        <v>20181027</v>
       </c>
       <c r="C110">
         <f t="shared" ca="1" si="1"/>
@@ -1843,7 +1839,7 @@
         <v>44</v>
       </c>
       <c r="B111">
-        <v>20191096</v>
+        <v>20181096</v>
       </c>
       <c r="C111">
         <f t="shared" ca="1" si="1"/>
@@ -1855,7 +1851,7 @@
         <v>45</v>
       </c>
       <c r="B112">
-        <v>20191103</v>
+        <v>20181103</v>
       </c>
       <c r="C112">
         <f t="shared" ca="1" si="1"/>
@@ -1867,7 +1863,7 @@
         <v>46</v>
       </c>
       <c r="B113">
-        <v>20191110</v>
+        <v>20181110</v>
       </c>
       <c r="C113">
         <f t="shared" ca="1" si="1"/>
@@ -1879,7 +1875,7 @@
         <v>47</v>
       </c>
       <c r="B114">
-        <v>20191117</v>
+        <v>20181117</v>
       </c>
       <c r="C114">
         <f t="shared" ca="1" si="1"/>
@@ -1891,7 +1887,7 @@
         <v>48</v>
       </c>
       <c r="B115">
-        <v>20191124</v>
+        <v>20181124</v>
       </c>
       <c r="C115">
         <f t="shared" ca="1" si="1"/>
@@ -1903,7 +1899,7 @@
         <v>49</v>
       </c>
       <c r="B116">
-        <v>20191201</v>
+        <v>20181201</v>
       </c>
       <c r="C116">
         <f t="shared" ca="1" si="1"/>
@@ -1915,7 +1911,7 @@
         <v>50</v>
       </c>
       <c r="B117">
-        <v>20191208</v>
+        <v>20181208</v>
       </c>
       <c r="C117">
         <f t="shared" ca="1" si="1"/>
@@ -1927,7 +1923,7 @@
         <v>51</v>
       </c>
       <c r="B118">
-        <v>20191215</v>
+        <v>20181215</v>
       </c>
       <c r="C118">
         <f t="shared" ca="1" si="1"/>
@@ -1939,7 +1935,7 @@
         <v>52</v>
       </c>
       <c r="B119">
-        <v>20191222</v>
+        <v>20181222</v>
       </c>
       <c r="C119">
         <f t="shared" ca="1" si="1"/>
@@ -1951,7 +1947,7 @@
         <v>53</v>
       </c>
       <c r="B120">
-        <v>20191229</v>
+        <v>20181229</v>
       </c>
       <c r="C120">
         <f t="shared" ca="1" si="1"/>
@@ -1963,7 +1959,7 @@
         <v>1</v>
       </c>
       <c r="B121">
-        <v>20200101</v>
+        <v>20190101</v>
       </c>
       <c r="C121">
         <f t="shared" ca="1" si="1"/>
@@ -1975,7 +1971,7 @@
         <v>2</v>
       </c>
       <c r="B122">
-        <v>20200105</v>
+        <v>20190105</v>
       </c>
       <c r="C122">
         <f t="shared" ca="1" si="1"/>
@@ -1987,7 +1983,7 @@
         <v>3</v>
       </c>
       <c r="B123">
-        <v>20200112</v>
+        <v>20190112</v>
       </c>
       <c r="C123">
         <f t="shared" ca="1" si="1"/>
@@ -1999,7 +1995,7 @@
         <v>4</v>
       </c>
       <c r="B124">
-        <v>20200119</v>
+        <v>20190119</v>
       </c>
       <c r="C124">
         <f t="shared" ca="1" si="1"/>
@@ -2011,7 +2007,7 @@
         <v>5</v>
       </c>
       <c r="B125">
-        <v>20200126</v>
+        <v>20190126</v>
       </c>
       <c r="C125">
         <f t="shared" ca="1" si="1"/>
@@ -2023,7 +2019,7 @@
         <v>6</v>
       </c>
       <c r="B126">
-        <v>20200202</v>
+        <v>20190202</v>
       </c>
       <c r="C126">
         <f t="shared" ca="1" si="1"/>
@@ -2035,7 +2031,7 @@
         <v>7</v>
       </c>
       <c r="B127">
-        <v>20200209</v>
+        <v>20190209</v>
       </c>
       <c r="C127">
         <f t="shared" ca="1" si="1"/>
@@ -2047,7 +2043,7 @@
         <v>8</v>
       </c>
       <c r="B128">
-        <v>20200216</v>
+        <v>20190216</v>
       </c>
       <c r="C128">
         <f t="shared" ca="1" si="1"/>
@@ -2059,7 +2055,7 @@
         <v>9</v>
       </c>
       <c r="B129">
-        <v>20200223</v>
+        <v>20190223</v>
       </c>
       <c r="C129">
         <f t="shared" ca="1" si="1"/>
@@ -2071,7 +2067,7 @@
         <v>10</v>
       </c>
       <c r="B130">
-        <v>20200301</v>
+        <v>20190301</v>
       </c>
       <c r="C130">
         <f t="shared" ca="1" si="1"/>
@@ -2083,10 +2079,10 @@
         <v>11</v>
       </c>
       <c r="B131">
-        <v>20200308</v>
+        <v>20190308</v>
       </c>
       <c r="C131">
-        <f t="shared" ref="C131:D194" ca="1" si="2">(B131/$C$2)*100</f>
+        <f t="shared" ref="C131:C194" ca="1" si="2">(B131/$C$2)*100</f>
         <v>195.27507073247406</v>
       </c>
     </row>
@@ -2095,7 +2091,7 @@
         <v>12</v>
       </c>
       <c r="B132">
-        <v>20200315</v>
+        <v>20190315</v>
       </c>
       <c r="C132">
         <f t="shared" ca="1" si="2"/>
@@ -2107,7 +2103,7 @@
         <v>13</v>
       </c>
       <c r="B133">
-        <v>20200322</v>
+        <v>20190322</v>
       </c>
       <c r="C133">
         <f t="shared" ca="1" si="2"/>
@@ -2119,7 +2115,7 @@
         <v>14</v>
       </c>
       <c r="B134">
-        <v>20200329</v>
+        <v>20190329</v>
       </c>
       <c r="C134">
         <f t="shared" ca="1" si="2"/>
@@ -2131,7 +2127,7 @@
         <v>14</v>
       </c>
       <c r="B135">
-        <v>20200398</v>
+        <v>20190398</v>
       </c>
       <c r="C135">
         <f t="shared" ca="1" si="2"/>
@@ -2143,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="B136">
-        <v>20200405</v>
+        <v>20190405</v>
       </c>
       <c r="C136">
         <f t="shared" ca="1" si="2"/>
@@ -2155,7 +2151,7 @@
         <v>16</v>
       </c>
       <c r="B137">
-        <v>20200412</v>
+        <v>20190412</v>
       </c>
       <c r="C137">
         <f t="shared" ca="1" si="2"/>
@@ -2167,7 +2163,7 @@
         <v>17</v>
       </c>
       <c r="B138">
-        <v>20200419</v>
+        <v>20190419</v>
       </c>
       <c r="C138">
         <f t="shared" ca="1" si="2"/>
@@ -2179,7 +2175,7 @@
         <v>18</v>
       </c>
       <c r="B139">
-        <v>20200426</v>
+        <v>20190426</v>
       </c>
       <c r="C139">
         <f t="shared" ca="1" si="2"/>
@@ -2191,7 +2187,7 @@
         <v>19</v>
       </c>
       <c r="B140">
-        <v>20200503</v>
+        <v>20190503</v>
       </c>
       <c r="C140">
         <f t="shared" ca="1" si="2"/>
@@ -2203,7 +2199,7 @@
         <v>20</v>
       </c>
       <c r="B141">
-        <v>20200510</v>
+        <v>20190510</v>
       </c>
       <c r="C141">
         <f t="shared" ca="1" si="2"/>
@@ -2215,7 +2211,7 @@
         <v>21</v>
       </c>
       <c r="B142">
-        <v>20200517</v>
+        <v>20190517</v>
       </c>
       <c r="C142">
         <f t="shared" ca="1" si="2"/>
@@ -2227,7 +2223,7 @@
         <v>22</v>
       </c>
       <c r="B143">
-        <v>20200524</v>
+        <v>20190524</v>
       </c>
       <c r="C143">
         <f t="shared" ca="1" si="2"/>
@@ -2239,7 +2235,7 @@
         <v>23</v>
       </c>
       <c r="B144">
-        <v>20200600</v>
+        <v>20190600</v>
       </c>
       <c r="C144">
         <f t="shared" ca="1" si="2"/>
@@ -2251,7 +2247,7 @@
         <v>24</v>
       </c>
       <c r="B145">
-        <v>20200607</v>
+        <v>20190607</v>
       </c>
       <c r="C145">
         <f t="shared" ca="1" si="2"/>
@@ -2263,7 +2259,7 @@
         <v>25</v>
       </c>
       <c r="B146">
-        <v>20200614</v>
+        <v>20190614</v>
       </c>
       <c r="C146">
         <f t="shared" ca="1" si="2"/>
@@ -2275,7 +2271,7 @@
         <v>26</v>
       </c>
       <c r="B147">
-        <v>20200621</v>
+        <v>20190621</v>
       </c>
       <c r="C147">
         <f t="shared" ca="1" si="2"/>
@@ -2287,7 +2283,7 @@
         <v>27</v>
       </c>
       <c r="B148">
-        <v>20200628</v>
+        <v>20190628</v>
       </c>
       <c r="C148">
         <f t="shared" ca="1" si="2"/>
@@ -2299,7 +2295,7 @@
         <v>27</v>
       </c>
       <c r="B149">
-        <v>20200698</v>
+        <v>20190698</v>
       </c>
       <c r="C149">
         <f t="shared" ca="1" si="2"/>
@@ -2311,7 +2307,7 @@
         <v>28</v>
       </c>
       <c r="B150">
-        <v>20200705</v>
+        <v>20190705</v>
       </c>
       <c r="C150">
         <f t="shared" ca="1" si="2"/>
@@ -2323,7 +2319,7 @@
         <v>29</v>
       </c>
       <c r="B151">
-        <v>20200712</v>
+        <v>20190712</v>
       </c>
       <c r="C151">
         <f t="shared" ca="1" si="2"/>
@@ -2335,7 +2331,7 @@
         <v>30</v>
       </c>
       <c r="B152">
-        <v>20200719</v>
+        <v>20190719</v>
       </c>
       <c r="C152">
         <f t="shared" ca="1" si="2"/>
@@ -2347,7 +2343,7 @@
         <v>31</v>
       </c>
       <c r="B153">
-        <v>20200726</v>
+        <v>20190726</v>
       </c>
       <c r="C153">
         <f t="shared" ca="1" si="2"/>
@@ -2359,7 +2355,7 @@
         <v>32</v>
       </c>
       <c r="B154">
-        <v>20200802</v>
+        <v>20190802</v>
       </c>
       <c r="C154">
         <f t="shared" ca="1" si="2"/>
@@ -2371,7 +2367,7 @@
         <v>33</v>
       </c>
       <c r="B155">
-        <v>20200809</v>
+        <v>20190809</v>
       </c>
       <c r="C155">
         <f t="shared" ca="1" si="2"/>
@@ -2383,7 +2379,7 @@
         <v>34</v>
       </c>
       <c r="B156">
-        <v>20200816</v>
+        <v>20190816</v>
       </c>
       <c r="C156">
         <f t="shared" ca="1" si="2"/>
@@ -2395,7 +2391,7 @@
         <v>35</v>
       </c>
       <c r="B157">
-        <v>20200823</v>
+        <v>20190823</v>
       </c>
       <c r="C157">
         <f t="shared" ca="1" si="2"/>
@@ -2407,7 +2403,7 @@
         <v>36</v>
       </c>
       <c r="B158">
-        <v>20200830</v>
+        <v>20190830</v>
       </c>
       <c r="C158">
         <f t="shared" ca="1" si="2"/>
@@ -2419,7 +2415,7 @@
         <v>36</v>
       </c>
       <c r="B159">
-        <v>20200899</v>
+        <v>20190899</v>
       </c>
       <c r="C159">
         <f t="shared" ca="1" si="2"/>
@@ -2431,7 +2427,7 @@
         <v>37</v>
       </c>
       <c r="B160">
-        <v>20200906</v>
+        <v>20190906</v>
       </c>
       <c r="C160">
         <f t="shared" ca="1" si="2"/>
@@ -2443,7 +2439,7 @@
         <v>38</v>
       </c>
       <c r="B161">
-        <v>20200913</v>
+        <v>20190913</v>
       </c>
       <c r="C161">
         <f t="shared" ca="1" si="2"/>
@@ -2455,7 +2451,7 @@
         <v>39</v>
       </c>
       <c r="B162">
-        <v>20200920</v>
+        <v>20190920</v>
       </c>
       <c r="C162">
         <f t="shared" ca="1" si="2"/>
@@ -2467,7 +2463,7 @@
         <v>40</v>
       </c>
       <c r="B163">
-        <v>20200927</v>
+        <v>20190927</v>
       </c>
       <c r="C163">
         <f t="shared" ca="1" si="2"/>
@@ -2479,7 +2475,7 @@
         <v>40</v>
       </c>
       <c r="B164">
-        <v>20200997</v>
+        <v>20190997</v>
       </c>
       <c r="C164">
         <f t="shared" ca="1" si="2"/>
@@ -2491,7 +2487,7 @@
         <v>41</v>
       </c>
       <c r="B165">
-        <v>20201004</v>
+        <v>20191004</v>
       </c>
       <c r="C165">
         <f t="shared" ca="1" si="2"/>
@@ -2503,7 +2499,7 @@
         <v>42</v>
       </c>
       <c r="B166">
-        <v>20201011</v>
+        <v>20191011</v>
       </c>
       <c r="C166">
         <f t="shared" ca="1" si="2"/>
@@ -2515,7 +2511,7 @@
         <v>43</v>
       </c>
       <c r="B167">
-        <v>20201018</v>
+        <v>20191018</v>
       </c>
       <c r="C167">
         <f t="shared" ca="1" si="2"/>
@@ -2527,7 +2523,7 @@
         <v>44</v>
       </c>
       <c r="B168">
-        <v>20201025</v>
+        <v>20191025</v>
       </c>
       <c r="C168">
         <f t="shared" ca="1" si="2"/>
@@ -2539,7 +2535,7 @@
         <v>45</v>
       </c>
       <c r="B169">
-        <v>20201101</v>
+        <v>20191101</v>
       </c>
       <c r="C169">
         <f t="shared" ca="1" si="2"/>
@@ -2551,7 +2547,7 @@
         <v>46</v>
       </c>
       <c r="B170">
-        <v>20201108</v>
+        <v>20191108</v>
       </c>
       <c r="C170">
         <f t="shared" ca="1" si="2"/>
@@ -2563,7 +2559,7 @@
         <v>47</v>
       </c>
       <c r="B171">
-        <v>20201115</v>
+        <v>20191115</v>
       </c>
       <c r="C171">
         <f t="shared" ca="1" si="2"/>
@@ -2575,7 +2571,7 @@
         <v>48</v>
       </c>
       <c r="B172">
-        <v>20201122</v>
+        <v>20191122</v>
       </c>
       <c r="C172">
         <f t="shared" ca="1" si="2"/>
@@ -2587,7 +2583,7 @@
         <v>49</v>
       </c>
       <c r="B173">
-        <v>20201129</v>
+        <v>20191129</v>
       </c>
       <c r="C173">
         <f t="shared" ca="1" si="2"/>
@@ -2599,7 +2595,7 @@
         <v>49</v>
       </c>
       <c r="B174">
-        <v>20201199</v>
+        <v>20191199</v>
       </c>
       <c r="C174">
         <f t="shared" ca="1" si="2"/>
@@ -2611,7 +2607,7 @@
         <v>50</v>
       </c>
       <c r="B175">
-        <v>20201206</v>
+        <v>20191206</v>
       </c>
       <c r="C175">
         <f t="shared" ca="1" si="2"/>
@@ -2623,7 +2619,7 @@
         <v>51</v>
       </c>
       <c r="B176">
-        <v>20201213</v>
+        <v>20191213</v>
       </c>
       <c r="C176">
         <f t="shared" ca="1" si="2"/>
@@ -2635,7 +2631,7 @@
         <v>52</v>
       </c>
       <c r="B177">
-        <v>20201220</v>
+        <v>20191220</v>
       </c>
       <c r="C177">
         <f t="shared" ca="1" si="2"/>
@@ -2647,7 +2643,7 @@
         <v>53</v>
       </c>
       <c r="B178">
-        <v>20201227</v>
+        <v>20191227</v>
       </c>
       <c r="C178">
         <f t="shared" ca="1" si="2"/>
@@ -2659,7 +2655,7 @@
         <v>2</v>
       </c>
       <c r="B179">
-        <v>20210103</v>
+        <v>20200103</v>
       </c>
       <c r="C179">
         <f t="shared" ca="1" si="2"/>
@@ -2671,7 +2667,7 @@
         <v>3</v>
       </c>
       <c r="B180">
-        <v>20210110</v>
+        <v>20200110</v>
       </c>
       <c r="C180">
         <f t="shared" ca="1" si="2"/>
@@ -2683,7 +2679,7 @@
         <v>4</v>
       </c>
       <c r="B181">
-        <v>20210117</v>
+        <v>20200117</v>
       </c>
       <c r="C181">
         <f t="shared" ca="1" si="2"/>
@@ -2695,7 +2691,7 @@
         <v>5</v>
       </c>
       <c r="B182">
-        <v>20210124</v>
+        <v>20200124</v>
       </c>
       <c r="C182">
         <f t="shared" ca="1" si="2"/>
@@ -2707,7 +2703,7 @@
         <v>6</v>
       </c>
       <c r="B183">
-        <v>20210200</v>
+        <v>20200200</v>
       </c>
       <c r="C183">
         <f t="shared" ca="1" si="2"/>
@@ -2719,7 +2715,7 @@
         <v>7</v>
       </c>
       <c r="B184">
-        <v>20210207</v>
+        <v>20200207</v>
       </c>
       <c r="C184">
         <f t="shared" ca="1" si="2"/>
@@ -2731,7 +2727,7 @@
         <v>8</v>
       </c>
       <c r="B185">
-        <v>20210214</v>
+        <v>20200214</v>
       </c>
       <c r="C185">
         <f t="shared" ca="1" si="2"/>
@@ -2743,7 +2739,7 @@
         <v>9</v>
       </c>
       <c r="B186">
-        <v>20210221</v>
+        <v>20200221</v>
       </c>
       <c r="C186">
         <f t="shared" ca="1" si="2"/>
@@ -2755,7 +2751,7 @@
         <v>10</v>
       </c>
       <c r="B187">
-        <v>20210300</v>
+        <v>20200300</v>
       </c>
       <c r="C187">
         <f t="shared" ca="1" si="2"/>
@@ -2767,7 +2763,7 @@
         <v>11</v>
       </c>
       <c r="B188">
-        <v>20210307</v>
+        <v>20200307</v>
       </c>
       <c r="C188">
         <f t="shared" ca="1" si="2"/>
@@ -2779,7 +2775,7 @@
         <v>12</v>
       </c>
       <c r="B189">
-        <v>20210314</v>
+        <v>20200314</v>
       </c>
       <c r="C189">
         <f t="shared" ca="1" si="2"/>
@@ -2791,7 +2787,7 @@
         <v>13</v>
       </c>
       <c r="B190">
-        <v>20210321</v>
+        <v>20200321</v>
       </c>
       <c r="C190">
         <f t="shared" ca="1" si="2"/>
@@ -2803,7 +2799,7 @@
         <v>14</v>
       </c>
       <c r="B191">
-        <v>20210328</v>
+        <v>20200328</v>
       </c>
       <c r="C191">
         <f t="shared" ca="1" si="2"/>
@@ -2815,7 +2811,7 @@
         <v>14</v>
       </c>
       <c r="B192">
-        <v>20210397</v>
+        <v>20200397</v>
       </c>
       <c r="C192">
         <f t="shared" ca="1" si="2"/>
@@ -2827,7 +2823,7 @@
         <v>15</v>
       </c>
       <c r="B193">
-        <v>20210404</v>
+        <v>20200404</v>
       </c>
       <c r="C193">
         <f t="shared" ca="1" si="2"/>
@@ -2839,7 +2835,7 @@
         <v>16</v>
       </c>
       <c r="B194">
-        <v>20210411</v>
+        <v>20200411</v>
       </c>
       <c r="C194">
         <f t="shared" ca="1" si="2"/>
@@ -2851,10 +2847,10 @@
         <v>17</v>
       </c>
       <c r="B195">
-        <v>20210418</v>
+        <v>20200418</v>
       </c>
       <c r="C195">
-        <f t="shared" ref="C195:D258" ca="1" si="3">(B195/$C$2)*100</f>
+        <f t="shared" ref="C195:C258" ca="1" si="3">(B195/$C$2)*100</f>
         <v>176.07670543854135</v>
       </c>
     </row>
@@ -2863,7 +2859,7 @@
         <v>18</v>
       </c>
       <c r="B196">
-        <v>20210425</v>
+        <v>20200425</v>
       </c>
       <c r="C196">
         <f t="shared" ca="1" si="3"/>
@@ -2875,7 +2871,7 @@
         <v>18</v>
       </c>
       <c r="B197">
-        <v>20210495</v>
+        <v>20200495</v>
       </c>
       <c r="C197">
         <f t="shared" ca="1" si="3"/>
@@ -2887,7 +2883,7 @@
         <v>19</v>
       </c>
       <c r="B198">
-        <v>20210502</v>
+        <v>20200502</v>
       </c>
       <c r="C198">
         <f t="shared" ca="1" si="3"/>
@@ -2899,7 +2895,7 @@
         <v>20</v>
       </c>
       <c r="B199">
-        <v>20210509</v>
+        <v>20200509</v>
       </c>
       <c r="C199">
         <f t="shared" ca="1" si="3"/>
@@ -2911,7 +2907,7 @@
         <v>21</v>
       </c>
       <c r="B200">
-        <v>20210516</v>
+        <v>20200516</v>
       </c>
       <c r="C200">
         <f t="shared" ca="1" si="3"/>
@@ -2923,7 +2919,7 @@
         <v>22</v>
       </c>
       <c r="B201">
-        <v>20210523</v>
+        <v>20200523</v>
       </c>
       <c r="C201">
         <f t="shared" ca="1" si="3"/>
@@ -2935,7 +2931,7 @@
         <v>23</v>
       </c>
       <c r="B202">
-        <v>20210530</v>
+        <v>20200530</v>
       </c>
       <c r="C202">
         <f t="shared" ca="1" si="3"/>
@@ -2947,7 +2943,7 @@
         <v>23</v>
       </c>
       <c r="B203">
-        <v>20210599</v>
+        <v>20200599</v>
       </c>
       <c r="C203">
         <f t="shared" ca="1" si="3"/>
@@ -2959,7 +2955,7 @@
         <v>24</v>
       </c>
       <c r="B204">
-        <v>20210606</v>
+        <v>20200606</v>
       </c>
       <c r="C204">
         <f t="shared" ca="1" si="3"/>
@@ -2971,7 +2967,7 @@
         <v>25</v>
       </c>
       <c r="B205">
-        <v>20210613</v>
+        <v>20200613</v>
       </c>
       <c r="C205">
         <f t="shared" ca="1" si="3"/>
@@ -2983,7 +2979,7 @@
         <v>26</v>
       </c>
       <c r="B206">
-        <v>20210620</v>
+        <v>20200620</v>
       </c>
       <c r="C206">
         <f t="shared" ca="1" si="3"/>
@@ -2995,7 +2991,7 @@
         <v>27</v>
       </c>
       <c r="B207">
-        <v>20210627</v>
+        <v>20200627</v>
       </c>
       <c r="C207">
         <f t="shared" ca="1" si="3"/>
@@ -3007,7 +3003,7 @@
         <v>27</v>
       </c>
       <c r="B208">
-        <v>20210697</v>
+        <v>20200697</v>
       </c>
       <c r="C208">
         <f t="shared" ca="1" si="3"/>
@@ -3019,7 +3015,7 @@
         <v>28</v>
       </c>
       <c r="B209">
-        <v>20210704</v>
+        <v>20200704</v>
       </c>
       <c r="C209">
         <f t="shared" ca="1" si="3"/>
@@ -3031,7 +3027,7 @@
         <v>29</v>
       </c>
       <c r="B210">
-        <v>20210711</v>
+        <v>20200711</v>
       </c>
       <c r="C210">
         <f t="shared" ca="1" si="3"/>
@@ -3043,7 +3039,7 @@
         <v>30</v>
       </c>
       <c r="B211">
-        <v>20210718</v>
+        <v>20200718</v>
       </c>
       <c r="C211">
         <f t="shared" ca="1" si="3"/>
@@ -3055,7 +3051,7 @@
         <v>31</v>
       </c>
       <c r="B212">
-        <v>20210725</v>
+        <v>20200725</v>
       </c>
       <c r="C212">
         <f t="shared" ca="1" si="3"/>
@@ -3067,7 +3063,7 @@
         <v>32</v>
       </c>
       <c r="B213">
-        <v>20210801</v>
+        <v>20200801</v>
       </c>
       <c r="C213">
         <f t="shared" ca="1" si="3"/>
@@ -3079,7 +3075,7 @@
         <v>33</v>
       </c>
       <c r="B214">
-        <v>20210808</v>
+        <v>20200808</v>
       </c>
       <c r="C214">
         <f t="shared" ca="1" si="3"/>
@@ -3091,7 +3087,7 @@
         <v>34</v>
       </c>
       <c r="B215">
-        <v>20210815</v>
+        <v>20200815</v>
       </c>
       <c r="C215">
         <f t="shared" ca="1" si="3"/>
@@ -3103,7 +3099,7 @@
         <v>35</v>
       </c>
       <c r="B216">
-        <v>20210822</v>
+        <v>20200822</v>
       </c>
       <c r="C216">
         <f t="shared" ca="1" si="3"/>
@@ -3115,7 +3111,7 @@
         <v>36</v>
       </c>
       <c r="B217">
-        <v>20210829</v>
+        <v>20200829</v>
       </c>
       <c r="C217">
         <f t="shared" ca="1" si="3"/>
@@ -3127,7 +3123,7 @@
         <v>36</v>
       </c>
       <c r="B218">
-        <v>20210898</v>
+        <v>20200898</v>
       </c>
       <c r="C218">
         <f t="shared" ca="1" si="3"/>
@@ -3139,7 +3135,7 @@
         <v>37</v>
       </c>
       <c r="B219">
-        <v>20210905</v>
+        <v>20200905</v>
       </c>
       <c r="C219">
         <f t="shared" ca="1" si="3"/>
@@ -3151,7 +3147,7 @@
         <v>38</v>
       </c>
       <c r="B220">
-        <v>20210912</v>
+        <v>20200912</v>
       </c>
       <c r="C220">
         <f t="shared" ca="1" si="3"/>
@@ -3163,7 +3159,7 @@
         <v>39</v>
       </c>
       <c r="B221">
-        <v>20210919</v>
+        <v>20200919</v>
       </c>
       <c r="C221">
         <f t="shared" ca="1" si="3"/>
@@ -3175,7 +3171,7 @@
         <v>40</v>
       </c>
       <c r="B222">
-        <v>20210926</v>
+        <v>20200926</v>
       </c>
       <c r="C222">
         <f t="shared" ca="1" si="3"/>
@@ -3187,7 +3183,7 @@
         <v>40</v>
       </c>
       <c r="B223">
-        <v>20210996</v>
+        <v>20200996</v>
       </c>
       <c r="C223">
         <f t="shared" ca="1" si="3"/>
@@ -3199,7 +3195,7 @@
         <v>41</v>
       </c>
       <c r="B224">
-        <v>20211003</v>
+        <v>20201003</v>
       </c>
       <c r="C224">
         <f t="shared" ca="1" si="3"/>
@@ -3211,7 +3207,7 @@
         <v>42</v>
       </c>
       <c r="B225">
-        <v>20211010</v>
+        <v>20201010</v>
       </c>
       <c r="C225">
         <f t="shared" ca="1" si="3"/>
@@ -3223,7 +3219,7 @@
         <v>43</v>
       </c>
       <c r="B226">
-        <v>20211017</v>
+        <v>20201017</v>
       </c>
       <c r="C226">
         <f t="shared" ca="1" si="3"/>
@@ -3235,7 +3231,7 @@
         <v>44</v>
       </c>
       <c r="B227">
-        <v>20211024</v>
+        <v>20201024</v>
       </c>
       <c r="C227">
         <f t="shared" ca="1" si="3"/>
@@ -3247,7 +3243,7 @@
         <v>45</v>
       </c>
       <c r="B228">
-        <v>20211100</v>
+        <v>20201100</v>
       </c>
       <c r="C228">
         <f t="shared" ca="1" si="3"/>
@@ -3259,7 +3255,7 @@
         <v>46</v>
       </c>
       <c r="B229">
-        <v>20211107</v>
+        <v>20201107</v>
       </c>
       <c r="C229">
         <f t="shared" ca="1" si="3"/>
@@ -3271,7 +3267,7 @@
         <v>47</v>
       </c>
       <c r="B230">
-        <v>20211114</v>
+        <v>20201114</v>
       </c>
       <c r="C230">
         <f t="shared" ca="1" si="3"/>
@@ -3283,7 +3279,7 @@
         <v>48</v>
       </c>
       <c r="B231">
-        <v>20211121</v>
+        <v>20201121</v>
       </c>
       <c r="C231">
         <f t="shared" ca="1" si="3"/>
@@ -3295,7 +3291,7 @@
         <v>49</v>
       </c>
       <c r="B232">
-        <v>20211128</v>
+        <v>20201128</v>
       </c>
       <c r="C232">
         <f t="shared" ca="1" si="3"/>
@@ -3307,7 +3303,7 @@
         <v>49</v>
       </c>
       <c r="B233">
-        <v>20211198</v>
+        <v>20201198</v>
       </c>
       <c r="C233">
         <f t="shared" ca="1" si="3"/>
@@ -3319,7 +3315,7 @@
         <v>50</v>
       </c>
       <c r="B234">
-        <v>20211205</v>
+        <v>20201205</v>
       </c>
       <c r="C234">
         <f t="shared" ca="1" si="3"/>
@@ -3331,7 +3327,7 @@
         <v>51</v>
       </c>
       <c r="B235">
-        <v>20211212</v>
+        <v>20201212</v>
       </c>
       <c r="C235">
         <f t="shared" ca="1" si="3"/>
@@ -3343,7 +3339,7 @@
         <v>52</v>
       </c>
       <c r="B236">
-        <v>20211219</v>
+        <v>20201219</v>
       </c>
       <c r="C236">
         <f t="shared" ca="1" si="3"/>
@@ -3355,7 +3351,7 @@
         <v>53</v>
       </c>
       <c r="B237">
-        <v>20211226</v>
+        <v>20201226</v>
       </c>
       <c r="C237">
         <f t="shared" ca="1" si="3"/>
@@ -3367,7 +3363,7 @@
         <v>2</v>
       </c>
       <c r="B238">
-        <v>20220102</v>
+        <v>20210102</v>
       </c>
       <c r="C238">
         <f t="shared" ca="1" si="3"/>
@@ -3379,7 +3375,7 @@
         <v>3</v>
       </c>
       <c r="B239">
-        <v>20220109</v>
+        <v>20210109</v>
       </c>
       <c r="C239">
         <f t="shared" ca="1" si="3"/>
@@ -3391,7 +3387,7 @@
         <v>4</v>
       </c>
       <c r="B240">
-        <v>20220116</v>
+        <v>20210116</v>
       </c>
       <c r="C240">
         <f t="shared" ca="1" si="3"/>
@@ -3403,7 +3399,7 @@
         <v>5</v>
       </c>
       <c r="B241">
-        <v>20220123</v>
+        <v>20210123</v>
       </c>
       <c r="C241">
         <f t="shared" ca="1" si="3"/>
@@ -3415,7 +3411,7 @@
         <v>6</v>
       </c>
       <c r="B242">
-        <v>20220130</v>
+        <v>20210130</v>
       </c>
       <c r="C242">
         <f t="shared" ca="1" si="3"/>
@@ -3427,7 +3423,7 @@
         <v>6</v>
       </c>
       <c r="B243">
-        <v>20220199</v>
+        <v>20210199</v>
       </c>
       <c r="C243">
         <f t="shared" ca="1" si="3"/>
@@ -3439,7 +3435,7 @@
         <v>7</v>
       </c>
       <c r="B244">
-        <v>20220206</v>
+        <v>20210206</v>
       </c>
       <c r="C244">
         <f t="shared" ca="1" si="3"/>
@@ -3451,7 +3447,7 @@
         <v>8</v>
       </c>
       <c r="B245">
-        <v>20220213</v>
+        <v>20210213</v>
       </c>
       <c r="C245">
         <f t="shared" ca="1" si="3"/>
@@ -3463,7 +3459,7 @@
         <v>9</v>
       </c>
       <c r="B246">
-        <v>20220220</v>
+        <v>20210220</v>
       </c>
       <c r="C246">
         <f t="shared" ca="1" si="3"/>
@@ -3475,7 +3471,7 @@
         <v>10</v>
       </c>
       <c r="B247">
-        <v>20220227</v>
+        <v>20210227</v>
       </c>
       <c r="C247">
         <f t="shared" ca="1" si="3"/>
@@ -3487,7 +3483,7 @@
         <v>10</v>
       </c>
       <c r="B248">
-        <v>20220299</v>
+        <v>20210299</v>
       </c>
       <c r="C248">
         <f t="shared" ca="1" si="3"/>
@@ -3499,7 +3495,7 @@
         <v>11</v>
       </c>
       <c r="B249">
-        <v>20220306</v>
+        <v>20210306</v>
       </c>
       <c r="C249">
         <f t="shared" ca="1" si="3"/>
@@ -3511,7 +3507,7 @@
         <v>12</v>
       </c>
       <c r="B250">
-        <v>20220313</v>
+        <v>20210313</v>
       </c>
       <c r="C250">
         <f t="shared" ca="1" si="3"/>
@@ -3523,7 +3519,7 @@
         <v>13</v>
       </c>
       <c r="B251">
-        <v>20220320</v>
+        <v>20210320</v>
       </c>
       <c r="C251">
         <f t="shared" ca="1" si="3"/>
@@ -3535,7 +3531,7 @@
         <v>14</v>
       </c>
       <c r="B252">
-        <v>20220327</v>
+        <v>20210327</v>
       </c>
       <c r="C252">
         <f t="shared" ca="1" si="3"/>
@@ -3547,7 +3543,7 @@
         <v>14</v>
       </c>
       <c r="B253">
-        <v>20220396</v>
+        <v>20210396</v>
       </c>
       <c r="C253">
         <f t="shared" ca="1" si="3"/>
@@ -3559,7 +3555,7 @@
         <v>15</v>
       </c>
       <c r="B254">
-        <v>20220403</v>
+        <v>20210403</v>
       </c>
       <c r="C254">
         <f t="shared" ca="1" si="3"/>
@@ -3571,7 +3567,7 @@
         <v>16</v>
       </c>
       <c r="B255">
-        <v>20220410</v>
+        <v>20210410</v>
       </c>
       <c r="C255">
         <f t="shared" ca="1" si="3"/>
@@ -3583,7 +3579,7 @@
         <v>17</v>
       </c>
       <c r="B256">
-        <v>20220417</v>
+        <v>20210417</v>
       </c>
       <c r="C256">
         <f t="shared" ca="1" si="3"/>
@@ -3595,7 +3591,7 @@
         <v>18</v>
       </c>
       <c r="B257">
-        <v>20220424</v>
+        <v>20210424</v>
       </c>
       <c r="C257">
         <f t="shared" ca="1" si="3"/>
@@ -3607,7 +3603,7 @@
         <v>19</v>
       </c>
       <c r="B258">
-        <v>20220501</v>
+        <v>20210501</v>
       </c>
       <c r="C258">
         <f t="shared" ca="1" si="3"/>
@@ -3619,10 +3615,10 @@
         <v>20</v>
       </c>
       <c r="B259">
-        <v>20220508</v>
+        <v>20210508</v>
       </c>
       <c r="C259">
-        <f t="shared" ref="C259:D322" ca="1" si="4">(B259/$C$2)*100</f>
+        <f t="shared" ref="C259:C322" ca="1" si="4">(B259/$C$2)*100</f>
         <v>243.23797547940899</v>
       </c>
     </row>
@@ -3631,7 +3627,7 @@
         <v>21</v>
       </c>
       <c r="B260">
-        <v>20220515</v>
+        <v>20210515</v>
       </c>
       <c r="C260">
         <f t="shared" ca="1" si="4"/>
@@ -3643,7 +3639,7 @@
         <v>22</v>
       </c>
       <c r="B261">
-        <v>20220522</v>
+        <v>20210522</v>
       </c>
       <c r="C261">
         <f t="shared" ca="1" si="4"/>
@@ -3655,7 +3651,7 @@
         <v>23</v>
       </c>
       <c r="B262">
-        <v>20220529</v>
+        <v>20210529</v>
       </c>
       <c r="C262">
         <f t="shared" ca="1" si="4"/>
@@ -3667,7 +3663,7 @@
         <v>23</v>
       </c>
       <c r="B263">
-        <v>20220598</v>
+        <v>20210598</v>
       </c>
       <c r="C263">
         <f t="shared" ca="1" si="4"/>
@@ -3679,7 +3675,7 @@
         <v>24</v>
       </c>
       <c r="B264">
-        <v>20220605</v>
+        <v>20210605</v>
       </c>
       <c r="C264">
         <f t="shared" ca="1" si="4"/>
@@ -3691,7 +3687,7 @@
         <v>25</v>
       </c>
       <c r="B265">
-        <v>20220612</v>
+        <v>20210612</v>
       </c>
       <c r="C265">
         <f t="shared" ca="1" si="4"/>
@@ -3703,7 +3699,7 @@
         <v>26</v>
       </c>
       <c r="B266">
-        <v>20220619</v>
+        <v>20210619</v>
       </c>
       <c r="C266">
         <f t="shared" ca="1" si="4"/>
@@ -3715,7 +3711,7 @@
         <v>27</v>
       </c>
       <c r="B267">
-        <v>20220626</v>
+        <v>20210626</v>
       </c>
       <c r="C267">
         <f t="shared" ca="1" si="4"/>
@@ -3727,7 +3723,7 @@
         <v>27</v>
       </c>
       <c r="B268">
-        <v>20220696</v>
+        <v>20210696</v>
       </c>
       <c r="C268">
         <f t="shared" ca="1" si="4"/>
@@ -3739,7 +3735,7 @@
         <v>28</v>
       </c>
       <c r="B269">
-        <v>20220703</v>
+        <v>20210703</v>
       </c>
       <c r="C269">
         <f t="shared" ca="1" si="4"/>
@@ -3751,7 +3747,7 @@
         <v>29</v>
       </c>
       <c r="B270">
-        <v>20220710</v>
+        <v>20210710</v>
       </c>
       <c r="C270">
         <f t="shared" ca="1" si="4"/>
@@ -3763,7 +3759,7 @@
         <v>30</v>
       </c>
       <c r="B271">
-        <v>20220717</v>
+        <v>20210717</v>
       </c>
       <c r="C271">
         <f t="shared" ca="1" si="4"/>
@@ -3775,7 +3771,7 @@
         <v>31</v>
       </c>
       <c r="B272">
-        <v>20220724</v>
+        <v>20210724</v>
       </c>
       <c r="C272">
         <f t="shared" ca="1" si="4"/>
@@ -3787,7 +3783,7 @@
         <v>32</v>
       </c>
       <c r="B273">
-        <v>20220800</v>
+        <v>20210800</v>
       </c>
       <c r="C273">
         <f t="shared" ca="1" si="4"/>
@@ -3799,7 +3795,7 @@
         <v>33</v>
       </c>
       <c r="B274">
-        <v>20220807</v>
+        <v>20210807</v>
       </c>
       <c r="C274">
         <f t="shared" ca="1" si="4"/>
@@ -3811,7 +3807,7 @@
         <v>34</v>
       </c>
       <c r="B275">
-        <v>20220814</v>
+        <v>20210814</v>
       </c>
       <c r="C275">
         <f t="shared" ca="1" si="4"/>
@@ -3823,7 +3819,7 @@
         <v>35</v>
       </c>
       <c r="B276">
-        <v>20220821</v>
+        <v>20210821</v>
       </c>
       <c r="C276">
         <f t="shared" ca="1" si="4"/>
@@ -3835,7 +3831,7 @@
         <v>36</v>
       </c>
       <c r="B277">
-        <v>20220828</v>
+        <v>20210828</v>
       </c>
       <c r="C277">
         <f t="shared" ca="1" si="4"/>
@@ -3847,7 +3843,7 @@
         <v>36</v>
       </c>
       <c r="B278">
-        <v>20220897</v>
+        <v>20210897</v>
       </c>
       <c r="C278">
         <f t="shared" ca="1" si="4"/>
@@ -3859,7 +3855,7 @@
         <v>37</v>
       </c>
       <c r="B279">
-        <v>20220904</v>
+        <v>20210904</v>
       </c>
       <c r="C279">
         <f t="shared" ca="1" si="4"/>
@@ -3871,7 +3867,7 @@
         <v>38</v>
       </c>
       <c r="B280">
-        <v>20220911</v>
+        <v>20210911</v>
       </c>
       <c r="C280">
         <f t="shared" ca="1" si="4"/>
@@ -3883,7 +3879,7 @@
         <v>39</v>
       </c>
       <c r="B281">
-        <v>20220918</v>
+        <v>20210918</v>
       </c>
       <c r="C281">
         <f t="shared" ca="1" si="4"/>
@@ -3895,7 +3891,7 @@
         <v>40</v>
       </c>
       <c r="B282">
-        <v>20220925</v>
+        <v>20210925</v>
       </c>
       <c r="C282">
         <f t="shared" ca="1" si="4"/>
@@ -3907,7 +3903,7 @@
         <v>41</v>
       </c>
       <c r="B283">
-        <v>20221002</v>
+        <v>20211002</v>
       </c>
       <c r="C283">
         <f t="shared" ca="1" si="4"/>
@@ -3919,7 +3915,7 @@
         <v>42</v>
       </c>
       <c r="B284">
-        <v>20221009</v>
+        <v>20211009</v>
       </c>
       <c r="C284">
         <f t="shared" ca="1" si="4"/>
@@ -3931,7 +3927,7 @@
         <v>43</v>
       </c>
       <c r="B285">
-        <v>20221016</v>
+        <v>20211016</v>
       </c>
       <c r="C285">
         <f t="shared" ca="1" si="4"/>
@@ -3943,7 +3939,7 @@
         <v>44</v>
       </c>
       <c r="B286">
-        <v>20221023</v>
+        <v>20211023</v>
       </c>
       <c r="C286">
         <f t="shared" ca="1" si="4"/>
@@ -3955,7 +3951,7 @@
         <v>45</v>
       </c>
       <c r="B287">
-        <v>20221030</v>
+        <v>20211030</v>
       </c>
       <c r="C287">
         <f t="shared" ca="1" si="4"/>
@@ -3967,7 +3963,7 @@
         <v>45</v>
       </c>
       <c r="B288">
-        <v>20221099</v>
+        <v>20211099</v>
       </c>
       <c r="C288">
         <f t="shared" ca="1" si="4"/>
@@ -3979,7 +3975,7 @@
         <v>46</v>
       </c>
       <c r="B289">
-        <v>20221106</v>
+        <v>20211106</v>
       </c>
       <c r="C289">
         <f t="shared" ca="1" si="4"/>
@@ -3991,7 +3987,7 @@
         <v>47</v>
       </c>
       <c r="B290">
-        <v>20221113</v>
+        <v>20211113</v>
       </c>
       <c r="C290">
         <f t="shared" ca="1" si="4"/>
@@ -4003,7 +3999,7 @@
         <v>48</v>
       </c>
       <c r="B291">
-        <v>20221120</v>
+        <v>20211120</v>
       </c>
       <c r="C291">
         <f t="shared" ca="1" si="4"/>
@@ -4015,7 +4011,7 @@
         <v>49</v>
       </c>
       <c r="B292">
-        <v>20221127</v>
+        <v>20211127</v>
       </c>
       <c r="C292">
         <f t="shared" ca="1" si="4"/>
@@ -4027,7 +4023,7 @@
         <v>49</v>
       </c>
       <c r="B293">
-        <v>20221197</v>
+        <v>20211197</v>
       </c>
       <c r="C293">
         <f t="shared" ca="1" si="4"/>
@@ -4039,7 +4035,7 @@
         <v>50</v>
       </c>
       <c r="B294">
-        <v>20221204</v>
+        <v>20211204</v>
       </c>
       <c r="C294">
         <f t="shared" ca="1" si="4"/>
@@ -4051,7 +4047,7 @@
         <v>51</v>
       </c>
       <c r="B295">
-        <v>20221211</v>
+        <v>20211211</v>
       </c>
       <c r="C295">
         <f t="shared" ca="1" si="4"/>
@@ -4063,7 +4059,7 @@
         <v>52</v>
       </c>
       <c r="B296">
-        <v>20221218</v>
+        <v>20211218</v>
       </c>
       <c r="C296">
         <f t="shared" ca="1" si="4"/>
@@ -4075,7 +4071,7 @@
         <v>53</v>
       </c>
       <c r="B297">
-        <v>20221225</v>
+        <v>20211225</v>
       </c>
       <c r="C297">
         <f t="shared" ca="1" si="4"/>
@@ -4087,7 +4083,7 @@
         <v>1</v>
       </c>
       <c r="B298">
-        <v>20230101</v>
+        <v>20220101</v>
       </c>
       <c r="C298">
         <f t="shared" ca="1" si="4"/>
@@ -4099,7 +4095,7 @@
         <v>2</v>
       </c>
       <c r="B299">
-        <v>20230108</v>
+        <v>20220108</v>
       </c>
       <c r="C299">
         <f t="shared" ca="1" si="4"/>
@@ -4111,7 +4107,7 @@
         <v>3</v>
       </c>
       <c r="B300">
-        <v>20230115</v>
+        <v>20220115</v>
       </c>
       <c r="C300">
         <f t="shared" ca="1" si="4"/>
@@ -4123,7 +4119,7 @@
         <v>4</v>
       </c>
       <c r="B301">
-        <v>20230122</v>
+        <v>20220122</v>
       </c>
       <c r="C301">
         <f t="shared" ca="1" si="4"/>
@@ -4135,7 +4131,7 @@
         <v>5</v>
       </c>
       <c r="B302">
-        <v>20230129</v>
+        <v>20220129</v>
       </c>
       <c r="C302">
         <f t="shared" ca="1" si="4"/>
@@ -4147,7 +4143,7 @@
         <v>5</v>
       </c>
       <c r="B303">
-        <v>20230198</v>
+        <v>20220198</v>
       </c>
       <c r="C303">
         <f t="shared" ca="1" si="4"/>
@@ -4159,7 +4155,7 @@
         <v>6</v>
       </c>
       <c r="B304">
-        <v>20230205</v>
+        <v>20220205</v>
       </c>
       <c r="C304">
         <f t="shared" ca="1" si="4"/>
@@ -4171,7 +4167,7 @@
         <v>7</v>
       </c>
       <c r="B305">
-        <v>20230212</v>
+        <v>20220212</v>
       </c>
       <c r="C305">
         <f t="shared" ca="1" si="4"/>
@@ -4183,7 +4179,7 @@
         <v>8</v>
       </c>
       <c r="B306">
-        <v>20230219</v>
+        <v>20220219</v>
       </c>
       <c r="C306">
         <f t="shared" ca="1" si="4"/>
@@ -4195,7 +4191,7 @@
         <v>9</v>
       </c>
       <c r="B307">
-        <v>20230226</v>
+        <v>20220226</v>
       </c>
       <c r="C307">
         <f t="shared" ca="1" si="4"/>
@@ -4207,7 +4203,7 @@
         <v>9</v>
       </c>
       <c r="B308">
-        <v>20230298</v>
+        <v>20220298</v>
       </c>
       <c r="C308">
         <f t="shared" ca="1" si="4"/>
@@ -4219,7 +4215,7 @@
         <v>10</v>
       </c>
       <c r="B309">
-        <v>20230305</v>
+        <v>20220305</v>
       </c>
       <c r="C309">
         <f t="shared" ca="1" si="4"/>
@@ -4231,7 +4227,7 @@
         <v>11</v>
       </c>
       <c r="B310">
-        <v>20230312</v>
+        <v>20220312</v>
       </c>
       <c r="C310">
         <f t="shared" ca="1" si="4"/>
@@ -4243,7 +4239,7 @@
         <v>12</v>
       </c>
       <c r="B311">
-        <v>20230319</v>
+        <v>20220319</v>
       </c>
       <c r="C311">
         <f t="shared" ca="1" si="4"/>
@@ -4255,7 +4251,7 @@
         <v>13</v>
       </c>
       <c r="B312">
-        <v>20230326</v>
+        <v>20220326</v>
       </c>
       <c r="C312">
         <f t="shared" ca="1" si="4"/>
@@ -4267,7 +4263,7 @@
         <v>13</v>
       </c>
       <c r="B313">
-        <v>20230395</v>
+        <v>20220395</v>
       </c>
       <c r="C313">
         <f t="shared" ca="1" si="4"/>
@@ -4279,7 +4275,7 @@
         <v>14</v>
       </c>
       <c r="B314">
-        <v>20230402</v>
+        <v>20220402</v>
       </c>
       <c r="C314">
         <f t="shared" ca="1" si="4"/>
@@ -4291,7 +4287,7 @@
         <v>15</v>
       </c>
       <c r="B315">
-        <v>20230409</v>
+        <v>20220409</v>
       </c>
       <c r="C315">
         <f t="shared" ca="1" si="4"/>
@@ -4303,7 +4299,7 @@
         <v>16</v>
       </c>
       <c r="B316">
-        <v>20230416</v>
+        <v>20220416</v>
       </c>
       <c r="C316">
         <f t="shared" ca="1" si="4"/>
@@ -4315,7 +4311,7 @@
         <v>17</v>
       </c>
       <c r="B317">
-        <v>20230423</v>
+        <v>20220423</v>
       </c>
       <c r="C317">
         <f t="shared" ca="1" si="4"/>
@@ -4327,7 +4323,7 @@
         <v>18</v>
       </c>
       <c r="B318">
-        <v>20230500</v>
+        <v>20220500</v>
       </c>
       <c r="C318">
         <f t="shared" ca="1" si="4"/>
@@ -4339,7 +4335,7 @@
         <v>19</v>
       </c>
       <c r="B319">
-        <v>20230507</v>
+        <v>20220507</v>
       </c>
       <c r="C319">
         <f t="shared" ca="1" si="4"/>
@@ -4351,7 +4347,7 @@
         <v>20</v>
       </c>
       <c r="B320">
-        <v>20230514</v>
+        <v>20220514</v>
       </c>
       <c r="C320">
         <f t="shared" ca="1" si="4"/>
@@ -4363,7 +4359,7 @@
         <v>21</v>
       </c>
       <c r="B321">
-        <v>20230521</v>
+        <v>20220521</v>
       </c>
       <c r="C321">
         <f t="shared" ca="1" si="4"/>
@@ -4375,7 +4371,7 @@
         <v>22</v>
       </c>
       <c r="B322">
-        <v>20230528</v>
+        <v>20220528</v>
       </c>
       <c r="C322">
         <f t="shared" ca="1" si="4"/>
@@ -4387,10 +4383,10 @@
         <v>22</v>
       </c>
       <c r="B323">
-        <v>20230597</v>
+        <v>20220597</v>
       </c>
       <c r="C323">
-        <f t="shared" ref="C323:D342" ca="1" si="5">(B323/$C$2)*100</f>
+        <f t="shared" ref="C323:C342" ca="1" si="5">(B323/$C$2)*100</f>
         <v>117.28387299591323</v>
       </c>
     </row>
@@ -4399,7 +4395,7 @@
         <v>23</v>
       </c>
       <c r="B324">
-        <v>20230604</v>
+        <v>20220604</v>
       </c>
       <c r="C324">
         <f t="shared" ca="1" si="5"/>
@@ -4411,7 +4407,7 @@
         <v>24</v>
       </c>
       <c r="B325">
-        <v>20230611</v>
+        <v>20220611</v>
       </c>
       <c r="C325">
         <f t="shared" ca="1" si="5"/>
@@ -4423,7 +4419,7 @@
         <v>25</v>
       </c>
       <c r="B326">
-        <v>20230618</v>
+        <v>20220618</v>
       </c>
       <c r="C326">
         <f t="shared" ca="1" si="5"/>
@@ -4435,7 +4431,7 @@
         <v>26</v>
       </c>
       <c r="B327">
-        <v>20230625</v>
+        <v>20220625</v>
       </c>
       <c r="C327">
         <f t="shared" ca="1" si="5"/>
@@ -4447,7 +4443,7 @@
         <v>27</v>
       </c>
       <c r="B328">
-        <v>20230702</v>
+        <v>20220702</v>
       </c>
       <c r="C328">
         <f t="shared" ca="1" si="5"/>
@@ -4459,7 +4455,7 @@
         <v>28</v>
       </c>
       <c r="B329">
-        <v>20230709</v>
+        <v>20220709</v>
       </c>
       <c r="C329">
         <f t="shared" ca="1" si="5"/>
@@ -4471,7 +4467,7 @@
         <v>29</v>
       </c>
       <c r="B330">
-        <v>20230716</v>
+        <v>20220716</v>
       </c>
       <c r="C330">
         <f t="shared" ca="1" si="5"/>
@@ -4483,7 +4479,7 @@
         <v>30</v>
       </c>
       <c r="B331">
-        <v>20230723</v>
+        <v>20220723</v>
       </c>
       <c r="C331">
         <f t="shared" ca="1" si="5"/>
@@ -4495,7 +4491,7 @@
         <v>31</v>
       </c>
       <c r="B332">
-        <v>20230730</v>
+        <v>20220730</v>
       </c>
       <c r="C332">
         <f t="shared" ca="1" si="5"/>
@@ -4507,7 +4503,7 @@
         <v>31</v>
       </c>
       <c r="B333">
-        <v>20230799</v>
+        <v>20220799</v>
       </c>
       <c r="C333">
         <f t="shared" ca="1" si="5"/>
@@ -4519,7 +4515,7 @@
         <v>32</v>
       </c>
       <c r="B334">
-        <v>20230806</v>
+        <v>20220806</v>
       </c>
       <c r="C334">
         <f t="shared" ca="1" si="5"/>
@@ -4531,7 +4527,7 @@
         <v>33</v>
       </c>
       <c r="B335">
-        <v>20230813</v>
+        <v>20220813</v>
       </c>
       <c r="C335">
         <f t="shared" ca="1" si="5"/>
@@ -4543,7 +4539,7 @@
         <v>34</v>
       </c>
       <c r="B336">
-        <v>20230820</v>
+        <v>20220820</v>
       </c>
       <c r="C336">
         <f t="shared" ca="1" si="5"/>
@@ -4555,7 +4551,7 @@
         <v>35</v>
       </c>
       <c r="B337">
-        <v>20230827</v>
+        <v>20220827</v>
       </c>
       <c r="C337">
         <f t="shared" ca="1" si="5"/>
@@ -4568,7 +4564,7 @@
         <v>35</v>
       </c>
       <c r="B338">
-        <v>20230896</v>
+        <v>20220896</v>
       </c>
       <c r="C338">
         <f t="shared" ca="1" si="5"/>
@@ -4580,7 +4576,7 @@
         <v>36</v>
       </c>
       <c r="B339">
-        <v>20230903</v>
+        <v>20220903</v>
       </c>
       <c r="C339">
         <f t="shared" ca="1" si="5"/>
@@ -4592,7 +4588,7 @@
         <v>37</v>
       </c>
       <c r="B340">
-        <v>20230910</v>
+        <v>20220910</v>
       </c>
       <c r="C340">
         <f t="shared" ca="1" si="5"/>
@@ -4604,7 +4600,7 @@
         <v>38</v>
       </c>
       <c r="B341">
-        <v>20230917</v>
+        <v>20220917</v>
       </c>
       <c r="C341">
         <f t="shared" ca="1" si="5"/>
@@ -4616,7 +4612,7 @@
         <v>39</v>
       </c>
       <c r="B342">
-        <v>20230924</v>
+        <v>20220924</v>
       </c>
       <c r="C342">
         <f t="shared" ca="1" si="5"/>
@@ -4655,7 +4651,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>20180101</v>
+        <v>20170101</v>
       </c>
       <c r="C2">
         <f ca="1">(B2/$C$2)*100</f>
@@ -4667,10 +4663,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>20180107</v>
+        <v>20170107</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:D66" ca="1" si="0">(B3/$C$2)*100</f>
+        <f t="shared" ref="C3:C66" ca="1" si="0">(B3/$C$2)*100</f>
         <v>197.22222222222223</v>
       </c>
     </row>
@@ -4679,7 +4675,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>20180114</v>
+        <v>20170114</v>
       </c>
       <c r="C4">
         <f t="shared" ca="1" si="0"/>
@@ -4691,7 +4687,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>20180121</v>
+        <v>20170121</v>
       </c>
       <c r="C5">
         <f t="shared" ca="1" si="0"/>
@@ -4703,7 +4699,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>20180128</v>
+        <v>20170128</v>
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="0"/>
@@ -4715,7 +4711,7 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>20180197</v>
+        <v>20170197</v>
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="0"/>
@@ -4727,7 +4723,7 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>20180204</v>
+        <v>20170204</v>
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="0"/>
@@ -4739,7 +4735,7 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>20180211</v>
+        <v>20170211</v>
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="0"/>
@@ -4751,7 +4747,7 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>20180218</v>
+        <v>20170218</v>
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="0"/>
@@ -4763,7 +4759,7 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>20180225</v>
+        <v>20170225</v>
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="0"/>
@@ -4775,7 +4771,7 @@
         <v>9</v>
       </c>
       <c r="B12">
-        <v>20180297</v>
+        <v>20170297</v>
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="0"/>
@@ -4787,7 +4783,7 @@
         <v>10</v>
       </c>
       <c r="B13">
-        <v>20180304</v>
+        <v>20170304</v>
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="0"/>
@@ -4799,7 +4795,7 @@
         <v>11</v>
       </c>
       <c r="B14">
-        <v>20180311</v>
+        <v>20170311</v>
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="0"/>
@@ -4811,7 +4807,7 @@
         <v>12</v>
       </c>
       <c r="B15">
-        <v>20180318</v>
+        <v>20170318</v>
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="0"/>
@@ -4823,7 +4819,7 @@
         <v>13</v>
       </c>
       <c r="B16">
-        <v>20180325</v>
+        <v>20170325</v>
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="0"/>
@@ -4835,7 +4831,7 @@
         <v>14</v>
       </c>
       <c r="B17">
-        <v>20180401</v>
+        <v>20170401</v>
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="0"/>
@@ -4847,7 +4843,7 @@
         <v>15</v>
       </c>
       <c r="B18">
-        <v>20180408</v>
+        <v>20170408</v>
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="0"/>
@@ -4859,7 +4855,7 @@
         <v>16</v>
       </c>
       <c r="B19">
-        <v>20180415</v>
+        <v>20170415</v>
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="0"/>
@@ -4871,7 +4867,7 @@
         <v>17</v>
       </c>
       <c r="B20">
-        <v>20180422</v>
+        <v>20170422</v>
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="0"/>
@@ -4883,7 +4879,7 @@
         <v>18</v>
       </c>
       <c r="B21">
-        <v>20180429</v>
+        <v>20170429</v>
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="0"/>
@@ -4895,7 +4891,7 @@
         <v>18</v>
       </c>
       <c r="B22">
-        <v>20180499</v>
+        <v>20170499</v>
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="0"/>
@@ -4907,7 +4903,7 @@
         <v>19</v>
       </c>
       <c r="B23">
-        <v>20180506</v>
+        <v>20170506</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="0"/>
@@ -4919,7 +4915,7 @@
         <v>20</v>
       </c>
       <c r="B24">
-        <v>20180513</v>
+        <v>20170513</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="0"/>
@@ -4931,7 +4927,7 @@
         <v>21</v>
       </c>
       <c r="B25">
-        <v>20180520</v>
+        <v>20170520</v>
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="0"/>
@@ -4943,7 +4939,7 @@
         <v>22</v>
       </c>
       <c r="B26">
-        <v>20180527</v>
+        <v>20170527</v>
       </c>
       <c r="C26">
         <f t="shared" ca="1" si="0"/>
@@ -4955,7 +4951,7 @@
         <v>22</v>
       </c>
       <c r="B27">
-        <v>20180596</v>
+        <v>20170596</v>
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="0"/>
@@ -4967,7 +4963,7 @@
         <v>23</v>
       </c>
       <c r="B28">
-        <v>20180603</v>
+        <v>20170603</v>
       </c>
       <c r="C28">
         <f t="shared" ca="1" si="0"/>
@@ -4979,7 +4975,7 @@
         <v>24</v>
       </c>
       <c r="B29">
-        <v>20180610</v>
+        <v>20170610</v>
       </c>
       <c r="C29">
         <f t="shared" ca="1" si="0"/>
@@ -4991,7 +4987,7 @@
         <v>25</v>
       </c>
       <c r="B30">
-        <v>20180617</v>
+        <v>20170617</v>
       </c>
       <c r="C30">
         <f t="shared" ca="1" si="0"/>
@@ -5003,7 +4999,7 @@
         <v>26</v>
       </c>
       <c r="B31">
-        <v>20180624</v>
+        <v>20170624</v>
       </c>
       <c r="C31">
         <f t="shared" ca="1" si="0"/>
@@ -5015,7 +5011,7 @@
         <v>27</v>
       </c>
       <c r="B32">
-        <v>20180701</v>
+        <v>20170701</v>
       </c>
       <c r="C32">
         <f t="shared" ca="1" si="0"/>
@@ -5027,7 +5023,7 @@
         <v>28</v>
       </c>
       <c r="B33">
-        <v>20180708</v>
+        <v>20170708</v>
       </c>
       <c r="C33">
         <f t="shared" ca="1" si="0"/>
@@ -5039,7 +5035,7 @@
         <v>29</v>
       </c>
       <c r="B34">
-        <v>20180715</v>
+        <v>20170715</v>
       </c>
       <c r="C34">
         <f t="shared" ca="1" si="0"/>
@@ -5051,7 +5047,7 @@
         <v>30</v>
       </c>
       <c r="B35">
-        <v>20180722</v>
+        <v>20170722</v>
       </c>
       <c r="C35">
         <f t="shared" ca="1" si="0"/>
@@ -5063,7 +5059,7 @@
         <v>31</v>
       </c>
       <c r="B36">
-        <v>20180729</v>
+        <v>20170729</v>
       </c>
       <c r="C36">
         <f t="shared" ca="1" si="0"/>
@@ -5075,7 +5071,7 @@
         <v>31</v>
       </c>
       <c r="B37">
-        <v>20180798</v>
+        <v>20170798</v>
       </c>
       <c r="C37">
         <f t="shared" ca="1" si="0"/>
@@ -5087,7 +5083,7 @@
         <v>32</v>
       </c>
       <c r="B38">
-        <v>20180805</v>
+        <v>20170805</v>
       </c>
       <c r="C38">
         <f t="shared" ca="1" si="0"/>
@@ -5099,7 +5095,7 @@
         <v>33</v>
       </c>
       <c r="B39">
-        <v>20180812</v>
+        <v>20170812</v>
       </c>
       <c r="C39">
         <f t="shared" ca="1" si="0"/>
@@ -5111,7 +5107,7 @@
         <v>34</v>
       </c>
       <c r="B40">
-        <v>20180819</v>
+        <v>20170819</v>
       </c>
       <c r="C40">
         <f t="shared" ca="1" si="0"/>
@@ -5123,7 +5119,7 @@
         <v>35</v>
       </c>
       <c r="B41">
-        <v>20180826</v>
+        <v>20170826</v>
       </c>
       <c r="C41">
         <f t="shared" ca="1" si="0"/>
@@ -5135,7 +5131,7 @@
         <v>36</v>
       </c>
       <c r="B42">
-        <v>20180902</v>
+        <v>20170902</v>
       </c>
       <c r="C42">
         <f t="shared" ca="1" si="0"/>
@@ -5147,7 +5143,7 @@
         <v>37</v>
       </c>
       <c r="B43">
-        <v>20180909</v>
+        <v>20170909</v>
       </c>
       <c r="C43">
         <f t="shared" ca="1" si="0"/>
@@ -5159,7 +5155,7 @@
         <v>38</v>
       </c>
       <c r="B44">
-        <v>20180916</v>
+        <v>20170916</v>
       </c>
       <c r="C44">
         <f t="shared" ca="1" si="0"/>
@@ -5171,7 +5167,7 @@
         <v>39</v>
       </c>
       <c r="B45">
-        <v>20180923</v>
+        <v>20170923</v>
       </c>
       <c r="C45">
         <f t="shared" ca="1" si="0"/>
@@ -5183,7 +5179,7 @@
         <v>40</v>
       </c>
       <c r="B46">
-        <v>20181000</v>
+        <v>20171000</v>
       </c>
       <c r="C46">
         <f t="shared" ca="1" si="0"/>
@@ -5195,7 +5191,7 @@
         <v>41</v>
       </c>
       <c r="B47">
-        <v>20181007</v>
+        <v>20171007</v>
       </c>
       <c r="C47">
         <f t="shared" ca="1" si="0"/>
@@ -5207,7 +5203,7 @@
         <v>42</v>
       </c>
       <c r="B48">
-        <v>20181014</v>
+        <v>20171014</v>
       </c>
       <c r="C48">
         <f t="shared" ca="1" si="0"/>
@@ -5219,7 +5215,7 @@
         <v>43</v>
       </c>
       <c r="B49">
-        <v>20181021</v>
+        <v>20171021</v>
       </c>
       <c r="C49">
         <f t="shared" ca="1" si="0"/>
@@ -5231,7 +5227,7 @@
         <v>44</v>
       </c>
       <c r="B50">
-        <v>20181028</v>
+        <v>20171028</v>
       </c>
       <c r="C50">
         <f t="shared" ca="1" si="0"/>
@@ -5243,7 +5239,7 @@
         <v>44</v>
       </c>
       <c r="B51">
-        <v>20181097</v>
+        <v>20171097</v>
       </c>
       <c r="C51">
         <f t="shared" ca="1" si="0"/>
@@ -5255,7 +5251,7 @@
         <v>45</v>
       </c>
       <c r="B52">
-        <v>20181104</v>
+        <v>20171104</v>
       </c>
       <c r="C52">
         <f t="shared" ca="1" si="0"/>
@@ -5267,7 +5263,7 @@
         <v>46</v>
       </c>
       <c r="B53">
-        <v>20181111</v>
+        <v>20171111</v>
       </c>
       <c r="C53">
         <f t="shared" ca="1" si="0"/>
@@ -5279,7 +5275,7 @@
         <v>47</v>
       </c>
       <c r="B54">
-        <v>20181118</v>
+        <v>20171118</v>
       </c>
       <c r="C54">
         <f t="shared" ca="1" si="0"/>
@@ -5291,7 +5287,7 @@
         <v>48</v>
       </c>
       <c r="B55">
-        <v>20181125</v>
+        <v>20171125</v>
       </c>
       <c r="C55">
         <f t="shared" ca="1" si="0"/>
@@ -5303,7 +5299,7 @@
         <v>49</v>
       </c>
       <c r="B56">
-        <v>20181202</v>
+        <v>20171202</v>
       </c>
       <c r="C56">
         <f t="shared" ca="1" si="0"/>
@@ -5315,7 +5311,7 @@
         <v>50</v>
       </c>
       <c r="B57">
-        <v>20181209</v>
+        <v>20171209</v>
       </c>
       <c r="C57">
         <f t="shared" ca="1" si="0"/>
@@ -5327,7 +5323,7 @@
         <v>51</v>
       </c>
       <c r="B58">
-        <v>20181216</v>
+        <v>20171216</v>
       </c>
       <c r="C58">
         <f t="shared" ca="1" si="0"/>
@@ -5339,7 +5335,7 @@
         <v>52</v>
       </c>
       <c r="B59">
-        <v>20181223</v>
+        <v>20171223</v>
       </c>
       <c r="C59">
         <f t="shared" ca="1" si="0"/>
@@ -5351,7 +5347,7 @@
         <v>53</v>
       </c>
       <c r="B60">
-        <v>20181230</v>
+        <v>20171230</v>
       </c>
       <c r="C60">
         <f t="shared" ca="1" si="0"/>
@@ -5363,7 +5359,7 @@
         <v>1</v>
       </c>
       <c r="B61">
-        <v>20190101</v>
+        <v>20180101</v>
       </c>
       <c r="C61">
         <f t="shared" ca="1" si="0"/>
@@ -5375,7 +5371,7 @@
         <v>2</v>
       </c>
       <c r="B62">
-        <v>20190106</v>
+        <v>20180106</v>
       </c>
       <c r="C62">
         <f t="shared" ca="1" si="0"/>
@@ -5387,7 +5383,7 @@
         <v>3</v>
       </c>
       <c r="B63">
-        <v>20190113</v>
+        <v>20180113</v>
       </c>
       <c r="C63">
         <f t="shared" ca="1" si="0"/>
@@ -5399,7 +5395,7 @@
         <v>4</v>
       </c>
       <c r="B64">
-        <v>20190120</v>
+        <v>20180120</v>
       </c>
       <c r="C64">
         <f t="shared" ca="1" si="0"/>
@@ -5411,7 +5407,7 @@
         <v>5</v>
       </c>
       <c r="B65">
-        <v>20190127</v>
+        <v>20180127</v>
       </c>
       <c r="C65">
         <f t="shared" ca="1" si="0"/>
@@ -5423,7 +5419,7 @@
         <v>5</v>
       </c>
       <c r="B66">
-        <v>20190196</v>
+        <v>20180196</v>
       </c>
       <c r="C66">
         <f t="shared" ca="1" si="0"/>
@@ -5435,10 +5431,10 @@
         <v>6</v>
       </c>
       <c r="B67">
-        <v>20190203</v>
+        <v>20180203</v>
       </c>
       <c r="C67">
-        <f t="shared" ref="C67:D130" ca="1" si="1">(B67/$C$2)*100</f>
+        <f t="shared" ref="C67:C130" ca="1" si="1">(B67/$C$2)*100</f>
         <v>396.32936507936506</v>
       </c>
     </row>
@@ -5447,7 +5443,7 @@
         <v>7</v>
       </c>
       <c r="B68">
-        <v>20190210</v>
+        <v>20180210</v>
       </c>
       <c r="C68">
         <f t="shared" ca="1" si="1"/>
@@ -5459,7 +5455,7 @@
         <v>8</v>
       </c>
       <c r="B69">
-        <v>20190217</v>
+        <v>20180217</v>
       </c>
       <c r="C69">
         <f t="shared" ca="1" si="1"/>
@@ -5471,7 +5467,7 @@
         <v>9</v>
       </c>
       <c r="B70">
-        <v>20190224</v>
+        <v>20180224</v>
       </c>
       <c r="C70">
         <f t="shared" ca="1" si="1"/>
@@ -5483,7 +5479,7 @@
         <v>9</v>
       </c>
       <c r="B71">
-        <v>20190296</v>
+        <v>20180296</v>
       </c>
       <c r="C71">
         <f t="shared" ca="1" si="1"/>
@@ -5495,7 +5491,7 @@
         <v>10</v>
       </c>
       <c r="B72">
-        <v>20190303</v>
+        <v>20180303</v>
       </c>
       <c r="C72">
         <f t="shared" ca="1" si="1"/>
@@ -5507,7 +5503,7 @@
         <v>11</v>
       </c>
       <c r="B73">
-        <v>20190310</v>
+        <v>20180310</v>
       </c>
       <c r="C73">
         <f t="shared" ca="1" si="1"/>
@@ -5519,7 +5515,7 @@
         <v>12</v>
       </c>
       <c r="B74">
-        <v>20190317</v>
+        <v>20180317</v>
       </c>
       <c r="C74">
         <f t="shared" ca="1" si="1"/>
@@ -5531,7 +5527,7 @@
         <v>13</v>
       </c>
       <c r="B75">
-        <v>20190324</v>
+        <v>20180324</v>
       </c>
       <c r="C75">
         <f t="shared" ca="1" si="1"/>
@@ -5543,7 +5539,7 @@
         <v>14</v>
       </c>
       <c r="B76">
-        <v>20190400</v>
+        <v>20180400</v>
       </c>
       <c r="C76">
         <f t="shared" ca="1" si="1"/>
@@ -5555,7 +5551,7 @@
         <v>15</v>
       </c>
       <c r="B77">
-        <v>20190407</v>
+        <v>20180407</v>
       </c>
       <c r="C77">
         <f t="shared" ca="1" si="1"/>
@@ -5567,7 +5563,7 @@
         <v>16</v>
       </c>
       <c r="B78">
-        <v>20190414</v>
+        <v>20180414</v>
       </c>
       <c r="C78">
         <f t="shared" ca="1" si="1"/>
@@ -5579,7 +5575,7 @@
         <v>17</v>
       </c>
       <c r="B79">
-        <v>20190421</v>
+        <v>20180421</v>
       </c>
       <c r="C79">
         <f t="shared" ca="1" si="1"/>
@@ -5591,7 +5587,7 @@
         <v>18</v>
       </c>
       <c r="B80">
-        <v>20190428</v>
+        <v>20180428</v>
       </c>
       <c r="C80">
         <f t="shared" ca="1" si="1"/>
@@ -5603,7 +5599,7 @@
         <v>18</v>
       </c>
       <c r="B81">
-        <v>20190498</v>
+        <v>20180498</v>
       </c>
       <c r="C81">
         <f t="shared" ca="1" si="1"/>
@@ -5615,7 +5611,7 @@
         <v>19</v>
       </c>
       <c r="B82">
-        <v>20190505</v>
+        <v>20180505</v>
       </c>
       <c r="C82">
         <f t="shared" ca="1" si="1"/>
@@ -5627,7 +5623,7 @@
         <v>20</v>
       </c>
       <c r="B83">
-        <v>20190512</v>
+        <v>20180512</v>
       </c>
       <c r="C83">
         <f t="shared" ca="1" si="1"/>
@@ -5639,7 +5635,7 @@
         <v>21</v>
       </c>
       <c r="B84">
-        <v>20190519</v>
+        <v>20180519</v>
       </c>
       <c r="C84">
         <f t="shared" ca="1" si="1"/>
@@ -5651,7 +5647,7 @@
         <v>22</v>
       </c>
       <c r="B85">
-        <v>20190526</v>
+        <v>20180526</v>
       </c>
       <c r="C85">
         <f t="shared" ca="1" si="1"/>
@@ -5663,7 +5659,7 @@
         <v>23</v>
       </c>
       <c r="B86">
-        <v>20190602</v>
+        <v>20180602</v>
       </c>
       <c r="C86">
         <f t="shared" ca="1" si="1"/>
@@ -5675,7 +5671,7 @@
         <v>24</v>
       </c>
       <c r="B87">
-        <v>20190609</v>
+        <v>20180609</v>
       </c>
       <c r="C87">
         <f t="shared" ca="1" si="1"/>
@@ -5687,7 +5683,7 @@
         <v>25</v>
       </c>
       <c r="B88">
-        <v>20190616</v>
+        <v>20180616</v>
       </c>
       <c r="C88">
         <f t="shared" ca="1" si="1"/>
@@ -5699,7 +5695,7 @@
         <v>26</v>
       </c>
       <c r="B89">
-        <v>20190623</v>
+        <v>20180623</v>
       </c>
       <c r="C89">
         <f t="shared" ca="1" si="1"/>
@@ -5711,7 +5707,7 @@
         <v>27</v>
       </c>
       <c r="B90">
-        <v>20190700</v>
+        <v>20180700</v>
       </c>
       <c r="C90">
         <f t="shared" ca="1" si="1"/>
@@ -5723,7 +5719,7 @@
         <v>28</v>
       </c>
       <c r="B91">
-        <v>20190707</v>
+        <v>20180707</v>
       </c>
       <c r="C91">
         <f t="shared" ca="1" si="1"/>
@@ -5735,7 +5731,7 @@
         <v>29</v>
       </c>
       <c r="B92">
-        <v>20190714</v>
+        <v>20180714</v>
       </c>
       <c r="C92">
         <f t="shared" ca="1" si="1"/>
@@ -5747,7 +5743,7 @@
         <v>30</v>
       </c>
       <c r="B93">
-        <v>20190721</v>
+        <v>20180721</v>
       </c>
       <c r="C93">
         <f t="shared" ca="1" si="1"/>
@@ -5759,7 +5755,7 @@
         <v>31</v>
       </c>
       <c r="B94">
-        <v>20190728</v>
+        <v>20180728</v>
       </c>
       <c r="C94">
         <f t="shared" ca="1" si="1"/>
@@ -5771,7 +5767,7 @@
         <v>31</v>
       </c>
       <c r="B95">
-        <v>20190797</v>
+        <v>20180797</v>
       </c>
       <c r="C95">
         <f t="shared" ca="1" si="1"/>
@@ -5783,7 +5779,7 @@
         <v>32</v>
       </c>
       <c r="B96">
-        <v>20190804</v>
+        <v>20180804</v>
       </c>
       <c r="C96">
         <f t="shared" ca="1" si="1"/>
@@ -5795,7 +5791,7 @@
         <v>33</v>
       </c>
       <c r="B97">
-        <v>20190811</v>
+        <v>20180811</v>
       </c>
       <c r="C97">
         <f t="shared" ca="1" si="1"/>
@@ -5807,7 +5803,7 @@
         <v>34</v>
       </c>
       <c r="B98">
-        <v>20190818</v>
+        <v>20180818</v>
       </c>
       <c r="C98">
         <f t="shared" ca="1" si="1"/>
@@ -5819,7 +5815,7 @@
         <v>35</v>
       </c>
       <c r="B99">
-        <v>20190825</v>
+        <v>20180825</v>
       </c>
       <c r="C99">
         <f t="shared" ca="1" si="1"/>
@@ -5831,7 +5827,7 @@
         <v>36</v>
       </c>
       <c r="B100">
-        <v>20190901</v>
+        <v>20180901</v>
       </c>
       <c r="C100">
         <f t="shared" ca="1" si="1"/>
@@ -5843,7 +5839,7 @@
         <v>37</v>
       </c>
       <c r="B101">
-        <v>20190908</v>
+        <v>20180908</v>
       </c>
       <c r="C101">
         <f t="shared" ca="1" si="1"/>
@@ -5855,7 +5851,7 @@
         <v>38</v>
       </c>
       <c r="B102">
-        <v>20190915</v>
+        <v>20180915</v>
       </c>
       <c r="C102">
         <f t="shared" ca="1" si="1"/>
@@ -5867,7 +5863,7 @@
         <v>39</v>
       </c>
       <c r="B103">
-        <v>20190922</v>
+        <v>20180922</v>
       </c>
       <c r="C103">
         <f t="shared" ca="1" si="1"/>
@@ -5879,7 +5875,7 @@
         <v>40</v>
       </c>
       <c r="B104">
-        <v>20190929</v>
+        <v>20180929</v>
       </c>
       <c r="C104">
         <f t="shared" ca="1" si="1"/>
@@ -5891,7 +5887,7 @@
         <v>40</v>
       </c>
       <c r="B105">
-        <v>20190999</v>
+        <v>20180999</v>
       </c>
       <c r="C105">
         <f t="shared" ca="1" si="1"/>
@@ -5903,7 +5899,7 @@
         <v>41</v>
       </c>
       <c r="B106">
-        <v>20191006</v>
+        <v>20181006</v>
       </c>
       <c r="C106">
         <f t="shared" ca="1" si="1"/>
@@ -5915,7 +5911,7 @@
         <v>42</v>
       </c>
       <c r="B107">
-        <v>20191013</v>
+        <v>20181013</v>
       </c>
       <c r="C107">
         <f t="shared" ca="1" si="1"/>
@@ -5927,7 +5923,7 @@
         <v>43</v>
       </c>
       <c r="B108">
-        <v>20191020</v>
+        <v>20181020</v>
       </c>
       <c r="C108">
         <f t="shared" ca="1" si="1"/>
@@ -5939,7 +5935,7 @@
         <v>44</v>
       </c>
       <c r="B109">
-        <v>20191027</v>
+        <v>20181027</v>
       </c>
       <c r="C109">
         <f t="shared" ca="1" si="1"/>
@@ -5951,7 +5947,7 @@
         <v>44</v>
       </c>
       <c r="B110">
-        <v>20191096</v>
+        <v>20181096</v>
       </c>
       <c r="C110">
         <f t="shared" ca="1" si="1"/>
@@ -5963,7 +5959,7 @@
         <v>45</v>
       </c>
       <c r="B111">
-        <v>20191103</v>
+        <v>20181103</v>
       </c>
       <c r="C111">
         <f t="shared" ca="1" si="1"/>
@@ -5975,7 +5971,7 @@
         <v>46</v>
       </c>
       <c r="B112">
-        <v>20191110</v>
+        <v>20181110</v>
       </c>
       <c r="C112">
         <f t="shared" ca="1" si="1"/>
@@ -5987,7 +5983,7 @@
         <v>47</v>
       </c>
       <c r="B113">
-        <v>20191117</v>
+        <v>20181117</v>
       </c>
       <c r="C113">
         <f t="shared" ca="1" si="1"/>
@@ -5999,7 +5995,7 @@
         <v>48</v>
       </c>
       <c r="B114">
-        <v>20191124</v>
+        <v>20181124</v>
       </c>
       <c r="C114">
         <f t="shared" ca="1" si="1"/>
@@ -6011,7 +6007,7 @@
         <v>49</v>
       </c>
       <c r="B115">
-        <v>20191201</v>
+        <v>20181201</v>
       </c>
       <c r="C115">
         <f t="shared" ca="1" si="1"/>
@@ -6023,7 +6019,7 @@
         <v>50</v>
       </c>
       <c r="B116">
-        <v>20191208</v>
+        <v>20181208</v>
       </c>
       <c r="C116">
         <f t="shared" ca="1" si="1"/>
@@ -6035,7 +6031,7 @@
         <v>51</v>
       </c>
       <c r="B117">
-        <v>20191215</v>
+        <v>20181215</v>
       </c>
       <c r="C117">
         <f t="shared" ca="1" si="1"/>
@@ -6047,7 +6043,7 @@
         <v>52</v>
       </c>
       <c r="B118">
-        <v>20191222</v>
+        <v>20181222</v>
       </c>
       <c r="C118">
         <f t="shared" ca="1" si="1"/>
@@ -6059,7 +6055,7 @@
         <v>53</v>
       </c>
       <c r="B119">
-        <v>20191229</v>
+        <v>20181229</v>
       </c>
       <c r="C119">
         <f t="shared" ca="1" si="1"/>
@@ -6071,7 +6067,7 @@
         <v>1</v>
       </c>
       <c r="B120">
-        <v>20200101</v>
+        <v>20190101</v>
       </c>
       <c r="C120">
         <f t="shared" ca="1" si="1"/>
@@ -6083,7 +6079,7 @@
         <v>2</v>
       </c>
       <c r="B121">
-        <v>20200105</v>
+        <v>20190105</v>
       </c>
       <c r="C121">
         <f t="shared" ca="1" si="1"/>
@@ -6095,7 +6091,7 @@
         <v>3</v>
       </c>
       <c r="B122">
-        <v>20200112</v>
+        <v>20190112</v>
       </c>
       <c r="C122">
         <f t="shared" ca="1" si="1"/>
@@ -6107,7 +6103,7 @@
         <v>4</v>
       </c>
       <c r="B123">
-        <v>20200119</v>
+        <v>20190119</v>
       </c>
       <c r="C123">
         <f t="shared" ca="1" si="1"/>
@@ -6119,7 +6115,7 @@
         <v>5</v>
       </c>
       <c r="B124">
-        <v>20200126</v>
+        <v>20190126</v>
       </c>
       <c r="C124">
         <f t="shared" ca="1" si="1"/>
@@ -6131,7 +6127,7 @@
         <v>6</v>
       </c>
       <c r="B125">
-        <v>20200202</v>
+        <v>20190202</v>
       </c>
       <c r="C125">
         <f t="shared" ca="1" si="1"/>
@@ -6143,7 +6139,7 @@
         <v>7</v>
       </c>
       <c r="B126">
-        <v>20200209</v>
+        <v>20190209</v>
       </c>
       <c r="C126">
         <f t="shared" ca="1" si="1"/>
@@ -6155,7 +6151,7 @@
         <v>8</v>
       </c>
       <c r="B127">
-        <v>20200216</v>
+        <v>20190216</v>
       </c>
       <c r="C127">
         <f t="shared" ca="1" si="1"/>
@@ -6167,7 +6163,7 @@
         <v>9</v>
       </c>
       <c r="B128">
-        <v>20200223</v>
+        <v>20190223</v>
       </c>
       <c r="C128">
         <f t="shared" ca="1" si="1"/>
@@ -6179,7 +6175,7 @@
         <v>10</v>
       </c>
       <c r="B129">
-        <v>20200301</v>
+        <v>20190301</v>
       </c>
       <c r="C129">
         <f t="shared" ca="1" si="1"/>
@@ -6191,7 +6187,7 @@
         <v>11</v>
       </c>
       <c r="B130">
-        <v>20200308</v>
+        <v>20190308</v>
       </c>
       <c r="C130">
         <f t="shared" ca="1" si="1"/>
@@ -6203,10 +6199,10 @@
         <v>12</v>
       </c>
       <c r="B131">
-        <v>20200315</v>
+        <v>20190315</v>
       </c>
       <c r="C131">
-        <f t="shared" ref="C131:D194" ca="1" si="2">(B131/$C$2)*100</f>
+        <f t="shared" ref="C131:C194" ca="1" si="2">(B131/$C$2)*100</f>
         <v>471.23015873015868</v>
       </c>
     </row>
@@ -6215,7 +6211,7 @@
         <v>13</v>
       </c>
       <c r="B132">
-        <v>20200322</v>
+        <v>20190322</v>
       </c>
       <c r="C132">
         <f t="shared" ca="1" si="2"/>
@@ -6227,7 +6223,7 @@
         <v>14</v>
       </c>
       <c r="B133">
-        <v>20200329</v>
+        <v>20190329</v>
       </c>
       <c r="C133">
         <f t="shared" ca="1" si="2"/>
@@ -6239,7 +6235,7 @@
         <v>14</v>
       </c>
       <c r="B134">
-        <v>20200398</v>
+        <v>20190398</v>
       </c>
       <c r="C134">
         <f t="shared" ca="1" si="2"/>
@@ -6251,7 +6247,7 @@
         <v>15</v>
       </c>
       <c r="B135">
-        <v>20200405</v>
+        <v>20190405</v>
       </c>
       <c r="C135">
         <f t="shared" ca="1" si="2"/>
@@ -6263,7 +6259,7 @@
         <v>16</v>
       </c>
       <c r="B136">
-        <v>20200412</v>
+        <v>20190412</v>
       </c>
       <c r="C136">
         <f t="shared" ca="1" si="2"/>
@@ -6275,7 +6271,7 @@
         <v>17</v>
       </c>
       <c r="B137">
-        <v>20200419</v>
+        <v>20190419</v>
       </c>
       <c r="C137">
         <f t="shared" ca="1" si="2"/>
@@ -6287,7 +6283,7 @@
         <v>18</v>
       </c>
       <c r="B138">
-        <v>20200426</v>
+        <v>20190426</v>
       </c>
       <c r="C138">
         <f t="shared" ca="1" si="2"/>
@@ -6299,7 +6295,7 @@
         <v>19</v>
       </c>
       <c r="B139">
-        <v>20200503</v>
+        <v>20190503</v>
       </c>
       <c r="C139">
         <f t="shared" ca="1" si="2"/>
@@ -6311,7 +6307,7 @@
         <v>20</v>
       </c>
       <c r="B140">
-        <v>20200510</v>
+        <v>20190510</v>
       </c>
       <c r="C140">
         <f t="shared" ca="1" si="2"/>
@@ -6323,7 +6319,7 @@
         <v>21</v>
       </c>
       <c r="B141">
-        <v>20200517</v>
+        <v>20190517</v>
       </c>
       <c r="C141">
         <f t="shared" ca="1" si="2"/>
@@ -6335,7 +6331,7 @@
         <v>22</v>
       </c>
       <c r="B142">
-        <v>20200524</v>
+        <v>20190524</v>
       </c>
       <c r="C142">
         <f t="shared" ca="1" si="2"/>
@@ -6347,7 +6343,7 @@
         <v>23</v>
       </c>
       <c r="B143">
-        <v>20200600</v>
+        <v>20190600</v>
       </c>
       <c r="C143">
         <f t="shared" ca="1" si="2"/>
@@ -6359,7 +6355,7 @@
         <v>24</v>
       </c>
       <c r="B144">
-        <v>20200607</v>
+        <v>20190607</v>
       </c>
       <c r="C144">
         <f t="shared" ca="1" si="2"/>
@@ -6371,7 +6367,7 @@
         <v>25</v>
       </c>
       <c r="B145">
-        <v>20200614</v>
+        <v>20190614</v>
       </c>
       <c r="C145">
         <f t="shared" ca="1" si="2"/>
@@ -6383,7 +6379,7 @@
         <v>26</v>
       </c>
       <c r="B146">
-        <v>20200621</v>
+        <v>20190621</v>
       </c>
       <c r="C146">
         <f t="shared" ca="1" si="2"/>
@@ -6395,7 +6391,7 @@
         <v>27</v>
       </c>
       <c r="B147">
-        <v>20200628</v>
+        <v>20190628</v>
       </c>
       <c r="C147">
         <f t="shared" ca="1" si="2"/>
@@ -6407,7 +6403,7 @@
         <v>27</v>
       </c>
       <c r="B148">
-        <v>20200698</v>
+        <v>20190698</v>
       </c>
       <c r="C148">
         <f t="shared" ca="1" si="2"/>
@@ -6419,7 +6415,7 @@
         <v>28</v>
       </c>
       <c r="B149">
-        <v>20200705</v>
+        <v>20190705</v>
       </c>
       <c r="C149">
         <f t="shared" ca="1" si="2"/>
@@ -6431,7 +6427,7 @@
         <v>29</v>
       </c>
       <c r="B150">
-        <v>20200712</v>
+        <v>20190712</v>
       </c>
       <c r="C150">
         <f t="shared" ca="1" si="2"/>
@@ -6443,7 +6439,7 @@
         <v>30</v>
       </c>
       <c r="B151">
-        <v>20200719</v>
+        <v>20190719</v>
       </c>
       <c r="C151">
         <f t="shared" ca="1" si="2"/>
@@ -6455,7 +6451,7 @@
         <v>31</v>
       </c>
       <c r="B152">
-        <v>20200726</v>
+        <v>20190726</v>
       </c>
       <c r="C152">
         <f t="shared" ca="1" si="2"/>
@@ -6467,7 +6463,7 @@
         <v>32</v>
       </c>
       <c r="B153">
-        <v>20200802</v>
+        <v>20190802</v>
       </c>
       <c r="C153">
         <f t="shared" ca="1" si="2"/>
@@ -6479,7 +6475,7 @@
         <v>33</v>
       </c>
       <c r="B154">
-        <v>20200809</v>
+        <v>20190809</v>
       </c>
       <c r="C154">
         <f t="shared" ca="1" si="2"/>
@@ -6491,7 +6487,7 @@
         <v>34</v>
       </c>
       <c r="B155">
-        <v>20200816</v>
+        <v>20190816</v>
       </c>
       <c r="C155">
         <f t="shared" ca="1" si="2"/>
@@ -6503,7 +6499,7 @@
         <v>35</v>
       </c>
       <c r="B156">
-        <v>20200823</v>
+        <v>20190823</v>
       </c>
       <c r="C156">
         <f t="shared" ca="1" si="2"/>
@@ -6515,7 +6511,7 @@
         <v>36</v>
       </c>
       <c r="B157">
-        <v>20200830</v>
+        <v>20190830</v>
       </c>
       <c r="C157">
         <f t="shared" ca="1" si="2"/>
@@ -6527,7 +6523,7 @@
         <v>36</v>
       </c>
       <c r="B158">
-        <v>20200899</v>
+        <v>20190899</v>
       </c>
       <c r="C158">
         <f t="shared" ca="1" si="2"/>
@@ -6539,7 +6535,7 @@
         <v>37</v>
       </c>
       <c r="B159">
-        <v>20200906</v>
+        <v>20190906</v>
       </c>
       <c r="C159">
         <f t="shared" ca="1" si="2"/>
@@ -6551,7 +6547,7 @@
         <v>38</v>
       </c>
       <c r="B160">
-        <v>20200913</v>
+        <v>20190913</v>
       </c>
       <c r="C160">
         <f t="shared" ca="1" si="2"/>
@@ -6563,7 +6559,7 @@
         <v>39</v>
       </c>
       <c r="B161">
-        <v>20200920</v>
+        <v>20190920</v>
       </c>
       <c r="C161">
         <f t="shared" ca="1" si="2"/>
@@ -6575,7 +6571,7 @@
         <v>40</v>
       </c>
       <c r="B162">
-        <v>20200927</v>
+        <v>20190927</v>
       </c>
       <c r="C162">
         <f t="shared" ca="1" si="2"/>
@@ -6587,7 +6583,7 @@
         <v>40</v>
       </c>
       <c r="B163">
-        <v>20200997</v>
+        <v>20190997</v>
       </c>
       <c r="C163">
         <f t="shared" ca="1" si="2"/>
@@ -6599,7 +6595,7 @@
         <v>41</v>
       </c>
       <c r="B164">
-        <v>20201004</v>
+        <v>20191004</v>
       </c>
       <c r="C164">
         <f t="shared" ca="1" si="2"/>
@@ -6611,7 +6607,7 @@
         <v>42</v>
       </c>
       <c r="B165">
-        <v>20201011</v>
+        <v>20191011</v>
       </c>
       <c r="C165">
         <f t="shared" ca="1" si="2"/>
@@ -6623,7 +6619,7 @@
         <v>43</v>
       </c>
       <c r="B166">
-        <v>20201018</v>
+        <v>20191018</v>
       </c>
       <c r="C166">
         <f t="shared" ca="1" si="2"/>
@@ -6635,7 +6631,7 @@
         <v>44</v>
       </c>
       <c r="B167">
-        <v>20201025</v>
+        <v>20191025</v>
       </c>
       <c r="C167">
         <f t="shared" ca="1" si="2"/>
@@ -6647,7 +6643,7 @@
         <v>45</v>
       </c>
       <c r="B168">
-        <v>20201101</v>
+        <v>20191101</v>
       </c>
       <c r="C168">
         <f t="shared" ca="1" si="2"/>
@@ -6659,7 +6655,7 @@
         <v>46</v>
       </c>
       <c r="B169">
-        <v>20201108</v>
+        <v>20191108</v>
       </c>
       <c r="C169">
         <f t="shared" ca="1" si="2"/>
@@ -6671,7 +6667,7 @@
         <v>47</v>
       </c>
       <c r="B170">
-        <v>20201115</v>
+        <v>20191115</v>
       </c>
       <c r="C170">
         <f t="shared" ca="1" si="2"/>
@@ -6683,7 +6679,7 @@
         <v>48</v>
       </c>
       <c r="B171">
-        <v>20201122</v>
+        <v>20191122</v>
       </c>
       <c r="C171">
         <f t="shared" ca="1" si="2"/>
@@ -6695,7 +6691,7 @@
         <v>49</v>
       </c>
       <c r="B172">
-        <v>20201129</v>
+        <v>20191129</v>
       </c>
       <c r="C172">
         <f t="shared" ca="1" si="2"/>
@@ -6707,7 +6703,7 @@
         <v>49</v>
       </c>
       <c r="B173">
-        <v>20201199</v>
+        <v>20191199</v>
       </c>
       <c r="C173">
         <f t="shared" ca="1" si="2"/>
@@ -6719,7 +6715,7 @@
         <v>50</v>
       </c>
       <c r="B174">
-        <v>20201206</v>
+        <v>20191206</v>
       </c>
       <c r="C174">
         <f t="shared" ca="1" si="2"/>
@@ -6731,7 +6727,7 @@
         <v>51</v>
       </c>
       <c r="B175">
-        <v>20201213</v>
+        <v>20191213</v>
       </c>
       <c r="C175">
         <f t="shared" ca="1" si="2"/>
@@ -6743,7 +6739,7 @@
         <v>52</v>
       </c>
       <c r="B176">
-        <v>20201220</v>
+        <v>20191220</v>
       </c>
       <c r="C176">
         <f t="shared" ca="1" si="2"/>
@@ -6755,7 +6751,7 @@
         <v>53</v>
       </c>
       <c r="B177">
-        <v>20201227</v>
+        <v>20191227</v>
       </c>
       <c r="C177">
         <f t="shared" ca="1" si="2"/>
@@ -6767,7 +6763,7 @@
         <v>2</v>
       </c>
       <c r="B178">
-        <v>20210103</v>
+        <v>20200103</v>
       </c>
       <c r="C178">
         <f t="shared" ca="1" si="2"/>
@@ -6779,7 +6775,7 @@
         <v>3</v>
       </c>
       <c r="B179">
-        <v>20210110</v>
+        <v>20200110</v>
       </c>
       <c r="C179">
         <f t="shared" ca="1" si="2"/>
@@ -6791,7 +6787,7 @@
         <v>4</v>
       </c>
       <c r="B180">
-        <v>20210117</v>
+        <v>20200117</v>
       </c>
       <c r="C180">
         <f t="shared" ca="1" si="2"/>
@@ -6803,7 +6799,7 @@
         <v>5</v>
       </c>
       <c r="B181">
-        <v>20210124</v>
+        <v>20200124</v>
       </c>
       <c r="C181">
         <f t="shared" ca="1" si="2"/>
@@ -6815,7 +6811,7 @@
         <v>6</v>
       </c>
       <c r="B182">
-        <v>20210200</v>
+        <v>20200200</v>
       </c>
       <c r="C182">
         <f t="shared" ca="1" si="2"/>
@@ -6827,7 +6823,7 @@
         <v>7</v>
       </c>
       <c r="B183">
-        <v>20210207</v>
+        <v>20200207</v>
       </c>
       <c r="C183">
         <f t="shared" ca="1" si="2"/>
@@ -6839,7 +6835,7 @@
         <v>8</v>
       </c>
       <c r="B184">
-        <v>20210214</v>
+        <v>20200214</v>
       </c>
       <c r="C184">
         <f t="shared" ca="1" si="2"/>
@@ -6851,7 +6847,7 @@
         <v>9</v>
       </c>
       <c r="B185">
-        <v>20210221</v>
+        <v>20200221</v>
       </c>
       <c r="C185">
         <f t="shared" ca="1" si="2"/>
@@ -6863,7 +6859,7 @@
         <v>10</v>
       </c>
       <c r="B186">
-        <v>20210300</v>
+        <v>20200300</v>
       </c>
       <c r="C186">
         <f t="shared" ca="1" si="2"/>
@@ -6875,7 +6871,7 @@
         <v>11</v>
       </c>
       <c r="B187">
-        <v>20210307</v>
+        <v>20200307</v>
       </c>
       <c r="C187">
         <f t="shared" ca="1" si="2"/>
@@ -6887,7 +6883,7 @@
         <v>12</v>
       </c>
       <c r="B188">
-        <v>20210314</v>
+        <v>20200314</v>
       </c>
       <c r="C188">
         <f t="shared" ca="1" si="2"/>
@@ -6899,7 +6895,7 @@
         <v>13</v>
       </c>
       <c r="B189">
-        <v>20210321</v>
+        <v>20200321</v>
       </c>
       <c r="C189">
         <f t="shared" ca="1" si="2"/>
@@ -6911,7 +6907,7 @@
         <v>14</v>
       </c>
       <c r="B190">
-        <v>20210328</v>
+        <v>20200328</v>
       </c>
       <c r="C190">
         <f t="shared" ca="1" si="2"/>
@@ -6923,7 +6919,7 @@
         <v>14</v>
       </c>
       <c r="B191">
-        <v>20210397</v>
+        <v>20200397</v>
       </c>
       <c r="C191">
         <f t="shared" ca="1" si="2"/>
@@ -6935,7 +6931,7 @@
         <v>15</v>
       </c>
       <c r="B192">
-        <v>20210404</v>
+        <v>20200404</v>
       </c>
       <c r="C192">
         <f t="shared" ca="1" si="2"/>
@@ -6947,7 +6943,7 @@
         <v>16</v>
       </c>
       <c r="B193">
-        <v>20210411</v>
+        <v>20200411</v>
       </c>
       <c r="C193">
         <f t="shared" ca="1" si="2"/>
@@ -6959,7 +6955,7 @@
         <v>17</v>
       </c>
       <c r="B194">
-        <v>20210418</v>
+        <v>20200418</v>
       </c>
       <c r="C194">
         <f t="shared" ca="1" si="2"/>
@@ -6971,10 +6967,10 @@
         <v>18</v>
       </c>
       <c r="B195">
-        <v>20210425</v>
+        <v>20200425</v>
       </c>
       <c r="C195">
-        <f t="shared" ref="C195:D258" ca="1" si="3">(B195/$C$2)*100</f>
+        <f t="shared" ref="C195:C258" ca="1" si="3">(B195/$C$2)*100</f>
         <v>811.50793650793651</v>
       </c>
     </row>
@@ -6983,7 +6979,7 @@
         <v>18</v>
       </c>
       <c r="B196">
-        <v>20210495</v>
+        <v>20200495</v>
       </c>
       <c r="C196">
         <f t="shared" ca="1" si="3"/>
@@ -6995,7 +6991,7 @@
         <v>19</v>
       </c>
       <c r="B197">
-        <v>20210502</v>
+        <v>20200502</v>
       </c>
       <c r="C197">
         <f t="shared" ca="1" si="3"/>
@@ -7007,7 +7003,7 @@
         <v>20</v>
       </c>
       <c r="B198">
-        <v>20210509</v>
+        <v>20200509</v>
       </c>
       <c r="C198">
         <f t="shared" ca="1" si="3"/>
@@ -7019,7 +7015,7 @@
         <v>21</v>
       </c>
       <c r="B199">
-        <v>20210516</v>
+        <v>20200516</v>
       </c>
       <c r="C199">
         <f t="shared" ca="1" si="3"/>
@@ -7031,7 +7027,7 @@
         <v>22</v>
       </c>
       <c r="B200">
-        <v>20210523</v>
+        <v>20200523</v>
       </c>
       <c r="C200">
         <f t="shared" ca="1" si="3"/>
@@ -7043,7 +7039,7 @@
         <v>23</v>
       </c>
       <c r="B201">
-        <v>20210530</v>
+        <v>20200530</v>
       </c>
       <c r="C201">
         <f t="shared" ca="1" si="3"/>
@@ -7055,7 +7051,7 @@
         <v>23</v>
       </c>
       <c r="B202">
-        <v>20210599</v>
+        <v>20200599</v>
       </c>
       <c r="C202">
         <f t="shared" ca="1" si="3"/>
@@ -7067,7 +7063,7 @@
         <v>24</v>
       </c>
       <c r="B203">
-        <v>20210606</v>
+        <v>20200606</v>
       </c>
       <c r="C203">
         <f t="shared" ca="1" si="3"/>
@@ -7079,7 +7075,7 @@
         <v>25</v>
       </c>
       <c r="B204">
-        <v>20210613</v>
+        <v>20200613</v>
       </c>
       <c r="C204">
         <f t="shared" ca="1" si="3"/>
@@ -7091,7 +7087,7 @@
         <v>26</v>
       </c>
       <c r="B205">
-        <v>20210620</v>
+        <v>20200620</v>
       </c>
       <c r="C205">
         <f t="shared" ca="1" si="3"/>
@@ -7103,7 +7099,7 @@
         <v>27</v>
       </c>
       <c r="B206">
-        <v>20210627</v>
+        <v>20200627</v>
       </c>
       <c r="C206">
         <f t="shared" ca="1" si="3"/>
@@ -7115,7 +7111,7 @@
         <v>27</v>
       </c>
       <c r="B207">
-        <v>20210697</v>
+        <v>20200697</v>
       </c>
       <c r="C207">
         <f t="shared" ca="1" si="3"/>
@@ -7127,7 +7123,7 @@
         <v>28</v>
       </c>
       <c r="B208">
-        <v>20210704</v>
+        <v>20200704</v>
       </c>
       <c r="C208">
         <f t="shared" ca="1" si="3"/>
@@ -7139,7 +7135,7 @@
         <v>29</v>
       </c>
       <c r="B209">
-        <v>20210711</v>
+        <v>20200711</v>
       </c>
       <c r="C209">
         <f t="shared" ca="1" si="3"/>
@@ -7151,7 +7147,7 @@
         <v>30</v>
       </c>
       <c r="B210">
-        <v>20210718</v>
+        <v>20200718</v>
       </c>
       <c r="C210">
         <f t="shared" ca="1" si="3"/>
@@ -7163,7 +7159,7 @@
         <v>31</v>
       </c>
       <c r="B211">
-        <v>20210725</v>
+        <v>20200725</v>
       </c>
       <c r="C211">
         <f t="shared" ca="1" si="3"/>
@@ -7175,7 +7171,7 @@
         <v>32</v>
       </c>
       <c r="B212">
-        <v>20210801</v>
+        <v>20200801</v>
       </c>
       <c r="C212">
         <f t="shared" ca="1" si="3"/>
@@ -7187,7 +7183,7 @@
         <v>33</v>
       </c>
       <c r="B213">
-        <v>20210808</v>
+        <v>20200808</v>
       </c>
       <c r="C213">
         <f t="shared" ca="1" si="3"/>
@@ -7199,7 +7195,7 @@
         <v>34</v>
       </c>
       <c r="B214">
-        <v>20210815</v>
+        <v>20200815</v>
       </c>
       <c r="C214">
         <f t="shared" ca="1" si="3"/>
@@ -7211,7 +7207,7 @@
         <v>35</v>
       </c>
       <c r="B215">
-        <v>20210822</v>
+        <v>20200822</v>
       </c>
       <c r="C215">
         <f t="shared" ca="1" si="3"/>
@@ -7223,7 +7219,7 @@
         <v>36</v>
       </c>
       <c r="B216">
-        <v>20210829</v>
+        <v>20200829</v>
       </c>
       <c r="C216">
         <f t="shared" ca="1" si="3"/>
@@ -7235,7 +7231,7 @@
         <v>36</v>
       </c>
       <c r="B217">
-        <v>20210898</v>
+        <v>20200898</v>
       </c>
       <c r="C217">
         <f t="shared" ca="1" si="3"/>
@@ -7247,7 +7243,7 @@
         <v>37</v>
       </c>
       <c r="B218">
-        <v>20210905</v>
+        <v>20200905</v>
       </c>
       <c r="C218">
         <f t="shared" ca="1" si="3"/>
@@ -7259,7 +7255,7 @@
         <v>38</v>
       </c>
       <c r="B219">
-        <v>20210912</v>
+        <v>20200912</v>
       </c>
       <c r="C219">
         <f t="shared" ca="1" si="3"/>
@@ -7271,7 +7267,7 @@
         <v>39</v>
       </c>
       <c r="B220">
-        <v>20210919</v>
+        <v>20200919</v>
       </c>
       <c r="C220">
         <f t="shared" ca="1" si="3"/>
@@ -7283,7 +7279,7 @@
         <v>40</v>
       </c>
       <c r="B221">
-        <v>20210926</v>
+        <v>20200926</v>
       </c>
       <c r="C221">
         <f t="shared" ca="1" si="3"/>
@@ -7295,7 +7291,7 @@
         <v>40</v>
       </c>
       <c r="B222">
-        <v>20210996</v>
+        <v>20200996</v>
       </c>
       <c r="C222">
         <f t="shared" ca="1" si="3"/>
@@ -7307,7 +7303,7 @@
         <v>41</v>
       </c>
       <c r="B223">
-        <v>20211003</v>
+        <v>20201003</v>
       </c>
       <c r="C223">
         <f t="shared" ca="1" si="3"/>
@@ -7319,7 +7315,7 @@
         <v>42</v>
       </c>
       <c r="B224">
-        <v>20211010</v>
+        <v>20201010</v>
       </c>
       <c r="C224">
         <f t="shared" ca="1" si="3"/>
@@ -7331,7 +7327,7 @@
         <v>43</v>
       </c>
       <c r="B225">
-        <v>20211017</v>
+        <v>20201017</v>
       </c>
       <c r="C225">
         <f t="shared" ca="1" si="3"/>
@@ -7343,7 +7339,7 @@
         <v>44</v>
       </c>
       <c r="B226">
-        <v>20211024</v>
+        <v>20201024</v>
       </c>
       <c r="C226">
         <f t="shared" ca="1" si="3"/>
@@ -7355,7 +7351,7 @@
         <v>45</v>
       </c>
       <c r="B227">
-        <v>20211100</v>
+        <v>20201100</v>
       </c>
       <c r="C227">
         <f t="shared" ca="1" si="3"/>
@@ -7367,7 +7363,7 @@
         <v>46</v>
       </c>
       <c r="B228">
-        <v>20211107</v>
+        <v>20201107</v>
       </c>
       <c r="C228">
         <f t="shared" ca="1" si="3"/>
@@ -7379,7 +7375,7 @@
         <v>47</v>
       </c>
       <c r="B229">
-        <v>20211114</v>
+        <v>20201114</v>
       </c>
       <c r="C229">
         <f t="shared" ca="1" si="3"/>
@@ -7391,7 +7387,7 @@
         <v>48</v>
       </c>
       <c r="B230">
-        <v>20211121</v>
+        <v>20201121</v>
       </c>
       <c r="C230">
         <f t="shared" ca="1" si="3"/>
@@ -7403,7 +7399,7 @@
         <v>49</v>
       </c>
       <c r="B231">
-        <v>20211128</v>
+        <v>20201128</v>
       </c>
       <c r="C231">
         <f t="shared" ca="1" si="3"/>
@@ -7415,7 +7411,7 @@
         <v>49</v>
       </c>
       <c r="B232">
-        <v>20211198</v>
+        <v>20201198</v>
       </c>
       <c r="C232">
         <f t="shared" ca="1" si="3"/>
@@ -7427,7 +7423,7 @@
         <v>50</v>
       </c>
       <c r="B233">
-        <v>20211205</v>
+        <v>20201205</v>
       </c>
       <c r="C233">
         <f t="shared" ca="1" si="3"/>
@@ -7439,7 +7435,7 @@
         <v>51</v>
       </c>
       <c r="B234">
-        <v>20211212</v>
+        <v>20201212</v>
       </c>
       <c r="C234">
         <f t="shared" ca="1" si="3"/>
@@ -7451,7 +7447,7 @@
         <v>52</v>
       </c>
       <c r="B235">
-        <v>20211219</v>
+        <v>20201219</v>
       </c>
       <c r="C235">
         <f t="shared" ca="1" si="3"/>
@@ -7463,7 +7459,7 @@
         <v>53</v>
       </c>
       <c r="B236">
-        <v>20211226</v>
+        <v>20201226</v>
       </c>
       <c r="C236">
         <f t="shared" ca="1" si="3"/>
@@ -7475,7 +7471,7 @@
         <v>2</v>
       </c>
       <c r="B237">
-        <v>20220102</v>
+        <v>20210102</v>
       </c>
       <c r="C237">
         <f t="shared" ca="1" si="3"/>
@@ -7487,7 +7483,7 @@
         <v>3</v>
       </c>
       <c r="B238">
-        <v>20220109</v>
+        <v>20210109</v>
       </c>
       <c r="C238">
         <f t="shared" ca="1" si="3"/>
@@ -7499,7 +7495,7 @@
         <v>4</v>
       </c>
       <c r="B239">
-        <v>20220116</v>
+        <v>20210116</v>
       </c>
       <c r="C239">
         <f t="shared" ca="1" si="3"/>
@@ -7511,7 +7507,7 @@
         <v>5</v>
       </c>
       <c r="B240">
-        <v>20220123</v>
+        <v>20210123</v>
       </c>
       <c r="C240">
         <f t="shared" ca="1" si="3"/>
@@ -7523,7 +7519,7 @@
         <v>6</v>
       </c>
       <c r="B241">
-        <v>20220130</v>
+        <v>20210130</v>
       </c>
       <c r="C241">
         <f t="shared" ca="1" si="3"/>
@@ -7535,7 +7531,7 @@
         <v>6</v>
       </c>
       <c r="B242">
-        <v>20220199</v>
+        <v>20210199</v>
       </c>
       <c r="C242">
         <f t="shared" ca="1" si="3"/>
@@ -7547,7 +7543,7 @@
         <v>7</v>
       </c>
       <c r="B243">
-        <v>20220206</v>
+        <v>20210206</v>
       </c>
       <c r="C243">
         <f t="shared" ca="1" si="3"/>
@@ -7559,7 +7555,7 @@
         <v>8</v>
       </c>
       <c r="B244">
-        <v>20220213</v>
+        <v>20210213</v>
       </c>
       <c r="C244">
         <f t="shared" ca="1" si="3"/>
@@ -7571,7 +7567,7 @@
         <v>9</v>
       </c>
       <c r="B245">
-        <v>20220220</v>
+        <v>20210220</v>
       </c>
       <c r="C245">
         <f t="shared" ca="1" si="3"/>
@@ -7583,7 +7579,7 @@
         <v>10</v>
       </c>
       <c r="B246">
-        <v>20220227</v>
+        <v>20210227</v>
       </c>
       <c r="C246">
         <f t="shared" ca="1" si="3"/>
@@ -7595,7 +7591,7 @@
         <v>10</v>
       </c>
       <c r="B247">
-        <v>20220299</v>
+        <v>20210299</v>
       </c>
       <c r="C247">
         <f t="shared" ca="1" si="3"/>
@@ -7607,7 +7603,7 @@
         <v>11</v>
       </c>
       <c r="B248">
-        <v>20220306</v>
+        <v>20210306</v>
       </c>
       <c r="C248">
         <f t="shared" ca="1" si="3"/>
@@ -7619,7 +7615,7 @@
         <v>12</v>
       </c>
       <c r="B249">
-        <v>20220313</v>
+        <v>20210313</v>
       </c>
       <c r="C249">
         <f t="shared" ca="1" si="3"/>
@@ -7631,7 +7627,7 @@
         <v>13</v>
       </c>
       <c r="B250">
-        <v>20220320</v>
+        <v>20210320</v>
       </c>
       <c r="C250">
         <f t="shared" ca="1" si="3"/>
@@ -7643,7 +7639,7 @@
         <v>14</v>
       </c>
       <c r="B251">
-        <v>20220327</v>
+        <v>20210327</v>
       </c>
       <c r="C251">
         <f t="shared" ca="1" si="3"/>
@@ -7655,7 +7651,7 @@
         <v>14</v>
       </c>
       <c r="B252">
-        <v>20220396</v>
+        <v>20210396</v>
       </c>
       <c r="C252">
         <f t="shared" ca="1" si="3"/>
@@ -7667,7 +7663,7 @@
         <v>15</v>
       </c>
       <c r="B253">
-        <v>20220403</v>
+        <v>20210403</v>
       </c>
       <c r="C253">
         <f t="shared" ca="1" si="3"/>
@@ -7679,7 +7675,7 @@
         <v>16</v>
       </c>
       <c r="B254">
-        <v>20220410</v>
+        <v>20210410</v>
       </c>
       <c r="C254">
         <f t="shared" ca="1" si="3"/>
@@ -7691,7 +7687,7 @@
         <v>17</v>
       </c>
       <c r="B255">
-        <v>20220417</v>
+        <v>20210417</v>
       </c>
       <c r="C255">
         <f t="shared" ca="1" si="3"/>
@@ -7703,7 +7699,7 @@
         <v>18</v>
       </c>
       <c r="B256">
-        <v>20220424</v>
+        <v>20210424</v>
       </c>
       <c r="C256">
         <f t="shared" ca="1" si="3"/>
@@ -7715,7 +7711,7 @@
         <v>19</v>
       </c>
       <c r="B257">
-        <v>20220501</v>
+        <v>20210501</v>
       </c>
       <c r="C257">
         <f t="shared" ca="1" si="3"/>
@@ -7727,7 +7723,7 @@
         <v>20</v>
       </c>
       <c r="B258">
-        <v>20220508</v>
+        <v>20210508</v>
       </c>
       <c r="C258">
         <f t="shared" ca="1" si="3"/>
@@ -7739,10 +7735,10 @@
         <v>21</v>
       </c>
       <c r="B259">
-        <v>20220515</v>
+        <v>20210515</v>
       </c>
       <c r="C259">
-        <f t="shared" ref="C259:D322" ca="1" si="4">(B259/$C$2)*100</f>
+        <f t="shared" ref="C259:C322" ca="1" si="4">(B259/$C$2)*100</f>
         <v>744.54365079365084</v>
       </c>
     </row>
@@ -7751,7 +7747,7 @@
         <v>22</v>
       </c>
       <c r="B260">
-        <v>20220522</v>
+        <v>20210522</v>
       </c>
       <c r="C260">
         <f t="shared" ca="1" si="4"/>
@@ -7763,7 +7759,7 @@
         <v>23</v>
       </c>
       <c r="B261">
-        <v>20220529</v>
+        <v>20210529</v>
       </c>
       <c r="C261">
         <f t="shared" ca="1" si="4"/>
@@ -7775,7 +7771,7 @@
         <v>23</v>
       </c>
       <c r="B262">
-        <v>20220598</v>
+        <v>20210598</v>
       </c>
       <c r="C262">
         <f t="shared" ca="1" si="4"/>
@@ -7787,7 +7783,7 @@
         <v>24</v>
       </c>
       <c r="B263">
-        <v>20220605</v>
+        <v>20210605</v>
       </c>
       <c r="C263">
         <f t="shared" ca="1" si="4"/>
@@ -7799,7 +7795,7 @@
         <v>25</v>
       </c>
       <c r="B264">
-        <v>20220612</v>
+        <v>20210612</v>
       </c>
       <c r="C264">
         <f t="shared" ca="1" si="4"/>
@@ -7811,7 +7807,7 @@
         <v>26</v>
       </c>
       <c r="B265">
-        <v>20220619</v>
+        <v>20210619</v>
       </c>
       <c r="C265">
         <f t="shared" ca="1" si="4"/>
@@ -7823,7 +7819,7 @@
         <v>27</v>
       </c>
       <c r="B266">
-        <v>20220626</v>
+        <v>20210626</v>
       </c>
       <c r="C266">
         <f t="shared" ca="1" si="4"/>
@@ -7835,7 +7831,7 @@
         <v>27</v>
       </c>
       <c r="B267">
-        <v>20220696</v>
+        <v>20210696</v>
       </c>
       <c r="C267">
         <f t="shared" ca="1" si="4"/>
@@ -7847,7 +7843,7 @@
         <v>28</v>
       </c>
       <c r="B268">
-        <v>20220703</v>
+        <v>20210703</v>
       </c>
       <c r="C268">
         <f t="shared" ca="1" si="4"/>
@@ -7859,7 +7855,7 @@
         <v>29</v>
       </c>
       <c r="B269">
-        <v>20220710</v>
+        <v>20210710</v>
       </c>
       <c r="C269">
         <f t="shared" ca="1" si="4"/>
@@ -7871,7 +7867,7 @@
         <v>30</v>
       </c>
       <c r="B270">
-        <v>20220717</v>
+        <v>20210717</v>
       </c>
       <c r="C270">
         <f t="shared" ca="1" si="4"/>
@@ -7883,7 +7879,7 @@
         <v>31</v>
       </c>
       <c r="B271">
-        <v>20220724</v>
+        <v>20210724</v>
       </c>
       <c r="C271">
         <f t="shared" ca="1" si="4"/>
@@ -7895,7 +7891,7 @@
         <v>32</v>
       </c>
       <c r="B272">
-        <v>20220800</v>
+        <v>20210800</v>
       </c>
       <c r="C272">
         <f t="shared" ca="1" si="4"/>
@@ -7907,7 +7903,7 @@
         <v>33</v>
       </c>
       <c r="B273">
-        <v>20220807</v>
+        <v>20210807</v>
       </c>
       <c r="C273">
         <f t="shared" ca="1" si="4"/>
@@ -7919,7 +7915,7 @@
         <v>34</v>
       </c>
       <c r="B274">
-        <v>20220814</v>
+        <v>20210814</v>
       </c>
       <c r="C274">
         <f t="shared" ca="1" si="4"/>
@@ -7931,7 +7927,7 @@
         <v>35</v>
       </c>
       <c r="B275">
-        <v>20220821</v>
+        <v>20210821</v>
       </c>
       <c r="C275">
         <f t="shared" ca="1" si="4"/>
@@ -7943,7 +7939,7 @@
         <v>36</v>
       </c>
       <c r="B276">
-        <v>20220828</v>
+        <v>20210828</v>
       </c>
       <c r="C276">
         <f t="shared" ca="1" si="4"/>
@@ -7955,7 +7951,7 @@
         <v>36</v>
       </c>
       <c r="B277">
-        <v>20220897</v>
+        <v>20210897</v>
       </c>
       <c r="C277">
         <f t="shared" ca="1" si="4"/>
@@ -7967,7 +7963,7 @@
         <v>37</v>
       </c>
       <c r="B278">
-        <v>20220904</v>
+        <v>20210904</v>
       </c>
       <c r="C278">
         <f t="shared" ca="1" si="4"/>
@@ -7979,7 +7975,7 @@
         <v>38</v>
       </c>
       <c r="B279">
-        <v>20220911</v>
+        <v>20210911</v>
       </c>
       <c r="C279">
         <f t="shared" ca="1" si="4"/>
@@ -7991,7 +7987,7 @@
         <v>39</v>
       </c>
       <c r="B280">
-        <v>20220918</v>
+        <v>20210918</v>
       </c>
       <c r="C280">
         <f t="shared" ca="1" si="4"/>
@@ -8003,7 +7999,7 @@
         <v>40</v>
       </c>
       <c r="B281">
-        <v>20220925</v>
+        <v>20210925</v>
       </c>
       <c r="C281">
         <f t="shared" ca="1" si="4"/>
@@ -8015,7 +8011,7 @@
         <v>41</v>
       </c>
       <c r="B282">
-        <v>20221002</v>
+        <v>20211002</v>
       </c>
       <c r="C282">
         <f t="shared" ca="1" si="4"/>
@@ -8027,7 +8023,7 @@
         <v>42</v>
       </c>
       <c r="B283">
-        <v>20221009</v>
+        <v>20211009</v>
       </c>
       <c r="C283">
         <f t="shared" ca="1" si="4"/>
@@ -8039,7 +8035,7 @@
         <v>43</v>
       </c>
       <c r="B284">
-        <v>20221016</v>
+        <v>20211016</v>
       </c>
       <c r="C284">
         <f t="shared" ca="1" si="4"/>
@@ -8051,7 +8047,7 @@
         <v>44</v>
       </c>
       <c r="B285">
-        <v>20221023</v>
+        <v>20211023</v>
       </c>
       <c r="C285">
         <f t="shared" ca="1" si="4"/>
@@ -8063,7 +8059,7 @@
         <v>45</v>
       </c>
       <c r="B286">
-        <v>20221030</v>
+        <v>20211030</v>
       </c>
       <c r="C286">
         <f t="shared" ca="1" si="4"/>
@@ -8075,7 +8071,7 @@
         <v>45</v>
       </c>
       <c r="B287">
-        <v>20221099</v>
+        <v>20211099</v>
       </c>
       <c r="C287">
         <f t="shared" ca="1" si="4"/>
@@ -8087,7 +8083,7 @@
         <v>46</v>
       </c>
       <c r="B288">
-        <v>20221106</v>
+        <v>20211106</v>
       </c>
       <c r="C288">
         <f t="shared" ca="1" si="4"/>
@@ -8099,7 +8095,7 @@
         <v>47</v>
       </c>
       <c r="B289">
-        <v>20221113</v>
+        <v>20211113</v>
       </c>
       <c r="C289">
         <f t="shared" ca="1" si="4"/>
@@ -8111,7 +8107,7 @@
         <v>48</v>
       </c>
       <c r="B290">
-        <v>20221120</v>
+        <v>20211120</v>
       </c>
       <c r="C290">
         <f t="shared" ca="1" si="4"/>
@@ -8123,7 +8119,7 @@
         <v>49</v>
       </c>
       <c r="B291">
-        <v>20221127</v>
+        <v>20211127</v>
       </c>
       <c r="C291">
         <f t="shared" ca="1" si="4"/>
@@ -8135,7 +8131,7 @@
         <v>49</v>
       </c>
       <c r="B292">
-        <v>20221197</v>
+        <v>20211197</v>
       </c>
       <c r="C292">
         <f t="shared" ca="1" si="4"/>
@@ -8147,7 +8143,7 @@
         <v>50</v>
       </c>
       <c r="B293">
-        <v>20221204</v>
+        <v>20211204</v>
       </c>
       <c r="C293">
         <f t="shared" ca="1" si="4"/>
@@ -8159,7 +8155,7 @@
         <v>51</v>
       </c>
       <c r="B294">
-        <v>20221211</v>
+        <v>20211211</v>
       </c>
       <c r="C294">
         <f t="shared" ca="1" si="4"/>
@@ -8171,7 +8167,7 @@
         <v>52</v>
       </c>
       <c r="B295">
-        <v>20221218</v>
+        <v>20211218</v>
       </c>
       <c r="C295">
         <f t="shared" ca="1" si="4"/>
@@ -8183,7 +8179,7 @@
         <v>53</v>
       </c>
       <c r="B296">
-        <v>20221225</v>
+        <v>20211225</v>
       </c>
       <c r="C296">
         <f t="shared" ca="1" si="4"/>
@@ -8195,7 +8191,7 @@
         <v>1</v>
       </c>
       <c r="B297">
-        <v>20230101</v>
+        <v>20220101</v>
       </c>
       <c r="C297">
         <f t="shared" ca="1" si="4"/>
@@ -8207,7 +8203,7 @@
         <v>2</v>
       </c>
       <c r="B298">
-        <v>20230108</v>
+        <v>20220108</v>
       </c>
       <c r="C298">
         <f t="shared" ca="1" si="4"/>
@@ -8219,7 +8215,7 @@
         <v>3</v>
       </c>
       <c r="B299">
-        <v>20230115</v>
+        <v>20220115</v>
       </c>
       <c r="C299">
         <f t="shared" ca="1" si="4"/>
@@ -8231,7 +8227,7 @@
         <v>4</v>
       </c>
       <c r="B300">
-        <v>20230122</v>
+        <v>20220122</v>
       </c>
       <c r="C300">
         <f t="shared" ca="1" si="4"/>
@@ -8243,7 +8239,7 @@
         <v>5</v>
       </c>
       <c r="B301">
-        <v>20230129</v>
+        <v>20220129</v>
       </c>
       <c r="C301">
         <f t="shared" ca="1" si="4"/>
@@ -8255,7 +8251,7 @@
         <v>5</v>
       </c>
       <c r="B302">
-        <v>20230198</v>
+        <v>20220198</v>
       </c>
       <c r="C302">
         <f t="shared" ca="1" si="4"/>
@@ -8267,7 +8263,7 @@
         <v>6</v>
       </c>
       <c r="B303">
-        <v>20230205</v>
+        <v>20220205</v>
       </c>
       <c r="C303">
         <f t="shared" ca="1" si="4"/>
@@ -8279,7 +8275,7 @@
         <v>7</v>
       </c>
       <c r="B304">
-        <v>20230212</v>
+        <v>20220212</v>
       </c>
       <c r="C304">
         <f t="shared" ca="1" si="4"/>
@@ -8291,7 +8287,7 @@
         <v>8</v>
       </c>
       <c r="B305">
-        <v>20230219</v>
+        <v>20220219</v>
       </c>
       <c r="C305">
         <f t="shared" ca="1" si="4"/>
@@ -8303,7 +8299,7 @@
         <v>9</v>
       </c>
       <c r="B306">
-        <v>20230226</v>
+        <v>20220226</v>
       </c>
       <c r="C306">
         <f t="shared" ca="1" si="4"/>
@@ -8315,7 +8311,7 @@
         <v>9</v>
       </c>
       <c r="B307">
-        <v>20230298</v>
+        <v>20220298</v>
       </c>
       <c r="C307">
         <f t="shared" ca="1" si="4"/>
@@ -8327,7 +8323,7 @@
         <v>10</v>
       </c>
       <c r="B308">
-        <v>20230305</v>
+        <v>20220305</v>
       </c>
       <c r="C308">
         <f t="shared" ca="1" si="4"/>
@@ -8339,7 +8335,7 @@
         <v>11</v>
       </c>
       <c r="B309">
-        <v>20230312</v>
+        <v>20220312</v>
       </c>
       <c r="C309">
         <f t="shared" ca="1" si="4"/>
@@ -8351,7 +8347,7 @@
         <v>12</v>
       </c>
       <c r="B310">
-        <v>20230319</v>
+        <v>20220319</v>
       </c>
       <c r="C310">
         <f t="shared" ca="1" si="4"/>
@@ -8363,7 +8359,7 @@
         <v>13</v>
       </c>
       <c r="B311">
-        <v>20230326</v>
+        <v>20220326</v>
       </c>
       <c r="C311">
         <f t="shared" ca="1" si="4"/>
@@ -8375,7 +8371,7 @@
         <v>13</v>
       </c>
       <c r="B312">
-        <v>20230395</v>
+        <v>20220395</v>
       </c>
       <c r="C312">
         <f t="shared" ca="1" si="4"/>
@@ -8387,7 +8383,7 @@
         <v>14</v>
       </c>
       <c r="B313">
-        <v>20230402</v>
+        <v>20220402</v>
       </c>
       <c r="C313">
         <f t="shared" ca="1" si="4"/>
@@ -8399,7 +8395,7 @@
         <v>15</v>
       </c>
       <c r="B314">
-        <v>20230409</v>
+        <v>20220409</v>
       </c>
       <c r="C314">
         <f t="shared" ca="1" si="4"/>
@@ -8411,7 +8407,7 @@
         <v>16</v>
       </c>
       <c r="B315">
-        <v>20230416</v>
+        <v>20220416</v>
       </c>
       <c r="C315">
         <f t="shared" ca="1" si="4"/>
@@ -8423,7 +8419,7 @@
         <v>17</v>
       </c>
       <c r="B316">
-        <v>20230423</v>
+        <v>20220423</v>
       </c>
       <c r="C316">
         <f t="shared" ca="1" si="4"/>
@@ -8435,7 +8431,7 @@
         <v>18</v>
       </c>
       <c r="B317">
-        <v>20230500</v>
+        <v>20220500</v>
       </c>
       <c r="C317">
         <f t="shared" ca="1" si="4"/>
@@ -8447,7 +8443,7 @@
         <v>19</v>
       </c>
       <c r="B318">
-        <v>20230507</v>
+        <v>20220507</v>
       </c>
       <c r="C318">
         <f t="shared" ca="1" si="4"/>
@@ -8459,7 +8455,7 @@
         <v>20</v>
       </c>
       <c r="B319">
-        <v>20230514</v>
+        <v>20220514</v>
       </c>
       <c r="C319">
         <f t="shared" ca="1" si="4"/>
@@ -8471,7 +8467,7 @@
         <v>21</v>
       </c>
       <c r="B320">
-        <v>20230521</v>
+        <v>20220521</v>
       </c>
       <c r="C320">
         <f t="shared" ca="1" si="4"/>
@@ -8483,7 +8479,7 @@
         <v>22</v>
       </c>
       <c r="B321">
-        <v>20230528</v>
+        <v>20220528</v>
       </c>
       <c r="C321">
         <f t="shared" ca="1" si="4"/>
@@ -8495,7 +8491,7 @@
         <v>22</v>
       </c>
       <c r="B322">
-        <v>20230597</v>
+        <v>20220597</v>
       </c>
       <c r="C322">
         <f t="shared" ca="1" si="4"/>
@@ -8507,10 +8503,10 @@
         <v>23</v>
       </c>
       <c r="B323">
-        <v>20230604</v>
+        <v>20220604</v>
       </c>
       <c r="C323">
-        <f t="shared" ref="C323:D341" ca="1" si="5">(B323/$C$2)*100</f>
+        <f t="shared" ref="C323:C341" ca="1" si="5">(B323/$C$2)*100</f>
         <v>342.73809523809524</v>
       </c>
     </row>
@@ -8519,7 +8515,7 @@
         <v>24</v>
       </c>
       <c r="B324">
-        <v>20230611</v>
+        <v>20220611</v>
       </c>
       <c r="C324">
         <f t="shared" ca="1" si="5"/>
@@ -8531,7 +8527,7 @@
         <v>25</v>
       </c>
       <c r="B325">
-        <v>20230618</v>
+        <v>20220618</v>
       </c>
       <c r="C325">
         <f t="shared" ca="1" si="5"/>
@@ -8543,7 +8539,7 @@
         <v>26</v>
       </c>
       <c r="B326">
-        <v>20230625</v>
+        <v>20220625</v>
       </c>
       <c r="C326">
         <f t="shared" ca="1" si="5"/>
@@ -8555,7 +8551,7 @@
         <v>27</v>
       </c>
       <c r="B327">
-        <v>20230702</v>
+        <v>20220702</v>
       </c>
       <c r="C327">
         <f t="shared" ca="1" si="5"/>
@@ -8567,7 +8563,7 @@
         <v>28</v>
       </c>
       <c r="B328">
-        <v>20230709</v>
+        <v>20220709</v>
       </c>
       <c r="C328">
         <f t="shared" ca="1" si="5"/>
@@ -8579,7 +8575,7 @@
         <v>29</v>
       </c>
       <c r="B329">
-        <v>20230716</v>
+        <v>20220716</v>
       </c>
       <c r="C329">
         <f t="shared" ca="1" si="5"/>
@@ -8591,7 +8587,7 @@
         <v>30</v>
       </c>
       <c r="B330">
-        <v>20230723</v>
+        <v>20220723</v>
       </c>
       <c r="C330">
         <f t="shared" ca="1" si="5"/>
@@ -8603,7 +8599,7 @@
         <v>31</v>
       </c>
       <c r="B331">
-        <v>20230730</v>
+        <v>20220730</v>
       </c>
       <c r="C331">
         <f t="shared" ca="1" si="5"/>
@@ -8615,7 +8611,7 @@
         <v>31</v>
       </c>
       <c r="B332">
-        <v>20230799</v>
+        <v>20220799</v>
       </c>
       <c r="C332">
         <f t="shared" ca="1" si="5"/>
@@ -8627,7 +8623,7 @@
         <v>32</v>
       </c>
       <c r="B333">
-        <v>20230806</v>
+        <v>20220806</v>
       </c>
       <c r="C333">
         <f t="shared" ca="1" si="5"/>
@@ -8639,7 +8635,7 @@
         <v>33</v>
       </c>
       <c r="B334">
-        <v>20230813</v>
+        <v>20220813</v>
       </c>
       <c r="C334">
         <f t="shared" ca="1" si="5"/>
@@ -8651,7 +8647,7 @@
         <v>34</v>
       </c>
       <c r="B335">
-        <v>20230820</v>
+        <v>20220820</v>
       </c>
       <c r="C335">
         <f t="shared" ca="1" si="5"/>
@@ -8663,7 +8659,7 @@
         <v>35</v>
       </c>
       <c r="B336">
-        <v>20230827</v>
+        <v>20220827</v>
       </c>
       <c r="C336">
         <f t="shared" ca="1" si="5"/>
@@ -8675,7 +8671,7 @@
         <v>35</v>
       </c>
       <c r="B337">
-        <v>20230896</v>
+        <v>20220896</v>
       </c>
       <c r="C337">
         <f t="shared" ca="1" si="5"/>
@@ -8687,7 +8683,7 @@
         <v>36</v>
       </c>
       <c r="B338">
-        <v>20230903</v>
+        <v>20220903</v>
       </c>
       <c r="C338">
         <f t="shared" ca="1" si="5"/>
@@ -8699,7 +8695,7 @@
         <v>37</v>
       </c>
       <c r="B339">
-        <v>20230910</v>
+        <v>20220910</v>
       </c>
       <c r="C339">
         <f t="shared" ca="1" si="5"/>
@@ -8711,7 +8707,7 @@
         <v>38</v>
       </c>
       <c r="B340">
-        <v>20230917</v>
+        <v>20220917</v>
       </c>
       <c r="C340">
         <f t="shared" ca="1" si="5"/>
@@ -8723,7 +8719,7 @@
         <v>39</v>
       </c>
       <c r="B341">
-        <v>20230924</v>
+        <v>20220924</v>
       </c>
       <c r="C341">
         <f t="shared" ca="1" si="5"/>
@@ -8738,7 +8734,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C342"/>
+  <dimension ref="A1:O342"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" customWidth="1"/>
@@ -8763,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>20180100</v>
+        <v>20170100</v>
       </c>
       <c r="C2">
         <f ca="1">(B2/$C$2)*100</f>
@@ -8775,10 +8771,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>20180107</v>
+        <v>20170107</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:D66" ca="1" si="0">(B3/$C$2)*100</f>
+        <f t="shared" ref="C3:C66" ca="1" si="0">(B3/$C$2)*100</f>
         <v>117.16703056768559</v>
       </c>
     </row>
@@ -8787,7 +8783,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>20180114</v>
+        <v>20170114</v>
       </c>
       <c r="C4">
         <f t="shared" ca="1" si="0"/>
@@ -8799,7 +8795,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>20180121</v>
+        <v>20170121</v>
       </c>
       <c r="C5">
         <f t="shared" ca="1" si="0"/>
@@ -8811,7 +8807,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>20180128</v>
+        <v>20170128</v>
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="0"/>
@@ -8823,7 +8819,7 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>20180197</v>
+        <v>20170197</v>
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="0"/>
@@ -8835,7 +8831,7 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>20180204</v>
+        <v>20170204</v>
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="0"/>
@@ -8847,7 +8843,7 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>20180211</v>
+        <v>20170211</v>
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="0"/>
@@ -8859,7 +8855,7 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>20180218</v>
+        <v>20170218</v>
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="0"/>
@@ -8871,7 +8867,7 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>20180225</v>
+        <v>20170225</v>
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="0"/>
@@ -8883,7 +8879,7 @@
         <v>9</v>
       </c>
       <c r="B12">
-        <v>20180297</v>
+        <v>20170297</v>
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="0"/>
@@ -8895,7 +8891,7 @@
         <v>10</v>
       </c>
       <c r="B13">
-        <v>20180304</v>
+        <v>20170304</v>
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="0"/>
@@ -8907,7 +8903,7 @@
         <v>11</v>
       </c>
       <c r="B14">
-        <v>20180311</v>
+        <v>20170311</v>
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="0"/>
@@ -8919,7 +8915,7 @@
         <v>12</v>
       </c>
       <c r="B15">
-        <v>20180318</v>
+        <v>20170318</v>
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="0"/>
@@ -8931,7 +8927,7 @@
         <v>13</v>
       </c>
       <c r="B16">
-        <v>20180325</v>
+        <v>20170325</v>
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="0"/>
@@ -8943,7 +8939,7 @@
         <v>14</v>
       </c>
       <c r="B17">
-        <v>20180401</v>
+        <v>20170401</v>
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="0"/>
@@ -8955,7 +8951,7 @@
         <v>15</v>
       </c>
       <c r="B18">
-        <v>20180408</v>
+        <v>20170408</v>
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="0"/>
@@ -8967,7 +8963,7 @@
         <v>16</v>
       </c>
       <c r="B19">
-        <v>20180415</v>
+        <v>20170415</v>
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="0"/>
@@ -8979,7 +8975,7 @@
         <v>17</v>
       </c>
       <c r="B20">
-        <v>20180422</v>
+        <v>20170422</v>
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="0"/>
@@ -8991,7 +8987,7 @@
         <v>18</v>
       </c>
       <c r="B21">
-        <v>20180429</v>
+        <v>20170429</v>
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="0"/>
@@ -9003,7 +8999,7 @@
         <v>18</v>
       </c>
       <c r="B22">
-        <v>20180499</v>
+        <v>20170499</v>
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="0"/>
@@ -9015,7 +9011,7 @@
         <v>19</v>
       </c>
       <c r="B23">
-        <v>20180506</v>
+        <v>20170506</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="0"/>
@@ -9027,7 +9023,7 @@
         <v>20</v>
       </c>
       <c r="B24">
-        <v>20180513</v>
+        <v>20170513</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="0"/>
@@ -9039,7 +9035,7 @@
         <v>21</v>
       </c>
       <c r="B25">
-        <v>20180520</v>
+        <v>20170520</v>
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="0"/>
@@ -9051,7 +9047,7 @@
         <v>22</v>
       </c>
       <c r="B26">
-        <v>20180527</v>
+        <v>20170527</v>
       </c>
       <c r="C26">
         <f t="shared" ca="1" si="0"/>
@@ -9063,7 +9059,7 @@
         <v>22</v>
       </c>
       <c r="B27">
-        <v>20180596</v>
+        <v>20170596</v>
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="0"/>
@@ -9075,7 +9071,7 @@
         <v>23</v>
       </c>
       <c r="B28">
-        <v>20180603</v>
+        <v>20170603</v>
       </c>
       <c r="C28">
         <f t="shared" ca="1" si="0"/>
@@ -9087,7 +9083,7 @@
         <v>24</v>
       </c>
       <c r="B29">
-        <v>20180610</v>
+        <v>20170610</v>
       </c>
       <c r="C29">
         <f t="shared" ca="1" si="0"/>
@@ -9099,7 +9095,7 @@
         <v>25</v>
       </c>
       <c r="B30">
-        <v>20180617</v>
+        <v>20170617</v>
       </c>
       <c r="C30">
         <f t="shared" ca="1" si="0"/>
@@ -9111,7 +9107,7 @@
         <v>26</v>
       </c>
       <c r="B31">
-        <v>20180624</v>
+        <v>20170624</v>
       </c>
       <c r="C31">
         <f t="shared" ca="1" si="0"/>
@@ -9123,7 +9119,7 @@
         <v>27</v>
       </c>
       <c r="B32">
-        <v>20180701</v>
+        <v>20170701</v>
       </c>
       <c r="C32">
         <f t="shared" ca="1" si="0"/>
@@ -9135,7 +9131,7 @@
         <v>28</v>
       </c>
       <c r="B33">
-        <v>20180708</v>
+        <v>20170708</v>
       </c>
       <c r="C33">
         <f t="shared" ca="1" si="0"/>
@@ -9147,7 +9143,7 @@
         <v>29</v>
       </c>
       <c r="B34">
-        <v>20180715</v>
+        <v>20170715</v>
       </c>
       <c r="C34">
         <f t="shared" ca="1" si="0"/>
@@ -9159,7 +9155,7 @@
         <v>30</v>
       </c>
       <c r="B35">
-        <v>20180722</v>
+        <v>20170722</v>
       </c>
       <c r="C35">
         <f t="shared" ca="1" si="0"/>
@@ -9171,7 +9167,7 @@
         <v>31</v>
       </c>
       <c r="B36">
-        <v>20180729</v>
+        <v>20170729</v>
       </c>
       <c r="C36">
         <f t="shared" ca="1" si="0"/>
@@ -9183,7 +9179,7 @@
         <v>31</v>
       </c>
       <c r="B37">
-        <v>20180798</v>
+        <v>20170798</v>
       </c>
       <c r="C37">
         <f t="shared" ca="1" si="0"/>
@@ -9195,7 +9191,7 @@
         <v>32</v>
       </c>
       <c r="B38">
-        <v>20180805</v>
+        <v>20170805</v>
       </c>
       <c r="C38">
         <f t="shared" ca="1" si="0"/>
@@ -9207,7 +9203,7 @@
         <v>33</v>
       </c>
       <c r="B39">
-        <v>20180812</v>
+        <v>20170812</v>
       </c>
       <c r="C39">
         <f t="shared" ca="1" si="0"/>
@@ -9219,7 +9215,7 @@
         <v>34</v>
       </c>
       <c r="B40">
-        <v>20180819</v>
+        <v>20170819</v>
       </c>
       <c r="C40">
         <f t="shared" ca="1" si="0"/>
@@ -9231,7 +9227,7 @@
         <v>35</v>
       </c>
       <c r="B41">
-        <v>20180826</v>
+        <v>20170826</v>
       </c>
       <c r="C41">
         <f t="shared" ca="1" si="0"/>
@@ -9243,7 +9239,7 @@
         <v>36</v>
       </c>
       <c r="B42">
-        <v>20180902</v>
+        <v>20170902</v>
       </c>
       <c r="C42">
         <f t="shared" ca="1" si="0"/>
@@ -9255,7 +9251,7 @@
         <v>37</v>
       </c>
       <c r="B43">
-        <v>20180909</v>
+        <v>20170909</v>
       </c>
       <c r="C43">
         <f t="shared" ca="1" si="0"/>
@@ -9267,7 +9263,7 @@
         <v>38</v>
       </c>
       <c r="B44">
-        <v>20180916</v>
+        <v>20170916</v>
       </c>
       <c r="C44">
         <f t="shared" ca="1" si="0"/>
@@ -9279,7 +9275,7 @@
         <v>39</v>
       </c>
       <c r="B45">
-        <v>20180923</v>
+        <v>20170923</v>
       </c>
       <c r="C45">
         <f t="shared" ca="1" si="0"/>
@@ -9291,7 +9287,7 @@
         <v>40</v>
       </c>
       <c r="B46">
-        <v>20181001</v>
+        <v>20171001</v>
       </c>
       <c r="C46">
         <f t="shared" ca="1" si="0"/>
@@ -9303,7 +9299,7 @@
         <v>41</v>
       </c>
       <c r="B47">
-        <v>20181007</v>
+        <v>20171007</v>
       </c>
       <c r="C47">
         <f t="shared" ca="1" si="0"/>
@@ -9315,7 +9311,7 @@
         <v>42</v>
       </c>
       <c r="B48">
-        <v>20181014</v>
+        <v>20171014</v>
       </c>
       <c r="C48">
         <f t="shared" ca="1" si="0"/>
@@ -9327,7 +9323,7 @@
         <v>43</v>
       </c>
       <c r="B49">
-        <v>20181021</v>
+        <v>20171021</v>
       </c>
       <c r="C49">
         <f t="shared" ca="1" si="0"/>
@@ -9339,7 +9335,7 @@
         <v>44</v>
       </c>
       <c r="B50">
-        <v>20181028</v>
+        <v>20171028</v>
       </c>
       <c r="C50">
         <f t="shared" ca="1" si="0"/>
@@ -9351,7 +9347,7 @@
         <v>44</v>
       </c>
       <c r="B51">
-        <v>20181097</v>
+        <v>20171097</v>
       </c>
       <c r="C51">
         <f t="shared" ca="1" si="0"/>
@@ -9363,7 +9359,7 @@
         <v>45</v>
       </c>
       <c r="B52">
-        <v>20181104</v>
+        <v>20171104</v>
       </c>
       <c r="C52">
         <f t="shared" ca="1" si="0"/>
@@ -9375,7 +9371,7 @@
         <v>46</v>
       </c>
       <c r="B53">
-        <v>20181111</v>
+        <v>20171111</v>
       </c>
       <c r="C53">
         <f t="shared" ca="1" si="0"/>
@@ -9387,7 +9383,7 @@
         <v>47</v>
       </c>
       <c r="B54">
-        <v>20181118</v>
+        <v>20171118</v>
       </c>
       <c r="C54">
         <f t="shared" ca="1" si="0"/>
@@ -9399,7 +9395,7 @@
         <v>48</v>
       </c>
       <c r="B55">
-        <v>20181125</v>
+        <v>20171125</v>
       </c>
       <c r="C55">
         <f t="shared" ca="1" si="0"/>
@@ -9411,7 +9407,7 @@
         <v>48</v>
       </c>
       <c r="B56">
-        <v>20181195</v>
+        <v>20171195</v>
       </c>
       <c r="C56">
         <f t="shared" ca="1" si="0"/>
@@ -9423,7 +9419,7 @@
         <v>49</v>
       </c>
       <c r="B57">
-        <v>20181202</v>
+        <v>20171202</v>
       </c>
       <c r="C57">
         <f t="shared" ca="1" si="0"/>
@@ -9435,7 +9431,7 @@
         <v>50</v>
       </c>
       <c r="B58">
-        <v>20181209</v>
+        <v>20171209</v>
       </c>
       <c r="C58">
         <f t="shared" ca="1" si="0"/>
@@ -9447,7 +9443,7 @@
         <v>51</v>
       </c>
       <c r="B59">
-        <v>20181216</v>
+        <v>20171216</v>
       </c>
       <c r="C59">
         <f t="shared" ca="1" si="0"/>
@@ -9459,7 +9455,7 @@
         <v>52</v>
       </c>
       <c r="B60">
-        <v>20181223</v>
+        <v>20171223</v>
       </c>
       <c r="C60">
         <f t="shared" ca="1" si="0"/>
@@ -9471,7 +9467,7 @@
         <v>53</v>
       </c>
       <c r="B61">
-        <v>20181230</v>
+        <v>20171230</v>
       </c>
       <c r="C61">
         <f t="shared" ca="1" si="0"/>
@@ -9483,7 +9479,7 @@
         <v>1</v>
       </c>
       <c r="B62">
-        <v>20190101</v>
+        <v>20180101</v>
       </c>
       <c r="C62">
         <f t="shared" ca="1" si="0"/>
@@ -9495,7 +9491,7 @@
         <v>2</v>
       </c>
       <c r="B63">
-        <v>20190106</v>
+        <v>20180106</v>
       </c>
       <c r="C63">
         <f t="shared" ca="1" si="0"/>
@@ -9507,7 +9503,7 @@
         <v>3</v>
       </c>
       <c r="B64">
-        <v>20190113</v>
+        <v>20180113</v>
       </c>
       <c r="C64">
         <f t="shared" ca="1" si="0"/>
@@ -9519,7 +9515,7 @@
         <v>4</v>
       </c>
       <c r="B65">
-        <v>20190120</v>
+        <v>20180120</v>
       </c>
       <c r="C65">
         <f t="shared" ca="1" si="0"/>
@@ -9531,7 +9527,7 @@
         <v>5</v>
       </c>
       <c r="B66">
-        <v>20190127</v>
+        <v>20180127</v>
       </c>
       <c r="C66">
         <f t="shared" ca="1" si="0"/>
@@ -9543,10 +9539,10 @@
         <v>5</v>
       </c>
       <c r="B67">
-        <v>20190196</v>
+        <v>20180196</v>
       </c>
       <c r="C67">
-        <f t="shared" ref="C67:D130" ca="1" si="1">(B67/$C$2)*100</f>
+        <f t="shared" ref="C67:C130" ca="1" si="1">(B67/$C$2)*100</f>
         <v>51.637554585152834</v>
       </c>
     </row>
@@ -9555,7 +9551,7 @@
         <v>6</v>
       </c>
       <c r="B68">
-        <v>20190203</v>
+        <v>20180203</v>
       </c>
       <c r="C68">
         <f t="shared" ca="1" si="1"/>
@@ -9567,7 +9563,7 @@
         <v>7</v>
       </c>
       <c r="B69">
-        <v>20190210</v>
+        <v>20180210</v>
       </c>
       <c r="C69">
         <f t="shared" ca="1" si="1"/>
@@ -9579,7 +9575,7 @@
         <v>8</v>
       </c>
       <c r="B70">
-        <v>20190217</v>
+        <v>20180217</v>
       </c>
       <c r="C70">
         <f t="shared" ca="1" si="1"/>
@@ -9591,7 +9587,7 @@
         <v>9</v>
       </c>
       <c r="B71">
-        <v>20190224</v>
+        <v>20180224</v>
       </c>
       <c r="C71">
         <f t="shared" ca="1" si="1"/>
@@ -9603,7 +9599,7 @@
         <v>9</v>
       </c>
       <c r="B72">
-        <v>20190296</v>
+        <v>20180296</v>
       </c>
       <c r="C72">
         <f t="shared" ca="1" si="1"/>
@@ -9615,7 +9611,7 @@
         <v>10</v>
       </c>
       <c r="B73">
-        <v>20190303</v>
+        <v>20180303</v>
       </c>
       <c r="C73">
         <f t="shared" ca="1" si="1"/>
@@ -9627,7 +9623,7 @@
         <v>11</v>
       </c>
       <c r="B74">
-        <v>20190310</v>
+        <v>20180310</v>
       </c>
       <c r="C74">
         <f t="shared" ca="1" si="1"/>
@@ -9639,7 +9635,7 @@
         <v>12</v>
       </c>
       <c r="B75">
-        <v>20190317</v>
+        <v>20180317</v>
       </c>
       <c r="C75">
         <f t="shared" ca="1" si="1"/>
@@ -9651,7 +9647,7 @@
         <v>13</v>
       </c>
       <c r="B76">
-        <v>20190324</v>
+        <v>20180324</v>
       </c>
       <c r="C76">
         <f t="shared" ca="1" si="1"/>
@@ -9663,7 +9659,7 @@
         <v>14</v>
       </c>
       <c r="B77">
-        <v>20190401</v>
+        <v>20180401</v>
       </c>
       <c r="C77">
         <f t="shared" ca="1" si="1"/>
@@ -9675,7 +9671,7 @@
         <v>15</v>
       </c>
       <c r="B78">
-        <v>20190407</v>
+        <v>20180407</v>
       </c>
       <c r="C78">
         <f t="shared" ca="1" si="1"/>
@@ -9687,7 +9683,7 @@
         <v>16</v>
       </c>
       <c r="B79">
-        <v>20190414</v>
+        <v>20180414</v>
       </c>
       <c r="C79">
         <f t="shared" ca="1" si="1"/>
@@ -9699,7 +9695,7 @@
         <v>17</v>
       </c>
       <c r="B80">
-        <v>20190421</v>
+        <v>20180421</v>
       </c>
       <c r="C80">
         <f t="shared" ca="1" si="1"/>
@@ -9711,7 +9707,7 @@
         <v>18</v>
       </c>
       <c r="B81">
-        <v>20190428</v>
+        <v>20180428</v>
       </c>
       <c r="C81">
         <f t="shared" ca="1" si="1"/>
@@ -9723,7 +9719,7 @@
         <v>18</v>
       </c>
       <c r="B82">
-        <v>20190498</v>
+        <v>20180498</v>
       </c>
       <c r="C82">
         <f t="shared" ca="1" si="1"/>
@@ -9735,7 +9731,7 @@
         <v>19</v>
       </c>
       <c r="B83">
-        <v>20190505</v>
+        <v>20180505</v>
       </c>
       <c r="C83">
         <f t="shared" ca="1" si="1"/>
@@ -9747,7 +9743,7 @@
         <v>20</v>
       </c>
       <c r="B84">
-        <v>20190512</v>
+        <v>20180512</v>
       </c>
       <c r="C84">
         <f t="shared" ca="1" si="1"/>
@@ -9759,7 +9755,7 @@
         <v>21</v>
       </c>
       <c r="B85">
-        <v>20190519</v>
+        <v>20180519</v>
       </c>
       <c r="C85">
         <f t="shared" ca="1" si="1"/>
@@ -9771,7 +9767,7 @@
         <v>22</v>
       </c>
       <c r="B86">
-        <v>20190526</v>
+        <v>20180526</v>
       </c>
       <c r="C86">
         <f t="shared" ca="1" si="1"/>
@@ -9783,7 +9779,7 @@
         <v>23</v>
       </c>
       <c r="B87">
-        <v>20190602</v>
+        <v>20180602</v>
       </c>
       <c r="C87">
         <f t="shared" ca="1" si="1"/>
@@ -9795,7 +9791,7 @@
         <v>24</v>
       </c>
       <c r="B88">
-        <v>20190609</v>
+        <v>20180609</v>
       </c>
       <c r="C88">
         <f t="shared" ca="1" si="1"/>
@@ -9807,7 +9803,7 @@
         <v>25</v>
       </c>
       <c r="B89">
-        <v>20190616</v>
+        <v>20180616</v>
       </c>
       <c r="C89">
         <f t="shared" ca="1" si="1"/>
@@ -9819,7 +9815,7 @@
         <v>26</v>
       </c>
       <c r="B90">
-        <v>20190623</v>
+        <v>20180623</v>
       </c>
       <c r="C90">
         <f t="shared" ca="1" si="1"/>
@@ -9831,7 +9827,7 @@
         <v>27</v>
       </c>
       <c r="B91">
-        <v>20190701</v>
+        <v>20180701</v>
       </c>
       <c r="C91">
         <f t="shared" ca="1" si="1"/>
@@ -9843,7 +9839,7 @@
         <v>28</v>
       </c>
       <c r="B92">
-        <v>20190707</v>
+        <v>20180707</v>
       </c>
       <c r="C92">
         <f t="shared" ca="1" si="1"/>
@@ -9855,7 +9851,7 @@
         <v>29</v>
       </c>
       <c r="B93">
-        <v>20190714</v>
+        <v>20180714</v>
       </c>
       <c r="C93">
         <f t="shared" ca="1" si="1"/>
@@ -9867,7 +9863,7 @@
         <v>30</v>
       </c>
       <c r="B94">
-        <v>20190721</v>
+        <v>20180721</v>
       </c>
       <c r="C94">
         <f t="shared" ca="1" si="1"/>
@@ -9879,7 +9875,7 @@
         <v>31</v>
       </c>
       <c r="B95">
-        <v>20190728</v>
+        <v>20180728</v>
       </c>
       <c r="C95">
         <f t="shared" ca="1" si="1"/>
@@ -9891,7 +9887,7 @@
         <v>31</v>
       </c>
       <c r="B96">
-        <v>20190797</v>
+        <v>20180797</v>
       </c>
       <c r="C96">
         <f t="shared" ca="1" si="1"/>
@@ -9903,7 +9899,7 @@
         <v>32</v>
       </c>
       <c r="B97">
-        <v>20190804</v>
+        <v>20180804</v>
       </c>
       <c r="C97">
         <f t="shared" ca="1" si="1"/>
@@ -9915,7 +9911,7 @@
         <v>33</v>
       </c>
       <c r="B98">
-        <v>20190811</v>
+        <v>20180811</v>
       </c>
       <c r="C98">
         <f t="shared" ca="1" si="1"/>
@@ -9927,7 +9923,7 @@
         <v>34</v>
       </c>
       <c r="B99">
-        <v>20190818</v>
+        <v>20180818</v>
       </c>
       <c r="C99">
         <f t="shared" ca="1" si="1"/>
@@ -9939,7 +9935,7 @@
         <v>35</v>
       </c>
       <c r="B100">
-        <v>20190825</v>
+        <v>20180825</v>
       </c>
       <c r="C100">
         <f t="shared" ca="1" si="1"/>
@@ -9951,7 +9947,7 @@
         <v>36</v>
       </c>
       <c r="B101">
-        <v>20190901</v>
+        <v>20180901</v>
       </c>
       <c r="C101">
         <f t="shared" ca="1" si="1"/>
@@ -9963,7 +9959,7 @@
         <v>37</v>
       </c>
       <c r="B102">
-        <v>20190908</v>
+        <v>20180908</v>
       </c>
       <c r="C102">
         <f t="shared" ca="1" si="1"/>
@@ -9975,7 +9971,7 @@
         <v>38</v>
       </c>
       <c r="B103">
-        <v>20190915</v>
+        <v>20180915</v>
       </c>
       <c r="C103">
         <f t="shared" ca="1" si="1"/>
@@ -9987,7 +9983,7 @@
         <v>39</v>
       </c>
       <c r="B104">
-        <v>20190922</v>
+        <v>20180922</v>
       </c>
       <c r="C104">
         <f t="shared" ca="1" si="1"/>
@@ -9999,7 +9995,7 @@
         <v>40</v>
       </c>
       <c r="B105">
-        <v>20190929</v>
+        <v>20180929</v>
       </c>
       <c r="C105">
         <f t="shared" ca="1" si="1"/>
@@ -10011,7 +10007,7 @@
         <v>40</v>
       </c>
       <c r="B106">
-        <v>20190999</v>
+        <v>20180999</v>
       </c>
       <c r="C106">
         <f t="shared" ca="1" si="1"/>
@@ -10023,7 +10019,7 @@
         <v>41</v>
       </c>
       <c r="B107">
-        <v>20191006</v>
+        <v>20181006</v>
       </c>
       <c r="C107">
         <f t="shared" ca="1" si="1"/>
@@ -10035,7 +10031,7 @@
         <v>42</v>
       </c>
       <c r="B108">
-        <v>20191013</v>
+        <v>20181013</v>
       </c>
       <c r="C108">
         <f t="shared" ca="1" si="1"/>
@@ -10047,7 +10043,7 @@
         <v>43</v>
       </c>
       <c r="B109">
-        <v>20191020</v>
+        <v>20181020</v>
       </c>
       <c r="C109">
         <f t="shared" ca="1" si="1"/>
@@ -10059,7 +10055,7 @@
         <v>44</v>
       </c>
       <c r="B110">
-        <v>20191027</v>
+        <v>20181027</v>
       </c>
       <c r="C110">
         <f t="shared" ca="1" si="1"/>
@@ -10071,7 +10067,7 @@
         <v>44</v>
       </c>
       <c r="B111">
-        <v>20191096</v>
+        <v>20181096</v>
       </c>
       <c r="C111">
         <f t="shared" ca="1" si="1"/>
@@ -10083,7 +10079,7 @@
         <v>45</v>
       </c>
       <c r="B112">
-        <v>20191103</v>
+        <v>20181103</v>
       </c>
       <c r="C112">
         <f t="shared" ca="1" si="1"/>
@@ -10095,7 +10091,7 @@
         <v>46</v>
       </c>
       <c r="B113">
-        <v>20191110</v>
+        <v>20181110</v>
       </c>
       <c r="C113">
         <f t="shared" ca="1" si="1"/>
@@ -10107,7 +10103,7 @@
         <v>47</v>
       </c>
       <c r="B114">
-        <v>20191117</v>
+        <v>20181117</v>
       </c>
       <c r="C114">
         <f t="shared" ca="1" si="1"/>
@@ -10119,7 +10115,7 @@
         <v>48</v>
       </c>
       <c r="B115">
-        <v>20191124</v>
+        <v>20181124</v>
       </c>
       <c r="C115">
         <f t="shared" ca="1" si="1"/>
@@ -10131,7 +10127,7 @@
         <v>49</v>
       </c>
       <c r="B116">
-        <v>20191201</v>
+        <v>20181201</v>
       </c>
       <c r="C116">
         <f t="shared" ca="1" si="1"/>
@@ -10143,7 +10139,7 @@
         <v>50</v>
       </c>
       <c r="B117">
-        <v>20191208</v>
+        <v>20181208</v>
       </c>
       <c r="C117">
         <f t="shared" ca="1" si="1"/>
@@ -10155,7 +10151,7 @@
         <v>51</v>
       </c>
       <c r="B118">
-        <v>20191215</v>
+        <v>20181215</v>
       </c>
       <c r="C118">
         <f t="shared" ca="1" si="1"/>
@@ -10167,7 +10163,7 @@
         <v>52</v>
       </c>
       <c r="B119">
-        <v>20191222</v>
+        <v>20181222</v>
       </c>
       <c r="C119">
         <f t="shared" ca="1" si="1"/>
@@ -10179,7 +10175,7 @@
         <v>53</v>
       </c>
       <c r="B120">
-        <v>20191229</v>
+        <v>20181229</v>
       </c>
       <c r="C120">
         <f t="shared" ca="1" si="1"/>
@@ -10191,7 +10187,7 @@
         <v>1</v>
       </c>
       <c r="B121">
-        <v>20200101</v>
+        <v>20190101</v>
       </c>
       <c r="C121">
         <f t="shared" ca="1" si="1"/>
@@ -10203,7 +10199,7 @@
         <v>2</v>
       </c>
       <c r="B122">
-        <v>20200105</v>
+        <v>20190105</v>
       </c>
       <c r="C122">
         <f t="shared" ca="1" si="1"/>
@@ -10215,7 +10211,7 @@
         <v>3</v>
       </c>
       <c r="B123">
-        <v>20200112</v>
+        <v>20190112</v>
       </c>
       <c r="C123">
         <f t="shared" ca="1" si="1"/>
@@ -10227,7 +10223,7 @@
         <v>4</v>
       </c>
       <c r="B124">
-        <v>20200119</v>
+        <v>20190119</v>
       </c>
       <c r="C124">
         <f t="shared" ca="1" si="1"/>
@@ -10239,7 +10235,7 @@
         <v>5</v>
       </c>
       <c r="B125">
-        <v>20200126</v>
+        <v>20190126</v>
       </c>
       <c r="C125">
         <f t="shared" ca="1" si="1"/>
@@ -10251,7 +10247,7 @@
         <v>6</v>
       </c>
       <c r="B126">
-        <v>20200202</v>
+        <v>20190202</v>
       </c>
       <c r="C126">
         <f t="shared" ca="1" si="1"/>
@@ -10263,7 +10259,7 @@
         <v>7</v>
       </c>
       <c r="B127">
-        <v>20200209</v>
+        <v>20190209</v>
       </c>
       <c r="C127">
         <f t="shared" ca="1" si="1"/>
@@ -10275,7 +10271,7 @@
         <v>8</v>
       </c>
       <c r="B128">
-        <v>20200216</v>
+        <v>20190216</v>
       </c>
       <c r="C128">
         <f t="shared" ca="1" si="1"/>
@@ -10287,7 +10283,7 @@
         <v>9</v>
       </c>
       <c r="B129">
-        <v>20200223</v>
+        <v>20190223</v>
       </c>
       <c r="C129">
         <f t="shared" ca="1" si="1"/>
@@ -10299,7 +10295,7 @@
         <v>10</v>
       </c>
       <c r="B130">
-        <v>20200301</v>
+        <v>20190301</v>
       </c>
       <c r="C130">
         <f t="shared" ca="1" si="1"/>
@@ -10311,10 +10307,10 @@
         <v>11</v>
       </c>
       <c r="B131">
-        <v>20200308</v>
+        <v>20190308</v>
       </c>
       <c r="C131">
-        <f t="shared" ref="C131:D194" ca="1" si="2">(B131/$C$2)*100</f>
+        <f t="shared" ref="C131:C194" ca="1" si="2">(B131/$C$2)*100</f>
         <v>109.07629791363416</v>
       </c>
     </row>
@@ -10323,7 +10319,7 @@
         <v>12</v>
       </c>
       <c r="B132">
-        <v>20200315</v>
+        <v>20190315</v>
       </c>
       <c r="C132">
         <f t="shared" ca="1" si="2"/>
@@ -10335,7 +10331,7 @@
         <v>13</v>
       </c>
       <c r="B133">
-        <v>20200322</v>
+        <v>20190322</v>
       </c>
       <c r="C133">
         <f t="shared" ca="1" si="2"/>
@@ -10347,7 +10343,7 @@
         <v>14</v>
       </c>
       <c r="B134">
-        <v>20200329</v>
+        <v>20190329</v>
       </c>
       <c r="C134">
         <f t="shared" ca="1" si="2"/>
@@ -10359,7 +10355,7 @@
         <v>14</v>
       </c>
       <c r="B135">
-        <v>20200398</v>
+        <v>20190398</v>
       </c>
       <c r="C135">
         <f t="shared" ca="1" si="2"/>
@@ -10371,7 +10367,7 @@
         <v>15</v>
       </c>
       <c r="B136">
-        <v>20200405</v>
+        <v>20190405</v>
       </c>
       <c r="C136">
         <f t="shared" ca="1" si="2"/>
@@ -10383,7 +10379,7 @@
         <v>16</v>
       </c>
       <c r="B137">
-        <v>20200412</v>
+        <v>20190412</v>
       </c>
       <c r="C137">
         <f t="shared" ca="1" si="2"/>
@@ -10395,7 +10391,7 @@
         <v>17</v>
       </c>
       <c r="B138">
-        <v>20200419</v>
+        <v>20190419</v>
       </c>
       <c r="C138">
         <f t="shared" ca="1" si="2"/>
@@ -10407,7 +10403,7 @@
         <v>18</v>
       </c>
       <c r="B139">
-        <v>20200426</v>
+        <v>20190426</v>
       </c>
       <c r="C139">
         <f t="shared" ca="1" si="2"/>
@@ -10419,7 +10415,7 @@
         <v>19</v>
       </c>
       <c r="B140">
-        <v>20200503</v>
+        <v>20190503</v>
       </c>
       <c r="C140">
         <f t="shared" ca="1" si="2"/>
@@ -10431,7 +10427,7 @@
         <v>20</v>
       </c>
       <c r="B141">
-        <v>20200510</v>
+        <v>20190510</v>
       </c>
       <c r="C141">
         <f t="shared" ca="1" si="2"/>
@@ -10443,7 +10439,7 @@
         <v>21</v>
       </c>
       <c r="B142">
-        <v>20200517</v>
+        <v>20190517</v>
       </c>
       <c r="C142">
         <f t="shared" ca="1" si="2"/>
@@ -10455,7 +10451,7 @@
         <v>22</v>
       </c>
       <c r="B143">
-        <v>20200524</v>
+        <v>20190524</v>
       </c>
       <c r="C143">
         <f t="shared" ca="1" si="2"/>
@@ -10467,7 +10463,7 @@
         <v>23</v>
       </c>
       <c r="B144">
-        <v>20200601</v>
+        <v>20190601</v>
       </c>
       <c r="C144">
         <f t="shared" ca="1" si="2"/>
@@ -10479,7 +10475,7 @@
         <v>24</v>
       </c>
       <c r="B145">
-        <v>20200607</v>
+        <v>20190607</v>
       </c>
       <c r="C145">
         <f t="shared" ca="1" si="2"/>
@@ -10491,7 +10487,7 @@
         <v>25</v>
       </c>
       <c r="B146">
-        <v>20200614</v>
+        <v>20190614</v>
       </c>
       <c r="C146">
         <f t="shared" ca="1" si="2"/>
@@ -10503,7 +10499,7 @@
         <v>26</v>
       </c>
       <c r="B147">
-        <v>20200621</v>
+        <v>20190621</v>
       </c>
       <c r="C147">
         <f t="shared" ca="1" si="2"/>
@@ -10515,7 +10511,7 @@
         <v>27</v>
       </c>
       <c r="B148">
-        <v>20200628</v>
+        <v>20190628</v>
       </c>
       <c r="C148">
         <f t="shared" ca="1" si="2"/>
@@ -10527,7 +10523,7 @@
         <v>27</v>
       </c>
       <c r="B149">
-        <v>20200698</v>
+        <v>20190698</v>
       </c>
       <c r="C149">
         <f t="shared" ca="1" si="2"/>
@@ -10539,7 +10535,7 @@
         <v>28</v>
       </c>
       <c r="B150">
-        <v>20200705</v>
+        <v>20190705</v>
       </c>
       <c r="C150">
         <f t="shared" ca="1" si="2"/>
@@ -10551,7 +10547,7 @@
         <v>29</v>
       </c>
       <c r="B151">
-        <v>20200712</v>
+        <v>20190712</v>
       </c>
       <c r="C151">
         <f t="shared" ca="1" si="2"/>
@@ -10563,7 +10559,7 @@
         <v>30</v>
       </c>
       <c r="B152">
-        <v>20200719</v>
+        <v>20190719</v>
       </c>
       <c r="C152">
         <f t="shared" ca="1" si="2"/>
@@ -10575,7 +10571,7 @@
         <v>31</v>
       </c>
       <c r="B153">
-        <v>20200726</v>
+        <v>20190726</v>
       </c>
       <c r="C153">
         <f t="shared" ca="1" si="2"/>
@@ -10587,7 +10583,7 @@
         <v>32</v>
       </c>
       <c r="B154">
-        <v>20200802</v>
+        <v>20190802</v>
       </c>
       <c r="C154">
         <f t="shared" ca="1" si="2"/>
@@ -10599,7 +10595,7 @@
         <v>33</v>
       </c>
       <c r="B155">
-        <v>20200809</v>
+        <v>20190809</v>
       </c>
       <c r="C155">
         <f t="shared" ca="1" si="2"/>
@@ -10611,7 +10607,7 @@
         <v>34</v>
       </c>
       <c r="B156">
-        <v>20200816</v>
+        <v>20190816</v>
       </c>
       <c r="C156">
         <f t="shared" ca="1" si="2"/>
@@ -10623,7 +10619,7 @@
         <v>35</v>
       </c>
       <c r="B157">
-        <v>20200823</v>
+        <v>20190823</v>
       </c>
       <c r="C157">
         <f t="shared" ca="1" si="2"/>
@@ -10635,7 +10631,7 @@
         <v>36</v>
       </c>
       <c r="B158">
-        <v>20200830</v>
+        <v>20190830</v>
       </c>
       <c r="C158">
         <f t="shared" ca="1" si="2"/>
@@ -10647,7 +10643,7 @@
         <v>36</v>
       </c>
       <c r="B159">
-        <v>20200899</v>
+        <v>20190899</v>
       </c>
       <c r="C159">
         <f t="shared" ca="1" si="2"/>
@@ -10659,7 +10655,7 @@
         <v>37</v>
       </c>
       <c r="B160">
-        <v>20200906</v>
+        <v>20190906</v>
       </c>
       <c r="C160">
         <f t="shared" ca="1" si="2"/>
@@ -10671,7 +10667,7 @@
         <v>38</v>
       </c>
       <c r="B161">
-        <v>20200913</v>
+        <v>20190913</v>
       </c>
       <c r="C161">
         <f t="shared" ca="1" si="2"/>
@@ -10683,7 +10679,7 @@
         <v>39</v>
       </c>
       <c r="B162">
-        <v>20200920</v>
+        <v>20190920</v>
       </c>
       <c r="C162">
         <f t="shared" ca="1" si="2"/>
@@ -10695,7 +10691,7 @@
         <v>40</v>
       </c>
       <c r="B163">
-        <v>20200927</v>
+        <v>20190927</v>
       </c>
       <c r="C163">
         <f t="shared" ca="1" si="2"/>
@@ -10707,7 +10703,7 @@
         <v>40</v>
       </c>
       <c r="B164">
-        <v>20200997</v>
+        <v>20190997</v>
       </c>
       <c r="C164">
         <f t="shared" ca="1" si="2"/>
@@ -10719,7 +10715,7 @@
         <v>41</v>
       </c>
       <c r="B165">
-        <v>20201004</v>
+        <v>20191004</v>
       </c>
       <c r="C165">
         <f t="shared" ca="1" si="2"/>
@@ -10731,7 +10727,7 @@
         <v>42</v>
       </c>
       <c r="B166">
-        <v>20201011</v>
+        <v>20191011</v>
       </c>
       <c r="C166">
         <f t="shared" ca="1" si="2"/>
@@ -10743,7 +10739,7 @@
         <v>43</v>
       </c>
       <c r="B167">
-        <v>20201018</v>
+        <v>20191018</v>
       </c>
       <c r="C167">
         <f t="shared" ca="1" si="2"/>
@@ -10755,7 +10751,7 @@
         <v>44</v>
       </c>
       <c r="B168">
-        <v>20201025</v>
+        <v>20191025</v>
       </c>
       <c r="C168">
         <f t="shared" ca="1" si="2"/>
@@ -10767,7 +10763,7 @@
         <v>45</v>
       </c>
       <c r="B169">
-        <v>20201101</v>
+        <v>20191101</v>
       </c>
       <c r="C169">
         <f t="shared" ca="1" si="2"/>
@@ -10779,7 +10775,7 @@
         <v>46</v>
       </c>
       <c r="B170">
-        <v>20201108</v>
+        <v>20191108</v>
       </c>
       <c r="C170">
         <f t="shared" ca="1" si="2"/>
@@ -10791,7 +10787,7 @@
         <v>47</v>
       </c>
       <c r="B171">
-        <v>20201115</v>
+        <v>20191115</v>
       </c>
       <c r="C171">
         <f t="shared" ca="1" si="2"/>
@@ -10803,7 +10799,7 @@
         <v>48</v>
       </c>
       <c r="B172">
-        <v>20201122</v>
+        <v>20191122</v>
       </c>
       <c r="C172">
         <f t="shared" ca="1" si="2"/>
@@ -10815,7 +10811,7 @@
         <v>49</v>
       </c>
       <c r="B173">
-        <v>20201129</v>
+        <v>20191129</v>
       </c>
       <c r="C173">
         <f t="shared" ca="1" si="2"/>
@@ -10827,7 +10823,7 @@
         <v>49</v>
       </c>
       <c r="B174">
-        <v>20201199</v>
+        <v>20191199</v>
       </c>
       <c r="C174">
         <f t="shared" ca="1" si="2"/>
@@ -10839,7 +10835,7 @@
         <v>50</v>
       </c>
       <c r="B175">
-        <v>20201206</v>
+        <v>20191206</v>
       </c>
       <c r="C175">
         <f t="shared" ca="1" si="2"/>
@@ -10851,7 +10847,7 @@
         <v>51</v>
       </c>
       <c r="B176">
-        <v>20201213</v>
+        <v>20191213</v>
       </c>
       <c r="C176">
         <f t="shared" ca="1" si="2"/>
@@ -10863,7 +10859,7 @@
         <v>52</v>
       </c>
       <c r="B177">
-        <v>20201220</v>
+        <v>20191220</v>
       </c>
       <c r="C177">
         <f t="shared" ca="1" si="2"/>
@@ -10875,7 +10871,7 @@
         <v>53</v>
       </c>
       <c r="B178">
-        <v>20201227</v>
+        <v>20191227</v>
       </c>
       <c r="C178">
         <f t="shared" ca="1" si="2"/>
@@ -10887,7 +10883,7 @@
         <v>2</v>
       </c>
       <c r="B179">
-        <v>20210103</v>
+        <v>20200103</v>
       </c>
       <c r="C179">
         <f t="shared" ca="1" si="2"/>
@@ -10899,7 +10895,7 @@
         <v>3</v>
       </c>
       <c r="B180">
-        <v>20210110</v>
+        <v>20200110</v>
       </c>
       <c r="C180">
         <f t="shared" ca="1" si="2"/>
@@ -10911,7 +10907,7 @@
         <v>4</v>
       </c>
       <c r="B181">
-        <v>20210117</v>
+        <v>20200117</v>
       </c>
       <c r="C181">
         <f t="shared" ca="1" si="2"/>
@@ -10923,7 +10919,7 @@
         <v>5</v>
       </c>
       <c r="B182">
-        <v>20210124</v>
+        <v>20200124</v>
       </c>
       <c r="C182">
         <f t="shared" ca="1" si="2"/>
@@ -10935,7 +10931,7 @@
         <v>6</v>
       </c>
       <c r="B183">
-        <v>20210201</v>
+        <v>20200201</v>
       </c>
       <c r="C183">
         <f t="shared" ca="1" si="2"/>
@@ -10947,7 +10943,7 @@
         <v>7</v>
       </c>
       <c r="B184">
-        <v>20210207</v>
+        <v>20200207</v>
       </c>
       <c r="C184">
         <f t="shared" ca="1" si="2"/>
@@ -10959,7 +10955,7 @@
         <v>8</v>
       </c>
       <c r="B185">
-        <v>20210214</v>
+        <v>20200214</v>
       </c>
       <c r="C185">
         <f t="shared" ca="1" si="2"/>
@@ -10971,7 +10967,7 @@
         <v>9</v>
       </c>
       <c r="B186">
-        <v>20210221</v>
+        <v>20200221</v>
       </c>
       <c r="C186">
         <f t="shared" ca="1" si="2"/>
@@ -10983,7 +10979,7 @@
         <v>10</v>
       </c>
       <c r="B187">
-        <v>20210301</v>
+        <v>20200301</v>
       </c>
       <c r="C187">
         <f t="shared" ca="1" si="2"/>
@@ -10995,7 +10991,7 @@
         <v>11</v>
       </c>
       <c r="B188">
-        <v>20210307</v>
+        <v>20200307</v>
       </c>
       <c r="C188">
         <f t="shared" ca="1" si="2"/>
@@ -11007,7 +11003,7 @@
         <v>12</v>
       </c>
       <c r="B189">
-        <v>20210314</v>
+        <v>20200314</v>
       </c>
       <c r="C189">
         <f t="shared" ca="1" si="2"/>
@@ -11019,7 +11015,7 @@
         <v>13</v>
       </c>
       <c r="B190">
-        <v>20210321</v>
+        <v>20200321</v>
       </c>
       <c r="C190">
         <f t="shared" ca="1" si="2"/>
@@ -11031,7 +11027,7 @@
         <v>14</v>
       </c>
       <c r="B191">
-        <v>20210328</v>
+        <v>20200328</v>
       </c>
       <c r="C191">
         <f t="shared" ca="1" si="2"/>
@@ -11043,7 +11039,7 @@
         <v>14</v>
       </c>
       <c r="B192">
-        <v>20210397</v>
+        <v>20200397</v>
       </c>
       <c r="C192">
         <f t="shared" ca="1" si="2"/>
@@ -11055,7 +11051,7 @@
         <v>15</v>
       </c>
       <c r="B193">
-        <v>20210404</v>
+        <v>20200404</v>
       </c>
       <c r="C193">
         <f t="shared" ca="1" si="2"/>
@@ -11067,7 +11063,7 @@
         <v>16</v>
       </c>
       <c r="B194">
-        <v>20210411</v>
+        <v>20200411</v>
       </c>
       <c r="C194">
         <f t="shared" ca="1" si="2"/>
@@ -11079,10 +11075,10 @@
         <v>17</v>
       </c>
       <c r="B195">
-        <v>20210418</v>
+        <v>20200418</v>
       </c>
       <c r="C195">
-        <f t="shared" ref="C195:D258" ca="1" si="3">(B195/$C$2)*100</f>
+        <f t="shared" ref="C195:C258" ca="1" si="3">(B195/$C$2)*100</f>
         <v>123.85371179039302</v>
       </c>
     </row>
@@ -11091,7 +11087,7 @@
         <v>18</v>
       </c>
       <c r="B196">
-        <v>20210425</v>
+        <v>20200425</v>
       </c>
       <c r="C196">
         <f t="shared" ca="1" si="3"/>
@@ -11103,7 +11099,7 @@
         <v>18</v>
       </c>
       <c r="B197">
-        <v>20210495</v>
+        <v>20200495</v>
       </c>
       <c r="C197">
         <f t="shared" ca="1" si="3"/>
@@ -11115,7 +11111,7 @@
         <v>19</v>
       </c>
       <c r="B198">
-        <v>20210502</v>
+        <v>20200502</v>
       </c>
       <c r="C198">
         <f t="shared" ca="1" si="3"/>
@@ -11127,7 +11123,7 @@
         <v>20</v>
       </c>
       <c r="B199">
-        <v>20210509</v>
+        <v>20200509</v>
       </c>
       <c r="C199">
         <f t="shared" ca="1" si="3"/>
@@ -11139,7 +11135,7 @@
         <v>21</v>
       </c>
       <c r="B200">
-        <v>20210516</v>
+        <v>20200516</v>
       </c>
       <c r="C200">
         <f t="shared" ca="1" si="3"/>
@@ -11151,7 +11147,7 @@
         <v>22</v>
       </c>
       <c r="B201">
-        <v>20210523</v>
+        <v>20200523</v>
       </c>
       <c r="C201">
         <f t="shared" ca="1" si="3"/>
@@ -11163,7 +11159,7 @@
         <v>23</v>
       </c>
       <c r="B202">
-        <v>20210530</v>
+        <v>20200530</v>
       </c>
       <c r="C202">
         <f t="shared" ca="1" si="3"/>
@@ -11175,7 +11171,7 @@
         <v>23</v>
       </c>
       <c r="B203">
-        <v>20210599</v>
+        <v>20200599</v>
       </c>
       <c r="C203">
         <f t="shared" ca="1" si="3"/>
@@ -11187,7 +11183,7 @@
         <v>24</v>
       </c>
       <c r="B204">
-        <v>20210606</v>
+        <v>20200606</v>
       </c>
       <c r="C204">
         <f t="shared" ca="1" si="3"/>
@@ -11199,7 +11195,7 @@
         <v>25</v>
       </c>
       <c r="B205">
-        <v>20210613</v>
+        <v>20200613</v>
       </c>
       <c r="C205">
         <f t="shared" ca="1" si="3"/>
@@ -11211,7 +11207,7 @@
         <v>26</v>
       </c>
       <c r="B206">
-        <v>20210620</v>
+        <v>20200620</v>
       </c>
       <c r="C206">
         <f t="shared" ca="1" si="3"/>
@@ -11223,7 +11219,7 @@
         <v>27</v>
       </c>
       <c r="B207">
-        <v>20210627</v>
+        <v>20200627</v>
       </c>
       <c r="C207">
         <f t="shared" ca="1" si="3"/>
@@ -11235,7 +11231,7 @@
         <v>27</v>
       </c>
       <c r="B208">
-        <v>20210697</v>
+        <v>20200697</v>
       </c>
       <c r="C208">
         <f t="shared" ca="1" si="3"/>
@@ -11247,7 +11243,7 @@
         <v>28</v>
       </c>
       <c r="B209">
-        <v>20210704</v>
+        <v>20200704</v>
       </c>
       <c r="C209">
         <f t="shared" ca="1" si="3"/>
@@ -11259,7 +11255,7 @@
         <v>29</v>
       </c>
       <c r="B210">
-        <v>20210711</v>
+        <v>20200711</v>
       </c>
       <c r="C210">
         <f t="shared" ca="1" si="3"/>
@@ -11271,7 +11267,7 @@
         <v>30</v>
       </c>
       <c r="B211">
-        <v>20210718</v>
+        <v>20200718</v>
       </c>
       <c r="C211">
         <f t="shared" ca="1" si="3"/>
@@ -11283,7 +11279,7 @@
         <v>31</v>
       </c>
       <c r="B212">
-        <v>20210725</v>
+        <v>20200725</v>
       </c>
       <c r="C212">
         <f t="shared" ca="1" si="3"/>
@@ -11295,7 +11291,7 @@
         <v>32</v>
       </c>
       <c r="B213">
-        <v>20210801</v>
+        <v>20200801</v>
       </c>
       <c r="C213">
         <f t="shared" ca="1" si="3"/>
@@ -11307,7 +11303,7 @@
         <v>33</v>
       </c>
       <c r="B214">
-        <v>20210808</v>
+        <v>20200808</v>
       </c>
       <c r="C214">
         <f t="shared" ca="1" si="3"/>
@@ -11319,7 +11315,7 @@
         <v>34</v>
       </c>
       <c r="B215">
-        <v>20210815</v>
+        <v>20200815</v>
       </c>
       <c r="C215">
         <f t="shared" ca="1" si="3"/>
@@ -11331,7 +11327,7 @@
         <v>35</v>
       </c>
       <c r="B216">
-        <v>20210822</v>
+        <v>20200822</v>
       </c>
       <c r="C216">
         <f t="shared" ca="1" si="3"/>
@@ -11343,7 +11339,7 @@
         <v>36</v>
       </c>
       <c r="B217">
-        <v>20210829</v>
+        <v>20200829</v>
       </c>
       <c r="C217">
         <f t="shared" ca="1" si="3"/>
@@ -11355,7 +11351,7 @@
         <v>36</v>
       </c>
       <c r="B218">
-        <v>20210898</v>
+        <v>20200898</v>
       </c>
       <c r="C218">
         <f t="shared" ca="1" si="3"/>
@@ -11367,7 +11363,7 @@
         <v>37</v>
       </c>
       <c r="B219">
-        <v>20210905</v>
+        <v>20200905</v>
       </c>
       <c r="C219">
         <f t="shared" ca="1" si="3"/>
@@ -11379,7 +11375,7 @@
         <v>38</v>
       </c>
       <c r="B220">
-        <v>20210912</v>
+        <v>20200912</v>
       </c>
       <c r="C220">
         <f t="shared" ca="1" si="3"/>
@@ -11391,7 +11387,7 @@
         <v>39</v>
       </c>
       <c r="B221">
-        <v>20210919</v>
+        <v>20200919</v>
       </c>
       <c r="C221">
         <f t="shared" ca="1" si="3"/>
@@ -11403,7 +11399,7 @@
         <v>40</v>
       </c>
       <c r="B222">
-        <v>20210926</v>
+        <v>20200926</v>
       </c>
       <c r="C222">
         <f t="shared" ca="1" si="3"/>
@@ -11415,7 +11411,7 @@
         <v>40</v>
       </c>
       <c r="B223">
-        <v>20210996</v>
+        <v>20200996</v>
       </c>
       <c r="C223">
         <f t="shared" ca="1" si="3"/>
@@ -11427,7 +11423,7 @@
         <v>41</v>
       </c>
       <c r="B224">
-        <v>20211003</v>
+        <v>20201003</v>
       </c>
       <c r="C224">
         <f t="shared" ca="1" si="3"/>
@@ -11439,7 +11435,7 @@
         <v>42</v>
       </c>
       <c r="B225">
-        <v>20211010</v>
+        <v>20201010</v>
       </c>
       <c r="C225">
         <f t="shared" ca="1" si="3"/>
@@ -11451,7 +11447,7 @@
         <v>43</v>
       </c>
       <c r="B226">
-        <v>20211017</v>
+        <v>20201017</v>
       </c>
       <c r="C226">
         <f t="shared" ca="1" si="3"/>
@@ -11463,7 +11459,7 @@
         <v>44</v>
       </c>
       <c r="B227">
-        <v>20211024</v>
+        <v>20201024</v>
       </c>
       <c r="C227">
         <f t="shared" ca="1" si="3"/>
@@ -11475,7 +11471,7 @@
         <v>45</v>
       </c>
       <c r="B228">
-        <v>20211101</v>
+        <v>20201101</v>
       </c>
       <c r="C228">
         <f t="shared" ca="1" si="3"/>
@@ -11487,7 +11483,7 @@
         <v>46</v>
       </c>
       <c r="B229">
-        <v>20211107</v>
+        <v>20201107</v>
       </c>
       <c r="C229">
         <f t="shared" ca="1" si="3"/>
@@ -11499,7 +11495,7 @@
         <v>47</v>
       </c>
       <c r="B230">
-        <v>20211114</v>
+        <v>20201114</v>
       </c>
       <c r="C230">
         <f t="shared" ca="1" si="3"/>
@@ -11511,7 +11507,7 @@
         <v>48</v>
       </c>
       <c r="B231">
-        <v>20211121</v>
+        <v>20201121</v>
       </c>
       <c r="C231">
         <f t="shared" ca="1" si="3"/>
@@ -11523,7 +11519,7 @@
         <v>49</v>
       </c>
       <c r="B232">
-        <v>20211128</v>
+        <v>20201128</v>
       </c>
       <c r="C232">
         <f t="shared" ca="1" si="3"/>
@@ -11535,7 +11531,7 @@
         <v>49</v>
       </c>
       <c r="B233">
-        <v>20211198</v>
+        <v>20201198</v>
       </c>
       <c r="C233">
         <f t="shared" ca="1" si="3"/>
@@ -11547,7 +11543,7 @@
         <v>50</v>
       </c>
       <c r="B234">
-        <v>20211205</v>
+        <v>20201205</v>
       </c>
       <c r="C234">
         <f t="shared" ca="1" si="3"/>
@@ -11559,7 +11555,7 @@
         <v>51</v>
       </c>
       <c r="B235">
-        <v>20211212</v>
+        <v>20201212</v>
       </c>
       <c r="C235">
         <f t="shared" ca="1" si="3"/>
@@ -11571,7 +11567,7 @@
         <v>52</v>
       </c>
       <c r="B236">
-        <v>20211219</v>
+        <v>20201219</v>
       </c>
       <c r="C236">
         <f t="shared" ca="1" si="3"/>
@@ -11583,7 +11579,7 @@
         <v>53</v>
       </c>
       <c r="B237">
-        <v>20211226</v>
+        <v>20201226</v>
       </c>
       <c r="C237">
         <f t="shared" ca="1" si="3"/>
@@ -11595,7 +11591,7 @@
         <v>2</v>
       </c>
       <c r="B238">
-        <v>20220102</v>
+        <v>20210102</v>
       </c>
       <c r="C238">
         <f t="shared" ca="1" si="3"/>
@@ -11607,7 +11603,7 @@
         <v>3</v>
       </c>
       <c r="B239">
-        <v>20220109</v>
+        <v>20210109</v>
       </c>
       <c r="C239">
         <f t="shared" ca="1" si="3"/>
@@ -11619,7 +11615,7 @@
         <v>4</v>
       </c>
       <c r="B240">
-        <v>20220116</v>
+        <v>20210116</v>
       </c>
       <c r="C240">
         <f t="shared" ca="1" si="3"/>
@@ -11631,7 +11627,7 @@
         <v>5</v>
       </c>
       <c r="B241">
-        <v>20220123</v>
+        <v>20210123</v>
       </c>
       <c r="C241">
         <f t="shared" ca="1" si="3"/>
@@ -11643,7 +11639,7 @@
         <v>6</v>
       </c>
       <c r="B242">
-        <v>20220130</v>
+        <v>20210130</v>
       </c>
       <c r="C242">
         <f t="shared" ca="1" si="3"/>
@@ -11655,7 +11651,7 @@
         <v>6</v>
       </c>
       <c r="B243">
-        <v>20220199</v>
+        <v>20210199</v>
       </c>
       <c r="C243">
         <f t="shared" ca="1" si="3"/>
@@ -11667,7 +11663,7 @@
         <v>7</v>
       </c>
       <c r="B244">
-        <v>20220206</v>
+        <v>20210206</v>
       </c>
       <c r="C244">
         <f t="shared" ca="1" si="3"/>
@@ -11679,7 +11675,7 @@
         <v>8</v>
       </c>
       <c r="B245">
-        <v>20220213</v>
+        <v>20210213</v>
       </c>
       <c r="C245">
         <f t="shared" ca="1" si="3"/>
@@ -11691,7 +11687,7 @@
         <v>9</v>
       </c>
       <c r="B246">
-        <v>20220220</v>
+        <v>20210220</v>
       </c>
       <c r="C246">
         <f t="shared" ca="1" si="3"/>
@@ -11703,7 +11699,7 @@
         <v>10</v>
       </c>
       <c r="B247">
-        <v>20220227</v>
+        <v>20210227</v>
       </c>
       <c r="C247">
         <f t="shared" ca="1" si="3"/>
@@ -11715,7 +11711,7 @@
         <v>10</v>
       </c>
       <c r="B248">
-        <v>20220299</v>
+        <v>20210299</v>
       </c>
       <c r="C248">
         <f t="shared" ca="1" si="3"/>
@@ -11727,7 +11723,7 @@
         <v>11</v>
       </c>
       <c r="B249">
-        <v>20220306</v>
+        <v>20210306</v>
       </c>
       <c r="C249">
         <f t="shared" ca="1" si="3"/>
@@ -11739,7 +11735,7 @@
         <v>12</v>
       </c>
       <c r="B250">
-        <v>20220313</v>
+        <v>20210313</v>
       </c>
       <c r="C250">
         <f t="shared" ca="1" si="3"/>
@@ -11751,7 +11747,7 @@
         <v>13</v>
       </c>
       <c r="B251">
-        <v>20220320</v>
+        <v>20210320</v>
       </c>
       <c r="C251">
         <f t="shared" ca="1" si="3"/>
@@ -11763,7 +11759,7 @@
         <v>14</v>
       </c>
       <c r="B252">
-        <v>20220327</v>
+        <v>20210327</v>
       </c>
       <c r="C252">
         <f t="shared" ca="1" si="3"/>
@@ -11775,7 +11771,7 @@
         <v>14</v>
       </c>
       <c r="B253">
-        <v>20220396</v>
+        <v>20210396</v>
       </c>
       <c r="C253">
         <f t="shared" ca="1" si="3"/>
@@ -11787,7 +11783,7 @@
         <v>15</v>
       </c>
       <c r="B254">
-        <v>20220403</v>
+        <v>20210403</v>
       </c>
       <c r="C254">
         <f t="shared" ca="1" si="3"/>
@@ -11799,7 +11795,7 @@
         <v>16</v>
       </c>
       <c r="B255">
-        <v>20220410</v>
+        <v>20210410</v>
       </c>
       <c r="C255">
         <f t="shared" ca="1" si="3"/>
@@ -11811,7 +11807,7 @@
         <v>17</v>
       </c>
       <c r="B256">
-        <v>20220417</v>
+        <v>20210417</v>
       </c>
       <c r="C256">
         <f t="shared" ca="1" si="3"/>
@@ -11823,7 +11819,7 @@
         <v>18</v>
       </c>
       <c r="B257">
-        <v>20220424</v>
+        <v>20210424</v>
       </c>
       <c r="C257">
         <f t="shared" ca="1" si="3"/>
@@ -11835,7 +11831,7 @@
         <v>19</v>
       </c>
       <c r="B258">
-        <v>20220501</v>
+        <v>20210501</v>
       </c>
       <c r="C258">
         <f t="shared" ca="1" si="3"/>
@@ -11847,10 +11843,10 @@
         <v>20</v>
       </c>
       <c r="B259">
-        <v>20220508</v>
+        <v>20210508</v>
       </c>
       <c r="C259">
-        <f t="shared" ref="C259:D322" ca="1" si="4">(B259/$C$2)*100</f>
+        <f t="shared" ref="C259:C322" ca="1" si="4">(B259/$C$2)*100</f>
         <v>133.59716157205239</v>
       </c>
     </row>
@@ -11859,7 +11855,7 @@
         <v>21</v>
       </c>
       <c r="B260">
-        <v>20220515</v>
+        <v>20210515</v>
       </c>
       <c r="C260">
         <f t="shared" ca="1" si="4"/>
@@ -11871,7 +11867,7 @@
         <v>22</v>
       </c>
       <c r="B261">
-        <v>20220522</v>
+        <v>20210522</v>
       </c>
       <c r="C261">
         <f t="shared" ca="1" si="4"/>
@@ -11883,7 +11879,7 @@
         <v>23</v>
       </c>
       <c r="B262">
-        <v>20220529</v>
+        <v>20210529</v>
       </c>
       <c r="C262">
         <f t="shared" ca="1" si="4"/>
@@ -11895,7 +11891,7 @@
         <v>23</v>
       </c>
       <c r="B263">
-        <v>20220598</v>
+        <v>20210598</v>
       </c>
       <c r="C263">
         <f t="shared" ca="1" si="4"/>
@@ -11907,7 +11903,7 @@
         <v>24</v>
       </c>
       <c r="B264">
-        <v>20220605</v>
+        <v>20210605</v>
       </c>
       <c r="C264">
         <f t="shared" ca="1" si="4"/>
@@ -11919,7 +11915,7 @@
         <v>25</v>
       </c>
       <c r="B265">
-        <v>20220612</v>
+        <v>20210612</v>
       </c>
       <c r="C265">
         <f t="shared" ca="1" si="4"/>
@@ -11931,7 +11927,7 @@
         <v>26</v>
       </c>
       <c r="B266">
-        <v>20220619</v>
+        <v>20210619</v>
       </c>
       <c r="C266">
         <f t="shared" ca="1" si="4"/>
@@ -11943,7 +11939,7 @@
         <v>27</v>
       </c>
       <c r="B267">
-        <v>20220626</v>
+        <v>20210626</v>
       </c>
       <c r="C267">
         <f t="shared" ca="1" si="4"/>
@@ -11955,7 +11951,7 @@
         <v>27</v>
       </c>
       <c r="B268">
-        <v>20220696</v>
+        <v>20210696</v>
       </c>
       <c r="C268">
         <f t="shared" ca="1" si="4"/>
@@ -11967,7 +11963,7 @@
         <v>28</v>
       </c>
       <c r="B269">
-        <v>20220703</v>
+        <v>20210703</v>
       </c>
       <c r="C269">
         <f t="shared" ca="1" si="4"/>
@@ -11979,7 +11975,7 @@
         <v>29</v>
       </c>
       <c r="B270">
-        <v>20220710</v>
+        <v>20210710</v>
       </c>
       <c r="C270">
         <f t="shared" ca="1" si="4"/>
@@ -11991,7 +11987,7 @@
         <v>30</v>
       </c>
       <c r="B271">
-        <v>20220717</v>
+        <v>20210717</v>
       </c>
       <c r="C271">
         <f t="shared" ca="1" si="4"/>
@@ -12003,7 +11999,7 @@
         <v>31</v>
       </c>
       <c r="B272">
-        <v>20220724</v>
+        <v>20210724</v>
       </c>
       <c r="C272">
         <f t="shared" ca="1" si="4"/>
@@ -12015,7 +12011,7 @@
         <v>32</v>
       </c>
       <c r="B273">
-        <v>20220801</v>
+        <v>20210801</v>
       </c>
       <c r="C273">
         <f t="shared" ca="1" si="4"/>
@@ -12027,7 +12023,7 @@
         <v>33</v>
       </c>
       <c r="B274">
-        <v>20220807</v>
+        <v>20210807</v>
       </c>
       <c r="C274">
         <f t="shared" ca="1" si="4"/>
@@ -12039,7 +12035,7 @@
         <v>34</v>
       </c>
       <c r="B275">
-        <v>20220814</v>
+        <v>20210814</v>
       </c>
       <c r="C275">
         <f t="shared" ca="1" si="4"/>
@@ -12051,7 +12047,7 @@
         <v>35</v>
       </c>
       <c r="B276">
-        <v>20220821</v>
+        <v>20210821</v>
       </c>
       <c r="C276">
         <f t="shared" ca="1" si="4"/>
@@ -12063,7 +12059,7 @@
         <v>36</v>
       </c>
       <c r="B277">
-        <v>20220828</v>
+        <v>20210828</v>
       </c>
       <c r="C277">
         <f t="shared" ca="1" si="4"/>
@@ -12075,7 +12071,7 @@
         <v>36</v>
       </c>
       <c r="B278">
-        <v>20220897</v>
+        <v>20210897</v>
       </c>
       <c r="C278">
         <f t="shared" ca="1" si="4"/>
@@ -12087,7 +12083,7 @@
         <v>37</v>
       </c>
       <c r="B279">
-        <v>20220904</v>
+        <v>20210904</v>
       </c>
       <c r="C279">
         <f t="shared" ca="1" si="4"/>
@@ -12099,7 +12095,7 @@
         <v>38</v>
       </c>
       <c r="B280">
-        <v>20220911</v>
+        <v>20210911</v>
       </c>
       <c r="C280">
         <f t="shared" ca="1" si="4"/>
@@ -12111,7 +12107,7 @@
         <v>39</v>
       </c>
       <c r="B281">
-        <v>20220918</v>
+        <v>20210918</v>
       </c>
       <c r="C281">
         <f t="shared" ca="1" si="4"/>
@@ -12123,7 +12119,7 @@
         <v>40</v>
       </c>
       <c r="B282">
-        <v>20220925</v>
+        <v>20210925</v>
       </c>
       <c r="C282">
         <f t="shared" ca="1" si="4"/>
@@ -12135,7 +12131,7 @@
         <v>41</v>
       </c>
       <c r="B283">
-        <v>20221002</v>
+        <v>20211002</v>
       </c>
       <c r="C283">
         <f t="shared" ca="1" si="4"/>
@@ -12147,7 +12143,7 @@
         <v>42</v>
       </c>
       <c r="B284">
-        <v>20221009</v>
+        <v>20211009</v>
       </c>
       <c r="C284">
         <f t="shared" ca="1" si="4"/>
@@ -12159,7 +12155,7 @@
         <v>43</v>
       </c>
       <c r="B285">
-        <v>20221016</v>
+        <v>20211016</v>
       </c>
       <c r="C285">
         <f t="shared" ca="1" si="4"/>
@@ -12171,7 +12167,7 @@
         <v>44</v>
       </c>
       <c r="B286">
-        <v>20221023</v>
+        <v>20211023</v>
       </c>
       <c r="C286">
         <f t="shared" ca="1" si="4"/>
@@ -12183,7 +12179,7 @@
         <v>45</v>
       </c>
       <c r="B287">
-        <v>20221030</v>
+        <v>20211030</v>
       </c>
       <c r="C287">
         <f t="shared" ca="1" si="4"/>
@@ -12195,7 +12191,7 @@
         <v>45</v>
       </c>
       <c r="B288">
-        <v>20221099</v>
+        <v>20211099</v>
       </c>
       <c r="C288">
         <f t="shared" ca="1" si="4"/>
@@ -12207,7 +12203,7 @@
         <v>46</v>
       </c>
       <c r="B289">
-        <v>20221106</v>
+        <v>20211106</v>
       </c>
       <c r="C289">
         <f t="shared" ca="1" si="4"/>
@@ -12219,7 +12215,7 @@
         <v>47</v>
       </c>
       <c r="B290">
-        <v>20221113</v>
+        <v>20211113</v>
       </c>
       <c r="C290">
         <f t="shared" ca="1" si="4"/>
@@ -12231,7 +12227,7 @@
         <v>48</v>
       </c>
       <c r="B291">
-        <v>20221120</v>
+        <v>20211120</v>
       </c>
       <c r="C291">
         <f t="shared" ca="1" si="4"/>
@@ -12243,7 +12239,7 @@
         <v>49</v>
       </c>
       <c r="B292">
-        <v>20221127</v>
+        <v>20211127</v>
       </c>
       <c r="C292">
         <f t="shared" ca="1" si="4"/>
@@ -12255,7 +12251,7 @@
         <v>49</v>
       </c>
       <c r="B293">
-        <v>20221197</v>
+        <v>20211197</v>
       </c>
       <c r="C293">
         <f t="shared" ca="1" si="4"/>
@@ -12267,7 +12263,7 @@
         <v>50</v>
       </c>
       <c r="B294">
-        <v>20221204</v>
+        <v>20211204</v>
       </c>
       <c r="C294">
         <f t="shared" ca="1" si="4"/>
@@ -12279,7 +12275,7 @@
         <v>51</v>
       </c>
       <c r="B295">
-        <v>20221211</v>
+        <v>20211211</v>
       </c>
       <c r="C295">
         <f t="shared" ca="1" si="4"/>
@@ -12291,7 +12287,7 @@
         <v>52</v>
       </c>
       <c r="B296">
-        <v>20221218</v>
+        <v>20211218</v>
       </c>
       <c r="C296">
         <f t="shared" ca="1" si="4"/>
@@ -12303,7 +12299,7 @@
         <v>53</v>
       </c>
       <c r="B297">
-        <v>20221225</v>
+        <v>20211225</v>
       </c>
       <c r="C297">
         <f t="shared" ca="1" si="4"/>
@@ -12315,7 +12311,7 @@
         <v>1</v>
       </c>
       <c r="B298">
-        <v>20230101</v>
+        <v>20220101</v>
       </c>
       <c r="C298">
         <f t="shared" ca="1" si="4"/>
@@ -12327,7 +12323,7 @@
         <v>2</v>
       </c>
       <c r="B299">
-        <v>20230108</v>
+        <v>20220108</v>
       </c>
       <c r="C299">
         <f t="shared" ca="1" si="4"/>
@@ -12339,7 +12335,7 @@
         <v>3</v>
       </c>
       <c r="B300">
-        <v>20230115</v>
+        <v>20220115</v>
       </c>
       <c r="C300">
         <f t="shared" ca="1" si="4"/>
@@ -12351,7 +12347,7 @@
         <v>4</v>
       </c>
       <c r="B301">
-        <v>20230122</v>
+        <v>20220122</v>
       </c>
       <c r="C301">
         <f t="shared" ca="1" si="4"/>
@@ -12363,7 +12359,7 @@
         <v>5</v>
       </c>
       <c r="B302">
-        <v>20230129</v>
+        <v>20220129</v>
       </c>
       <c r="C302">
         <f t="shared" ca="1" si="4"/>
@@ -12375,7 +12371,7 @@
         <v>5</v>
       </c>
       <c r="B303">
-        <v>20230198</v>
+        <v>20220198</v>
       </c>
       <c r="C303">
         <f t="shared" ca="1" si="4"/>
@@ -12387,199 +12383,200 @@
         <v>6</v>
       </c>
       <c r="B304">
-        <v>20230205</v>
+        <v>20220205</v>
       </c>
       <c r="C304">
         <f t="shared" ca="1" si="4"/>
         <v>139.86838913148958</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>7</v>
       </c>
       <c r="B305">
-        <v>20230212</v>
+        <v>20220212</v>
       </c>
       <c r="C305">
         <f t="shared" ca="1" si="4"/>
         <v>124.48144104803494</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>8</v>
       </c>
       <c r="B306">
-        <v>20230219</v>
+        <v>20220219</v>
       </c>
       <c r="C306">
         <f t="shared" ca="1" si="4"/>
         <v>97.052401746724897</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>9</v>
       </c>
       <c r="B307">
-        <v>20230226</v>
+        <v>20220226</v>
       </c>
       <c r="C307">
         <f t="shared" ca="1" si="4"/>
         <v>41.184497816593883</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>9</v>
       </c>
       <c r="B308">
-        <v>20230298</v>
+        <v>20220298</v>
       </c>
       <c r="C308">
         <f t="shared" ca="1" si="4"/>
         <v>83.454633672974282</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>10</v>
       </c>
       <c r="B309">
-        <v>20230305</v>
+        <v>20220305</v>
       </c>
       <c r="C309">
         <f t="shared" ca="1" si="4"/>
         <v>134.83290878214461</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>11</v>
       </c>
       <c r="B310">
-        <v>20230312</v>
+        <v>20220312</v>
       </c>
       <c r="C310">
         <f t="shared" ca="1" si="4"/>
         <v>110.3438864628821</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>12</v>
       </c>
       <c r="B311">
-        <v>20230319</v>
+        <v>20220319</v>
       </c>
       <c r="C311">
         <f t="shared" ca="1" si="4"/>
         <v>104.58515283842796</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>13</v>
       </c>
       <c r="B312">
-        <v>20230326</v>
+        <v>20220326</v>
       </c>
       <c r="C312">
         <f t="shared" ca="1" si="4"/>
         <v>112.36656962639495</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>13</v>
       </c>
       <c r="B313">
-        <v>20230395</v>
+        <v>20220395</v>
       </c>
       <c r="C313">
         <f t="shared" ca="1" si="4"/>
         <v>8.1877729257641918E-2</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>14</v>
       </c>
       <c r="B314">
-        <v>20230402</v>
+        <v>20220402</v>
       </c>
       <c r="C314">
         <f t="shared" ca="1" si="4"/>
         <v>108.98077389616691</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>15</v>
       </c>
       <c r="B315">
-        <v>20230409</v>
+        <v>20220409</v>
       </c>
       <c r="C315">
         <f t="shared" ca="1" si="4"/>
         <v>152.51698204754973</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>16</v>
       </c>
       <c r="B316">
-        <v>20230416</v>
+        <v>20220416</v>
       </c>
       <c r="C316">
         <f t="shared" ca="1" si="4"/>
         <v>100.51855895196506</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>17</v>
       </c>
       <c r="B317">
-        <v>20230423</v>
+        <v>20220423</v>
       </c>
       <c r="C317">
         <f t="shared" ca="1" si="4"/>
         <v>113.40065502183405</v>
       </c>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="O317" s="3"/>
+    </row>
+    <row r="318" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>18</v>
       </c>
       <c r="B318">
-        <v>20230501</v>
+        <v>20220501</v>
       </c>
       <c r="C318">
         <f t="shared" ca="1" si="4"/>
         <v>86.16266375545851</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>19</v>
       </c>
       <c r="B319">
-        <v>20230507</v>
+        <v>20220507</v>
       </c>
       <c r="C319">
         <f t="shared" ca="1" si="4"/>
         <v>143.75606501698203</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>20</v>
       </c>
       <c r="B320">
-        <v>20230514</v>
+        <v>20220514</v>
       </c>
       <c r="C320">
         <f t="shared" ca="1" si="4"/>
@@ -12591,7 +12588,7 @@
         <v>21</v>
       </c>
       <c r="B321">
-        <v>20230521</v>
+        <v>20220521</v>
       </c>
       <c r="C321">
         <f t="shared" ca="1" si="4"/>
@@ -12603,7 +12600,7 @@
         <v>22</v>
       </c>
       <c r="B322">
-        <v>20230528</v>
+        <v>20220528</v>
       </c>
       <c r="C322">
         <f t="shared" ca="1" si="4"/>
@@ -12615,10 +12612,10 @@
         <v>22</v>
       </c>
       <c r="B323">
-        <v>20230597</v>
+        <v>20220597</v>
       </c>
       <c r="C323">
-        <f t="shared" ref="C323:D342" ca="1" si="5">(B323/$C$2)*100</f>
+        <f t="shared" ref="C323:C342" ca="1" si="5">(B323/$C$2)*100</f>
         <v>49.42685589519651</v>
       </c>
     </row>
@@ -12627,7 +12624,7 @@
         <v>23</v>
       </c>
       <c r="B324">
-        <v>20230604</v>
+        <v>20220604</v>
       </c>
       <c r="C324">
         <f t="shared" ca="1" si="5"/>
@@ -12639,7 +12636,7 @@
         <v>24</v>
       </c>
       <c r="B325">
-        <v>20230611</v>
+        <v>20220611</v>
       </c>
       <c r="C325">
         <f t="shared" ca="1" si="5"/>
@@ -12651,7 +12648,7 @@
         <v>25</v>
       </c>
       <c r="B326">
-        <v>20230618</v>
+        <v>20220618</v>
       </c>
       <c r="C326">
         <f t="shared" ca="1" si="5"/>
@@ -12663,7 +12660,7 @@
         <v>26</v>
       </c>
       <c r="B327">
-        <v>20230625</v>
+        <v>20220625</v>
       </c>
       <c r="C327">
         <f t="shared" ca="1" si="5"/>
@@ -12675,7 +12672,7 @@
         <v>27</v>
       </c>
       <c r="B328">
-        <v>20230702</v>
+        <v>20220702</v>
       </c>
       <c r="C328">
         <f t="shared" ca="1" si="5"/>
@@ -12687,7 +12684,7 @@
         <v>28</v>
       </c>
       <c r="B329">
-        <v>20230709</v>
+        <v>20220709</v>
       </c>
       <c r="C329">
         <f t="shared" ca="1" si="5"/>
@@ -12699,7 +12696,7 @@
         <v>29</v>
       </c>
       <c r="B330">
-        <v>20230716</v>
+        <v>20220716</v>
       </c>
       <c r="C330">
         <f t="shared" ca="1" si="5"/>
@@ -12711,7 +12708,7 @@
         <v>30</v>
       </c>
       <c r="B331">
-        <v>20230723</v>
+        <v>20220723</v>
       </c>
       <c r="C331">
         <f t="shared" ca="1" si="5"/>
@@ -12723,7 +12720,7 @@
         <v>31</v>
       </c>
       <c r="B332">
-        <v>20230730</v>
+        <v>20220730</v>
       </c>
       <c r="C332">
         <f t="shared" ca="1" si="5"/>
@@ -12735,7 +12732,7 @@
         <v>31</v>
       </c>
       <c r="B333">
-        <v>20230799</v>
+        <v>20220799</v>
       </c>
       <c r="C333">
         <f t="shared" ca="1" si="5"/>
@@ -12747,7 +12744,7 @@
         <v>32</v>
       </c>
       <c r="B334">
-        <v>20230806</v>
+        <v>20220806</v>
       </c>
       <c r="C334">
         <f t="shared" ca="1" si="5"/>
@@ -12759,7 +12756,7 @@
         <v>33</v>
       </c>
       <c r="B335">
-        <v>20230813</v>
+        <v>20220813</v>
       </c>
       <c r="C335">
         <f t="shared" ca="1" si="5"/>
@@ -12771,7 +12768,7 @@
         <v>34</v>
       </c>
       <c r="B336">
-        <v>20230820</v>
+        <v>20220820</v>
       </c>
       <c r="C336">
         <f t="shared" ca="1" si="5"/>
@@ -12783,7 +12780,7 @@
         <v>35</v>
       </c>
       <c r="B337">
-        <v>20230827</v>
+        <v>20220827</v>
       </c>
       <c r="C337">
         <f t="shared" ca="1" si="5"/>
@@ -12795,7 +12792,7 @@
         <v>35</v>
       </c>
       <c r="B338">
-        <v>20230896</v>
+        <v>20220896</v>
       </c>
       <c r="C338">
         <f t="shared" ca="1" si="5"/>
@@ -12807,7 +12804,7 @@
         <v>36</v>
       </c>
       <c r="B339">
-        <v>20230903</v>
+        <v>20220903</v>
       </c>
       <c r="C339">
         <f t="shared" ca="1" si="5"/>
@@ -12819,7 +12816,7 @@
         <v>37</v>
       </c>
       <c r="B340">
-        <v>20230910</v>
+        <v>20220910</v>
       </c>
       <c r="C340">
         <f t="shared" ca="1" si="5"/>
@@ -12831,7 +12828,7 @@
         <v>38</v>
       </c>
       <c r="B341">
-        <v>20230917</v>
+        <v>20220917</v>
       </c>
       <c r="C341">
         <f t="shared" ca="1" si="5"/>
@@ -12843,7 +12840,7 @@
         <v>39</v>
       </c>
       <c r="B342">
-        <v>20230924</v>
+        <v>20220924</v>
       </c>
       <c r="C342">
         <f t="shared" ca="1" si="5"/>
